--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120473472</v>
+        <v>120470646</v>
       </c>
       <c r="B2" t="n">
-        <v>78624</v>
+        <v>96885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730920</v>
+        <v>730765</v>
       </c>
       <c r="R2" t="n">
-        <v>7280729</v>
+        <v>7280814</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120473837</v>
+        <v>120470546</v>
       </c>
       <c r="B3" t="n">
         <v>78624</v>
@@ -824,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730743</v>
+        <v>730856</v>
       </c>
       <c r="R3" t="n">
-        <v>7280839</v>
+        <v>7280769</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -854,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120470659</v>
+        <v>120470942</v>
       </c>
       <c r="B4" t="n">
-        <v>78624</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730744</v>
+        <v>730551</v>
       </c>
       <c r="R4" t="n">
-        <v>7280840</v>
+        <v>7281090</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120470660</v>
+        <v>120470931</v>
       </c>
       <c r="B5" t="n">
-        <v>96885</v>
+        <v>56532</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,27 +1010,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730744</v>
+        <v>730544</v>
       </c>
       <c r="R5" t="n">
-        <v>7280840</v>
+        <v>7281102</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1081,7 +1098,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1100,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120470614</v>
+        <v>120473443</v>
       </c>
       <c r="B6" t="n">
-        <v>56524</v>
+        <v>78624</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,27 +1132,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1144,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730776</v>
+        <v>730845</v>
       </c>
       <c r="R6" t="n">
-        <v>7280790</v>
+        <v>7280809</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1174,12 +1189,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,6 +1203,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1206,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120473407</v>
+        <v>120473397</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>57431</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,30 +1234,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1249,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730907</v>
+        <v>730897</v>
       </c>
       <c r="R7" t="n">
-        <v>7280757</v>
+        <v>7280732</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,13 +1312,17 @@
           <t>2024-08-15</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>En familjgrupp i sitt revir. Det är gruppen som håller till kring Kikkejaureberget/Tjitterberget men mycket av deras revir och hemvist i naturskogsresterna har undan för undan avverkats trots miljölöften av statliga Sveaskog. Även aktuell fyndplats i naturskogsrestfragment är planerad för kalavverkning och markberedning!</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1312,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120473140</v>
+        <v>120473472</v>
       </c>
       <c r="B8" t="n">
-        <v>78576</v>
+        <v>78624</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1384,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730799</v>
+        <v>730920</v>
       </c>
       <c r="R8" t="n">
-        <v>7280750</v>
+        <v>7280729</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1418,10 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120473156</v>
+        <v>120473462</v>
       </c>
       <c r="B9" t="n">
-        <v>78624</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,21 +1463,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730803</v>
+        <v>730869</v>
       </c>
       <c r="R9" t="n">
-        <v>7280729</v>
+        <v>7280791</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1524,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120470888</v>
+        <v>120473485</v>
       </c>
       <c r="B10" t="n">
-        <v>78576</v>
+        <v>57336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,37 +1569,54 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran , Pi lm</t>
+          <t>Garpmesliden-Römyran, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730611</v>
+        <v>730938</v>
       </c>
       <c r="R10" t="n">
-        <v>7281039</v>
+        <v>7280716</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1597,12 +1643,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1611,7 +1657,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1630,10 +1675,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120470931</v>
+        <v>120473635</v>
       </c>
       <c r="B11" t="n">
-        <v>56532</v>
+        <v>79131</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1642,47 +1687,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1690,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>730544</v>
+        <v>730880</v>
       </c>
       <c r="R11" t="n">
-        <v>7281102</v>
+        <v>7280720</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1720,12 +1748,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,6 +1762,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1752,10 +1781,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120470887</v>
+        <v>120473545</v>
       </c>
       <c r="B12" t="n">
-        <v>96885</v>
+        <v>56532</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1768,27 +1797,35 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1796,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730622</v>
+        <v>730894</v>
       </c>
       <c r="R12" t="n">
-        <v>7281028</v>
+        <v>7280702</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1826,12 +1863,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Env höna med sina nästan utvuxna kycklingar på födosök i häckningsområdet.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1840,7 +1882,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1859,10 +1900,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120470889</v>
+        <v>120470655</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1875,21 +1916,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1898,14 +1939,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran , Pi lm</t>
+          <t>Garpmesliden-Römyran, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730611</v>
+        <v>730744</v>
       </c>
       <c r="R13" t="n">
-        <v>7281039</v>
+        <v>7280840</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1965,10 +2006,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120470795</v>
+        <v>120470789</v>
       </c>
       <c r="B14" t="n">
-        <v>90545</v>
+        <v>78576</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1977,25 +2018,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2071,10 +2112,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120470809</v>
+        <v>120470957</v>
       </c>
       <c r="B15" t="n">
-        <v>96885</v>
+        <v>82321</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2083,31 +2124,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2115,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730676</v>
+        <v>730533</v>
       </c>
       <c r="R15" t="n">
-        <v>7280903</v>
+        <v>7281130</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2178,10 +2218,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120473754</v>
+        <v>120470614</v>
       </c>
       <c r="B16" t="n">
-        <v>78624</v>
+        <v>56524</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2194,26 +2234,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2221,10 +2262,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730833</v>
+        <v>730776</v>
       </c>
       <c r="R16" t="n">
-        <v>7280805</v>
+        <v>7280790</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2251,12 +2292,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2265,7 +2306,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2284,10 +2324,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120473807</v>
+        <v>120470659</v>
       </c>
       <c r="B17" t="n">
-        <v>57473</v>
+        <v>78624</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2300,35 +2340,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>revir, ej häckning</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2336,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730795</v>
+        <v>730744</v>
       </c>
       <c r="R17" t="n">
-        <v>7280824</v>
+        <v>7280840</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2366,17 +2397,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ett par med årets ungar i parets hemvist och häckningsrevir</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2385,6 +2411,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2403,10 +2430,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120473143</v>
+        <v>120470896</v>
       </c>
       <c r="B18" t="n">
-        <v>82321</v>
+        <v>78576</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2419,21 +2446,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2446,10 +2473,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730799</v>
+        <v>730587</v>
       </c>
       <c r="R18" t="n">
-        <v>7280750</v>
+        <v>7281038</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2476,12 +2503,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,10 +2536,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120470475</v>
+        <v>120470888</v>
       </c>
       <c r="B19" t="n">
-        <v>78624</v>
+        <v>78576</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,21 +2552,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2548,14 +2575,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran, Pi lm</t>
+          <t>Garpmesliden-Römyran , Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>730827</v>
+        <v>730611</v>
       </c>
       <c r="R19" t="n">
-        <v>7280751</v>
+        <v>7281039</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2615,7 +2642,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120473475</v>
+        <v>120470478</v>
       </c>
       <c r="B20" t="n">
         <v>82321</v>
@@ -2658,10 +2685,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730920</v>
+        <v>730827</v>
       </c>
       <c r="R20" t="n">
-        <v>7280729</v>
+        <v>7280751</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2688,12 +2715,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2721,10 +2748,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120473694</v>
+        <v>120473697</v>
       </c>
       <c r="B21" t="n">
-        <v>57336</v>
+        <v>78576</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2737,31 +2764,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2813,6 +2835,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2831,10 +2854,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120473423</v>
+        <v>120473746</v>
       </c>
       <c r="B22" t="n">
-        <v>78576</v>
+        <v>82321</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2847,21 +2870,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2874,10 +2897,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730869</v>
+        <v>730814</v>
       </c>
       <c r="R22" t="n">
-        <v>7280766</v>
+        <v>7280788</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2937,10 +2960,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120473194</v>
+        <v>120473444</v>
       </c>
       <c r="B23" t="n">
-        <v>79160</v>
+        <v>82321</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2953,21 +2976,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2980,10 +3003,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730852</v>
+        <v>730845</v>
       </c>
       <c r="R23" t="n">
-        <v>7280740</v>
+        <v>7280809</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3043,10 +3066,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120470940</v>
+        <v>120470660</v>
       </c>
       <c r="B24" t="n">
-        <v>82321</v>
+        <v>96885</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3055,30 +3078,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3086,10 +3110,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>730551</v>
+        <v>730744</v>
       </c>
       <c r="R24" t="n">
-        <v>7281090</v>
+        <v>7280840</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3149,10 +3173,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120470622</v>
+        <v>120470872</v>
       </c>
       <c r="B25" t="n">
-        <v>96885</v>
+        <v>82321</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3161,31 +3185,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3193,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>730781</v>
+        <v>730630</v>
       </c>
       <c r="R25" t="n">
-        <v>7280800</v>
+        <v>7280999</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3256,10 +3279,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120470858</v>
+        <v>120473808</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>78624</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3272,21 +3295,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3299,10 +3322,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730638</v>
+        <v>730795</v>
       </c>
       <c r="R26" t="n">
-        <v>7280995</v>
+        <v>7280824</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3329,12 +3352,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3362,10 +3385,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120470733</v>
+        <v>120473129</v>
       </c>
       <c r="B27" t="n">
-        <v>82321</v>
+        <v>90594</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3378,21 +3401,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3405,10 +3428,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730717</v>
+        <v>730789</v>
       </c>
       <c r="R27" t="n">
-        <v>7280872</v>
+        <v>7280765</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3435,12 +3458,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3468,10 +3491,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120473413</v>
+        <v>120470997</v>
       </c>
       <c r="B28" t="n">
-        <v>82321</v>
+        <v>78576</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3484,21 +3507,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3511,10 +3534,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730907</v>
+        <v>730452</v>
       </c>
       <c r="R28" t="n">
-        <v>7280757</v>
+        <v>7281226</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3541,12 +3564,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3574,7 +3597,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120473443</v>
+        <v>120470475</v>
       </c>
       <c r="B29" t="n">
         <v>78624</v>
@@ -3617,10 +3640,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730845</v>
+        <v>730827</v>
       </c>
       <c r="R29" t="n">
-        <v>7280809</v>
+        <v>7280751</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3647,12 +3670,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3680,7 +3703,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120470617</v>
+        <v>120470809</v>
       </c>
       <c r="B30" t="n">
         <v>96885</v>
@@ -3724,10 +3747,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730776</v>
+        <v>730676</v>
       </c>
       <c r="R30" t="n">
-        <v>7280790</v>
+        <v>7280903</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3787,10 +3810,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120470655</v>
+        <v>120470917</v>
       </c>
       <c r="B31" t="n">
-        <v>82321</v>
+        <v>96885</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3799,30 +3822,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3830,10 +3854,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730744</v>
+        <v>730563</v>
       </c>
       <c r="R31" t="n">
-        <v>7280840</v>
+        <v>7281056</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3893,7 +3917,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120470478</v>
+        <v>120470940</v>
       </c>
       <c r="B32" t="n">
         <v>82321</v>
@@ -3936,10 +3960,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730827</v>
+        <v>730551</v>
       </c>
       <c r="R32" t="n">
-        <v>7280751</v>
+        <v>7281090</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3999,7 +4023,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120470909</v>
+        <v>120470739</v>
       </c>
       <c r="B33" t="n">
         <v>78542</v>
@@ -4042,10 +4066,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>730587</v>
+        <v>730717</v>
       </c>
       <c r="R33" t="n">
-        <v>7281038</v>
+        <v>7280872</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4105,10 +4129,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120473571</v>
+        <v>120470935</v>
       </c>
       <c r="B34" t="n">
-        <v>90506</v>
+        <v>82321</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4121,21 +4145,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3242</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4148,10 +4172,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730915</v>
+        <v>730544</v>
       </c>
       <c r="R34" t="n">
-        <v>7280682</v>
+        <v>7281102</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4178,12 +4202,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4211,10 +4235,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120473410</v>
+        <v>120470795</v>
       </c>
       <c r="B35" t="n">
-        <v>78624</v>
+        <v>90545</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4223,25 +4247,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>864</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4254,10 +4278,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730907</v>
+        <v>730676</v>
       </c>
       <c r="R35" t="n">
-        <v>7280757</v>
+        <v>7280903</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4284,12 +4308,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4317,10 +4341,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120470646</v>
+        <v>120473571</v>
       </c>
       <c r="B36" t="n">
-        <v>96885</v>
+        <v>90506</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4329,31 +4353,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>3242</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4361,10 +4384,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730765</v>
+        <v>730915</v>
       </c>
       <c r="R36" t="n">
-        <v>7280814</v>
+        <v>7280682</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4391,12 +4414,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4424,10 +4447,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120470915</v>
+        <v>120473699</v>
       </c>
       <c r="B37" t="n">
-        <v>78576</v>
+        <v>89650</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4440,21 +4463,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>1962</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4467,10 +4490,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730563</v>
+        <v>730844</v>
       </c>
       <c r="R37" t="n">
-        <v>7281056</v>
+        <v>7280770</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4497,12 +4520,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4530,10 +4553,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120473547</v>
+        <v>120473694</v>
       </c>
       <c r="B38" t="n">
-        <v>91858</v>
+        <v>57336</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4542,30 +4565,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4573,10 +4601,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730894</v>
+        <v>730832</v>
       </c>
       <c r="R38" t="n">
-        <v>7280702</v>
+        <v>7280746</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4617,7 +4645,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4636,10 +4663,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120470896</v>
+        <v>120473156</v>
       </c>
       <c r="B39" t="n">
-        <v>78576</v>
+        <v>78624</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4652,21 +4679,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4679,10 +4706,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730587</v>
+        <v>730803</v>
       </c>
       <c r="R39" t="n">
-        <v>7281038</v>
+        <v>7280729</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4709,12 +4736,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4742,10 +4769,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120470964</v>
+        <v>120470733</v>
       </c>
       <c r="B40" t="n">
-        <v>97951</v>
+        <v>82321</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4754,31 +4781,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4786,10 +4812,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>730499</v>
+        <v>730717</v>
       </c>
       <c r="R40" t="n">
-        <v>7281141</v>
+        <v>7280872</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4849,10 +4875,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120473713</v>
+        <v>120470890</v>
       </c>
       <c r="B41" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4865,21 +4891,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4888,14 +4914,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran, Pi lm</t>
+          <t>Garpmesliden-Römyran , Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730844</v>
+        <v>730611</v>
       </c>
       <c r="R41" t="n">
-        <v>7280770</v>
+        <v>7281039</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4922,12 +4948,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4955,10 +4981,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120473217</v>
+        <v>120473565</v>
       </c>
       <c r="B42" t="n">
-        <v>79160</v>
+        <v>78576</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4971,21 +4997,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4998,10 +5024,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730876</v>
+        <v>730915</v>
       </c>
       <c r="R42" t="n">
-        <v>7280720</v>
+        <v>7280682</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5061,10 +5087,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120470620</v>
+        <v>120473807</v>
       </c>
       <c r="B43" t="n">
-        <v>82321</v>
+        <v>57473</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5077,26 +5103,35 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>revir, ej häckning</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5104,10 +5139,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>730781</v>
+        <v>730795</v>
       </c>
       <c r="R43" t="n">
-        <v>7280800</v>
+        <v>7280824</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5134,12 +5169,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ett par med årets ungar i parets hemvist och häckningsrevir</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5148,7 +5188,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5167,10 +5206,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120473592</v>
+        <v>120470812</v>
       </c>
       <c r="B44" t="n">
-        <v>74651</v>
+        <v>97951</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5183,26 +5222,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>311</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5210,10 +5250,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>730891</v>
+        <v>730676</v>
       </c>
       <c r="R44" t="n">
-        <v>7280715</v>
+        <v>7280903</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5240,12 +5280,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5273,10 +5313,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120473545</v>
+        <v>120473148</v>
       </c>
       <c r="B45" t="n">
-        <v>56532</v>
+        <v>82321</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5285,39 +5325,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5325,10 +5356,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>730894</v>
+        <v>730803</v>
       </c>
       <c r="R45" t="n">
-        <v>7280702</v>
+        <v>7280729</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5363,17 +5394,13 @@
           <t>2024-08-15</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Env höna med sina nästan utvuxna kycklingar på födosök i häckningsområdet.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5392,10 +5419,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120473746</v>
+        <v>120473492</v>
       </c>
       <c r="B46" t="n">
-        <v>82321</v>
+        <v>78576</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5408,21 +5435,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5435,10 +5462,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>730814</v>
+        <v>730912</v>
       </c>
       <c r="R46" t="n">
-        <v>7280788</v>
+        <v>7280701</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5498,10 +5525,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120473565</v>
+        <v>120470617</v>
       </c>
       <c r="B47" t="n">
-        <v>78576</v>
+        <v>96885</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5510,30 +5537,31 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5541,10 +5569,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>730915</v>
+        <v>730776</v>
       </c>
       <c r="R47" t="n">
-        <v>7280682</v>
+        <v>7280790</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5571,12 +5599,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5604,10 +5632,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120473159</v>
+        <v>120470889</v>
       </c>
       <c r="B48" t="n">
-        <v>96885</v>
+        <v>78542</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5616,42 +5644,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran, Pi lm</t>
+          <t>Garpmesliden-Römyran , Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>730803</v>
+        <v>730611</v>
       </c>
       <c r="R48" t="n">
-        <v>7280729</v>
+        <v>7281039</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5678,12 +5705,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5711,10 +5738,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120470914</v>
+        <v>120473407</v>
       </c>
       <c r="B49" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5727,21 +5754,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5754,10 +5781,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>730563</v>
+        <v>730907</v>
       </c>
       <c r="R49" t="n">
-        <v>7281056</v>
+        <v>7280757</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5784,12 +5811,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5817,10 +5844,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120470917</v>
+        <v>120473410</v>
       </c>
       <c r="B50" t="n">
-        <v>96885</v>
+        <v>78624</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5829,31 +5856,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221945</v>
+        <v>864</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5861,10 +5887,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>730563</v>
+        <v>730907</v>
       </c>
       <c r="R50" t="n">
-        <v>7281056</v>
+        <v>7280757</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5891,12 +5917,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5924,10 +5950,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120470748</v>
+        <v>120473467</v>
       </c>
       <c r="B51" t="n">
-        <v>78576</v>
+        <v>82321</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5940,21 +5966,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5967,10 +5993,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>730697</v>
+        <v>730894</v>
       </c>
       <c r="R51" t="n">
-        <v>7280886</v>
+        <v>7280757</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5997,12 +6023,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6030,10 +6056,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120473563</v>
+        <v>120473226</v>
       </c>
       <c r="B52" t="n">
-        <v>56524</v>
+        <v>90545</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6042,39 +6068,30 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6082,10 +6099,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>730915</v>
+        <v>730876</v>
       </c>
       <c r="R52" t="n">
-        <v>7280682</v>
+        <v>7280720</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6120,17 +6137,13 @@
           <t>2024-08-15</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>3 järpar i sin hemvist i den fuktiga gamla barrnaturskogen med sumpskogskaraktär som är planerad för kalhuggning och markberedning.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6149,10 +6162,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120473808</v>
+        <v>120470498</v>
       </c>
       <c r="B53" t="n">
-        <v>78624</v>
+        <v>57336</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6165,26 +6178,43 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>864</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6192,10 +6222,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>730795</v>
+        <v>730827</v>
       </c>
       <c r="R53" t="n">
-        <v>7280824</v>
+        <v>7280751</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6222,12 +6252,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6236,7 +6266,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6255,10 +6284,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120473450</v>
+        <v>120470955</v>
       </c>
       <c r="B54" t="n">
-        <v>77883</v>
+        <v>77489</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6267,25 +6296,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>498</v>
+        <v>314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6298,10 +6327,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>730869</v>
+        <v>730533</v>
       </c>
       <c r="R54" t="n">
-        <v>7280791</v>
+        <v>7281130</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6328,12 +6357,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6361,10 +6390,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120470812</v>
+        <v>120470620</v>
       </c>
       <c r="B55" t="n">
-        <v>97951</v>
+        <v>82321</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6373,31 +6402,30 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6405,10 +6433,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>730676</v>
+        <v>730781</v>
       </c>
       <c r="R55" t="n">
-        <v>7280903</v>
+        <v>7280800</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6468,7 +6496,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120470739</v>
+        <v>120473750</v>
       </c>
       <c r="B56" t="n">
         <v>78542</v>
@@ -6511,10 +6539,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>730717</v>
+        <v>730814</v>
       </c>
       <c r="R56" t="n">
-        <v>7280872</v>
+        <v>7280788</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6541,12 +6569,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6574,7 +6602,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120473420</v>
+        <v>120473143</v>
       </c>
       <c r="B57" t="n">
         <v>82321</v>
@@ -6617,10 +6645,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>730869</v>
+        <v>730799</v>
       </c>
       <c r="R57" t="n">
-        <v>7280766</v>
+        <v>7280750</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6680,10 +6708,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120473492</v>
+        <v>120470867</v>
       </c>
       <c r="B58" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6696,21 +6724,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6723,10 +6751,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730912</v>
+        <v>730630</v>
       </c>
       <c r="R58" t="n">
-        <v>7280701</v>
+        <v>7280999</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6753,12 +6781,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6786,10 +6814,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120470935</v>
+        <v>120473572</v>
       </c>
       <c r="B59" t="n">
-        <v>82321</v>
+        <v>77474</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6802,21 +6830,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1312</v>
+        <v>6487</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6829,10 +6857,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>730544</v>
+        <v>730891</v>
       </c>
       <c r="R59" t="n">
-        <v>7281102</v>
+        <v>7280715</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6859,12 +6887,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6998,7 +7026,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120473775</v>
+        <v>120473837</v>
       </c>
       <c r="B61" t="n">
         <v>78624</v>
@@ -7041,10 +7069,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>730816</v>
+        <v>730743</v>
       </c>
       <c r="R61" t="n">
-        <v>7280822</v>
+        <v>7280839</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7104,10 +7132,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120473226</v>
+        <v>120473132</v>
       </c>
       <c r="B62" t="n">
-        <v>90545</v>
+        <v>96885</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7120,26 +7148,27 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7147,10 +7176,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>730876</v>
+        <v>730789</v>
       </c>
       <c r="R62" t="n">
-        <v>7280720</v>
+        <v>7280765</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7210,10 +7239,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120473485</v>
+        <v>120473194</v>
       </c>
       <c r="B63" t="n">
-        <v>57336</v>
+        <v>79160</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7226,43 +7255,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7270,10 +7282,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>730938</v>
+        <v>730852</v>
       </c>
       <c r="R63" t="n">
-        <v>7280716</v>
+        <v>7280740</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7314,6 +7326,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7332,10 +7345,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120470867</v>
+        <v>120473201</v>
       </c>
       <c r="B64" t="n">
-        <v>78542</v>
+        <v>96891</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7344,30 +7357,31 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7375,10 +7389,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>730630</v>
+        <v>730852</v>
       </c>
       <c r="R64" t="n">
-        <v>7280999</v>
+        <v>7280740</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7405,12 +7419,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7438,10 +7452,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120470546</v>
+        <v>120473413</v>
       </c>
       <c r="B65" t="n">
-        <v>78624</v>
+        <v>82321</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7454,21 +7468,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7481,10 +7495,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>730856</v>
+        <v>730907</v>
       </c>
       <c r="R65" t="n">
-        <v>7280769</v>
+        <v>7280757</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7511,12 +7525,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7544,10 +7558,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120470945</v>
+        <v>120470858</v>
       </c>
       <c r="B66" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7560,21 +7574,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7587,10 +7601,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>730551</v>
+        <v>730638</v>
       </c>
       <c r="R66" t="n">
-        <v>7281090</v>
+        <v>7280995</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7650,7 +7664,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120473750</v>
+        <v>120470967</v>
       </c>
       <c r="B67" t="n">
         <v>78542</v>
@@ -7693,10 +7707,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>730814</v>
+        <v>730499</v>
       </c>
       <c r="R67" t="n">
-        <v>7280788</v>
+        <v>7281166</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7723,12 +7737,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7756,10 +7770,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120470942</v>
+        <v>120470964</v>
       </c>
       <c r="B68" t="n">
-        <v>78542</v>
+        <v>97951</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7768,30 +7782,31 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7799,10 +7814,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>730551</v>
+        <v>730499</v>
       </c>
       <c r="R68" t="n">
-        <v>7281090</v>
+        <v>7281141</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7862,10 +7877,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120470853</v>
+        <v>120470914</v>
       </c>
       <c r="B69" t="n">
-        <v>82321</v>
+        <v>90594</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7878,21 +7893,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7905,10 +7920,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>730639</v>
+        <v>730563</v>
       </c>
       <c r="R69" t="n">
-        <v>7280973</v>
+        <v>7281056</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7968,10 +7983,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120470498</v>
+        <v>120473423</v>
       </c>
       <c r="B70" t="n">
-        <v>57336</v>
+        <v>78576</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7984,43 +7999,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8028,10 +8026,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>730827</v>
+        <v>730869</v>
       </c>
       <c r="R70" t="n">
-        <v>7280751</v>
+        <v>7280766</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8058,12 +8056,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8072,6 +8070,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8090,10 +8089,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120470997</v>
+        <v>120473835</v>
       </c>
       <c r="B71" t="n">
-        <v>78576</v>
+        <v>97951</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8102,30 +8101,31 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -8133,10 +8133,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>730452</v>
+        <v>730783</v>
       </c>
       <c r="R71" t="n">
-        <v>7281226</v>
+        <v>7280820</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8163,12 +8163,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8196,10 +8196,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120473835</v>
+        <v>120470887</v>
       </c>
       <c r="B72" t="n">
-        <v>97951</v>
+        <v>96885</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8212,21 +8212,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8240,10 +8240,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>730783</v>
+        <v>730622</v>
       </c>
       <c r="R72" t="n">
-        <v>7280820</v>
+        <v>7281028</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8270,12 +8270,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8303,10 +8303,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120473148</v>
+        <v>120473756</v>
       </c>
       <c r="B73" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8319,21 +8319,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8346,10 +8346,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>730803</v>
+        <v>730833</v>
       </c>
       <c r="R73" t="n">
-        <v>7280729</v>
+        <v>7280805</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8409,7 +8409,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120473756</v>
+        <v>120473713</v>
       </c>
       <c r="B74" t="n">
         <v>78542</v>
@@ -8452,10 +8452,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>730833</v>
+        <v>730844</v>
       </c>
       <c r="R74" t="n">
-        <v>7280805</v>
+        <v>7280770</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8515,10 +8515,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120473635</v>
+        <v>120473140</v>
       </c>
       <c r="B75" t="n">
-        <v>79131</v>
+        <v>78576</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8531,21 +8531,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8558,10 +8558,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>730880</v>
+        <v>730799</v>
       </c>
       <c r="R75" t="n">
-        <v>7280720</v>
+        <v>7280750</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8621,10 +8621,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120473626</v>
+        <v>120473592</v>
       </c>
       <c r="B76" t="n">
-        <v>79160</v>
+        <v>74651</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8633,25 +8633,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>311</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8664,10 +8664,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>730880</v>
+        <v>730891</v>
       </c>
       <c r="R76" t="n">
-        <v>7280720</v>
+        <v>7280715</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8727,10 +8727,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120473132</v>
+        <v>120473626</v>
       </c>
       <c r="B77" t="n">
-        <v>96885</v>
+        <v>79160</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8739,31 +8739,30 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8771,10 +8770,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>730789</v>
+        <v>730880</v>
       </c>
       <c r="R77" t="n">
-        <v>7280765</v>
+        <v>7280720</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8834,10 +8833,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120473397</v>
+        <v>120470748</v>
       </c>
       <c r="B78" t="n">
-        <v>57431</v>
+        <v>78576</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8846,39 +8845,30 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103031</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -8886,10 +8876,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>730897</v>
+        <v>730697</v>
       </c>
       <c r="R78" t="n">
-        <v>7280732</v>
+        <v>7280886</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8916,17 +8906,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>En familjgrupp i sitt revir. Det är gruppen som håller till kring Kikkejaureberget/Tjitterberget men mycket av deras revir och hemvist i naturskogsresterna har undan för undan avverkats trots miljölöften av statliga Sveaskog. Även aktuell fyndplats i naturskogsrestfragment är planerad för kalavverkning och markberedning!</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8935,6 +8920,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8953,10 +8939,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120473699</v>
+        <v>120470909</v>
       </c>
       <c r="B79" t="n">
-        <v>89650</v>
+        <v>78542</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8969,21 +8955,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8996,10 +8982,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>730844</v>
+        <v>730587</v>
       </c>
       <c r="R79" t="n">
-        <v>7280770</v>
+        <v>7281038</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9026,12 +9012,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9059,10 +9045,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120473201</v>
+        <v>120470915</v>
       </c>
       <c r="B80" t="n">
-        <v>96891</v>
+        <v>78576</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9071,31 +9057,30 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221941</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9103,10 +9088,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>730852</v>
+        <v>730563</v>
       </c>
       <c r="R80" t="n">
-        <v>7280740</v>
+        <v>7281056</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9133,12 +9118,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9166,10 +9151,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120473129</v>
+        <v>120473754</v>
       </c>
       <c r="B81" t="n">
-        <v>90594</v>
+        <v>78624</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9182,21 +9167,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9209,10 +9194,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>730789</v>
+        <v>730833</v>
       </c>
       <c r="R81" t="n">
-        <v>7280765</v>
+        <v>7280805</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9272,10 +9257,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120470789</v>
+        <v>120473775</v>
       </c>
       <c r="B82" t="n">
-        <v>78576</v>
+        <v>78624</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9288,21 +9273,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9315,10 +9300,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>730676</v>
+        <v>730816</v>
       </c>
       <c r="R82" t="n">
-        <v>7280903</v>
+        <v>7280822</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9345,12 +9330,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9378,10 +9363,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120470955</v>
+        <v>120473421</v>
       </c>
       <c r="B83" t="n">
-        <v>77489</v>
+        <v>78542</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9394,21 +9379,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9421,10 +9406,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>730533</v>
+        <v>730869</v>
       </c>
       <c r="R83" t="n">
-        <v>7281130</v>
+        <v>7280766</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9451,12 +9436,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9484,7 +9469,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120470890</v>
+        <v>120473475</v>
       </c>
       <c r="B84" t="n">
         <v>82321</v>
@@ -9523,14 +9508,14 @@
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran , Pi lm</t>
+          <t>Garpmesliden-Römyran, Pi lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>730611</v>
+        <v>730920</v>
       </c>
       <c r="R84" t="n">
-        <v>7281039</v>
+        <v>7280729</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9557,12 +9542,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9590,10 +9575,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120470957</v>
+        <v>120473217</v>
       </c>
       <c r="B85" t="n">
-        <v>82321</v>
+        <v>79160</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9606,21 +9591,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9633,10 +9618,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>730533</v>
+        <v>730876</v>
       </c>
       <c r="R85" t="n">
-        <v>7281130</v>
+        <v>7280720</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9663,12 +9648,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9696,7 +9681,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120470872</v>
+        <v>120470853</v>
       </c>
       <c r="B86" t="n">
         <v>82321</v>
@@ -9739,10 +9724,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>730630</v>
+        <v>730639</v>
       </c>
       <c r="R86" t="n">
-        <v>7280999</v>
+        <v>7280973</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9802,10 +9787,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120473462</v>
+        <v>120470945</v>
       </c>
       <c r="B87" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9818,21 +9803,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9845,10 +9830,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>730869</v>
+        <v>730551</v>
       </c>
       <c r="R87" t="n">
-        <v>7280791</v>
+        <v>7281090</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9875,12 +9860,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9908,10 +9893,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120473444</v>
+        <v>120473450</v>
       </c>
       <c r="B88" t="n">
-        <v>82321</v>
+        <v>77883</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9920,25 +9905,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1312</v>
+        <v>498</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9951,10 +9936,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>730845</v>
+        <v>730869</v>
       </c>
       <c r="R88" t="n">
-        <v>7280809</v>
+        <v>7280791</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10014,10 +9999,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120470967</v>
+        <v>120473159</v>
       </c>
       <c r="B89" t="n">
-        <v>78542</v>
+        <v>96885</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10026,30 +10011,31 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10057,10 +10043,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>730499</v>
+        <v>730803</v>
       </c>
       <c r="R89" t="n">
-        <v>7281166</v>
+        <v>7280729</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10087,12 +10073,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10120,10 +10106,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120473572</v>
+        <v>120470622</v>
       </c>
       <c r="B90" t="n">
-        <v>77474</v>
+        <v>96885</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10132,30 +10118,31 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6487</v>
+        <v>221945</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10163,10 +10150,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>730891</v>
+        <v>730781</v>
       </c>
       <c r="R90" t="n">
-        <v>7280715</v>
+        <v>7280800</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10193,12 +10180,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10226,10 +10213,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120473697</v>
+        <v>120473547</v>
       </c>
       <c r="B91" t="n">
-        <v>78576</v>
+        <v>91858</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10238,25 +10225,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10269,10 +10256,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>730832</v>
+        <v>730894</v>
       </c>
       <c r="R91" t="n">
-        <v>7280746</v>
+        <v>7280702</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10332,10 +10319,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120473421</v>
+        <v>120473563</v>
       </c>
       <c r="B92" t="n">
-        <v>78542</v>
+        <v>56524</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10348,26 +10335,35 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -10375,10 +10371,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>730869</v>
+        <v>730915</v>
       </c>
       <c r="R92" t="n">
-        <v>7280766</v>
+        <v>7280682</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10413,13 +10409,17 @@
           <t>2024-08-15</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>3 järpar i sin hemvist i den fuktiga gamla barrnaturskogen med sumpskogskaraktär som är planerad för kalhuggning och markberedning.</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10438,7 +10438,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120473467</v>
+        <v>120473420</v>
       </c>
       <c r="B93" t="n">
         <v>82321</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>730894</v>
+        <v>730869</v>
       </c>
       <c r="R93" t="n">
-        <v>7280757</v>
+        <v>7280766</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -1447,10 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120473462</v>
+        <v>120470655</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1463,21 +1463,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730869</v>
+        <v>730744</v>
       </c>
       <c r="R9" t="n">
-        <v>7280791</v>
+        <v>7280840</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120473485</v>
+        <v>120470614</v>
       </c>
       <c r="B10" t="n">
-        <v>57336</v>
+        <v>56524</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,16 +1569,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1586,26 +1586,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1613,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730938</v>
+        <v>730776</v>
       </c>
       <c r="R10" t="n">
-        <v>7280716</v>
+        <v>7280790</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1643,12 +1627,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1675,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120473635</v>
+        <v>120470659</v>
       </c>
       <c r="B11" t="n">
-        <v>79131</v>
+        <v>78624</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,21 +1675,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1702,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>730880</v>
+        <v>730744</v>
       </c>
       <c r="R11" t="n">
-        <v>7280720</v>
+        <v>7280840</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1748,12 +1732,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120473545</v>
+        <v>120473462</v>
       </c>
       <c r="B12" t="n">
-        <v>56532</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1793,39 +1777,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1833,10 +1808,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730894</v>
+        <v>730869</v>
       </c>
       <c r="R12" t="n">
-        <v>7280702</v>
+        <v>7280791</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1871,17 +1846,13 @@
           <t>2024-08-15</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Env höna med sina nästan utvuxna kycklingar på födosök i häckningsområdet.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1900,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120470655</v>
+        <v>120473485</v>
       </c>
       <c r="B13" t="n">
-        <v>82321</v>
+        <v>57336</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1916,26 +1887,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1943,10 +1931,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730744</v>
+        <v>730938</v>
       </c>
       <c r="R13" t="n">
-        <v>7280840</v>
+        <v>7280716</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1973,12 +1961,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,7 +1975,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2006,10 +1993,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120470789</v>
+        <v>120473635</v>
       </c>
       <c r="B14" t="n">
-        <v>78576</v>
+        <v>79131</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2022,21 +2009,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2049,10 +2036,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730676</v>
+        <v>730880</v>
       </c>
       <c r="R14" t="n">
-        <v>7280903</v>
+        <v>7280720</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2079,12 +2066,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2112,10 +2099,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120470957</v>
+        <v>120473545</v>
       </c>
       <c r="B15" t="n">
-        <v>82321</v>
+        <v>56532</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2124,30 +2111,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2155,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730533</v>
+        <v>730894</v>
       </c>
       <c r="R15" t="n">
-        <v>7281130</v>
+        <v>7280702</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2185,12 +2181,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Env höna med sina nästan utvuxna kycklingar på födosök i häckningsområdet.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,7 +2200,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2218,10 +2218,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120470614</v>
+        <v>120470789</v>
       </c>
       <c r="B16" t="n">
-        <v>56524</v>
+        <v>78576</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2234,27 +2234,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2262,10 +2261,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730776</v>
+        <v>730676</v>
       </c>
       <c r="R16" t="n">
-        <v>7280790</v>
+        <v>7280903</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2306,6 +2305,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120470659</v>
+        <v>120470957</v>
       </c>
       <c r="B17" t="n">
-        <v>78624</v>
+        <v>82321</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2340,21 +2340,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730744</v>
+        <v>730533</v>
       </c>
       <c r="R17" t="n">
-        <v>7280840</v>
+        <v>7281130</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -3279,10 +3279,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120473808</v>
+        <v>120470997</v>
       </c>
       <c r="B26" t="n">
-        <v>78624</v>
+        <v>78576</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3295,21 +3295,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730795</v>
+        <v>730452</v>
       </c>
       <c r="R26" t="n">
-        <v>7280824</v>
+        <v>7281226</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3491,10 +3491,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120470997</v>
+        <v>120470475</v>
       </c>
       <c r="B28" t="n">
-        <v>78576</v>
+        <v>78624</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3507,21 +3507,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730452</v>
+        <v>730827</v>
       </c>
       <c r="R28" t="n">
-        <v>7281226</v>
+        <v>7280751</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3597,7 +3597,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120470475</v>
+        <v>120473808</v>
       </c>
       <c r="B29" t="n">
         <v>78624</v>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730827</v>
+        <v>730795</v>
       </c>
       <c r="R29" t="n">
-        <v>7280751</v>
+        <v>7280824</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3670,12 +3670,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4129,10 +4129,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120470935</v>
+        <v>120473571</v>
       </c>
       <c r="B34" t="n">
-        <v>82321</v>
+        <v>90506</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4145,21 +4145,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>3242</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730544</v>
+        <v>730915</v>
       </c>
       <c r="R34" t="n">
-        <v>7281102</v>
+        <v>7280682</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4202,12 +4202,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4235,10 +4235,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120470795</v>
+        <v>120473699</v>
       </c>
       <c r="B35" t="n">
-        <v>90545</v>
+        <v>89650</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4247,25 +4247,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4278,10 +4278,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730676</v>
+        <v>730844</v>
       </c>
       <c r="R35" t="n">
-        <v>7280903</v>
+        <v>7280770</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4308,12 +4308,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4341,10 +4341,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120473571</v>
+        <v>120473694</v>
       </c>
       <c r="B36" t="n">
-        <v>90506</v>
+        <v>57336</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4357,26 +4357,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3242</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4384,10 +4389,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730915</v>
+        <v>730832</v>
       </c>
       <c r="R36" t="n">
-        <v>7280682</v>
+        <v>7280746</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4428,7 +4433,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4447,10 +4451,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120473699</v>
+        <v>120470935</v>
       </c>
       <c r="B37" t="n">
-        <v>89650</v>
+        <v>82321</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4463,21 +4467,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1962</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4490,10 +4494,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730844</v>
+        <v>730544</v>
       </c>
       <c r="R37" t="n">
-        <v>7280770</v>
+        <v>7281102</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4520,12 +4524,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4553,10 +4557,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120473694</v>
+        <v>120470795</v>
       </c>
       <c r="B38" t="n">
-        <v>57336</v>
+        <v>90545</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4565,35 +4569,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4601,10 +4600,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730832</v>
+        <v>730676</v>
       </c>
       <c r="R38" t="n">
-        <v>7280746</v>
+        <v>7280903</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4631,12 +4630,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4645,6 +4644,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5206,10 +5206,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120470812</v>
+        <v>120473492</v>
       </c>
       <c r="B44" t="n">
-        <v>97951</v>
+        <v>78576</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5218,31 +5218,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5250,10 +5249,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>730676</v>
+        <v>730912</v>
       </c>
       <c r="R44" t="n">
-        <v>7280903</v>
+        <v>7280701</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5280,12 +5279,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5313,10 +5312,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120473148</v>
+        <v>120473407</v>
       </c>
       <c r="B45" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5329,21 +5328,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5356,10 +5355,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>730803</v>
+        <v>730907</v>
       </c>
       <c r="R45" t="n">
-        <v>7280729</v>
+        <v>7280757</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5419,10 +5418,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120473492</v>
+        <v>120473148</v>
       </c>
       <c r="B46" t="n">
-        <v>78576</v>
+        <v>82321</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5435,21 +5434,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5462,10 +5461,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>730912</v>
+        <v>730803</v>
       </c>
       <c r="R46" t="n">
-        <v>7280701</v>
+        <v>7280729</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5525,10 +5524,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120470617</v>
+        <v>120470812</v>
       </c>
       <c r="B47" t="n">
-        <v>96885</v>
+        <v>97951</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5541,21 +5540,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5569,10 +5568,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>730776</v>
+        <v>730676</v>
       </c>
       <c r="R47" t="n">
-        <v>7280790</v>
+        <v>7280903</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5632,10 +5631,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120470889</v>
+        <v>120470617</v>
       </c>
       <c r="B48" t="n">
-        <v>78542</v>
+        <v>96885</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5644,41 +5643,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran , Pi lm</t>
+          <t>Garpmesliden-Römyran, Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>730611</v>
+        <v>730776</v>
       </c>
       <c r="R48" t="n">
-        <v>7281039</v>
+        <v>7280790</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5738,7 +5738,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120473407</v>
+        <v>120470889</v>
       </c>
       <c r="B49" t="n">
         <v>78542</v>
@@ -5777,14 +5777,14 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran, Pi lm</t>
+          <t>Garpmesliden-Römyran , Pi lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>730907</v>
+        <v>730611</v>
       </c>
       <c r="R49" t="n">
-        <v>7280757</v>
+        <v>7281039</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5811,12 +5811,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5844,10 +5844,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120473410</v>
+        <v>120473226</v>
       </c>
       <c r="B50" t="n">
-        <v>78624</v>
+        <v>90545</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5856,25 +5856,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>864</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>730907</v>
+        <v>730876</v>
       </c>
       <c r="R50" t="n">
-        <v>7280757</v>
+        <v>7280720</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5950,10 +5950,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120473467</v>
+        <v>120470498</v>
       </c>
       <c r="B51" t="n">
-        <v>82321</v>
+        <v>57336</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5966,26 +5966,43 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5993,10 +6010,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>730894</v>
+        <v>730827</v>
       </c>
       <c r="R51" t="n">
-        <v>7280757</v>
+        <v>7280751</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6023,12 +6040,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6037,7 +6054,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6056,10 +6072,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120473226</v>
+        <v>120470955</v>
       </c>
       <c r="B52" t="n">
-        <v>90545</v>
+        <v>77489</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6068,25 +6084,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6099,10 +6115,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>730876</v>
+        <v>730533</v>
       </c>
       <c r="R52" t="n">
-        <v>7280720</v>
+        <v>7281130</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6129,12 +6145,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6162,10 +6178,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120470498</v>
+        <v>120473410</v>
       </c>
       <c r="B53" t="n">
-        <v>57336</v>
+        <v>78624</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6178,43 +6194,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>864</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6222,10 +6221,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>730827</v>
+        <v>730907</v>
       </c>
       <c r="R53" t="n">
-        <v>7280751</v>
+        <v>7280757</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6252,12 +6251,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6266,6 +6265,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6284,10 +6284,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120470955</v>
+        <v>120473467</v>
       </c>
       <c r="B54" t="n">
-        <v>77489</v>
+        <v>82321</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6300,21 +6300,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>314</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6327,10 +6327,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>730533</v>
+        <v>730894</v>
       </c>
       <c r="R54" t="n">
-        <v>7281130</v>
+        <v>7280757</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6357,12 +6357,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6708,10 +6708,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120470867</v>
+        <v>120473572</v>
       </c>
       <c r="B58" t="n">
-        <v>78542</v>
+        <v>77474</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6724,21 +6724,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6751,10 +6751,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730630</v>
+        <v>730891</v>
       </c>
       <c r="R58" t="n">
-        <v>7280999</v>
+        <v>7280715</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6814,10 +6814,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120473572</v>
+        <v>120473606</v>
       </c>
       <c r="B59" t="n">
-        <v>77474</v>
+        <v>79160</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6830,21 +6830,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6857,10 +6857,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>730891</v>
+        <v>730869</v>
       </c>
       <c r="R59" t="n">
-        <v>7280715</v>
+        <v>7280698</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6920,10 +6920,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120473606</v>
+        <v>120473837</v>
       </c>
       <c r="B60" t="n">
-        <v>79160</v>
+        <v>78624</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6936,21 +6936,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6963,10 +6963,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>730869</v>
+        <v>730743</v>
       </c>
       <c r="R60" t="n">
-        <v>7280698</v>
+        <v>7280839</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7026,10 +7026,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120473837</v>
+        <v>120473132</v>
       </c>
       <c r="B61" t="n">
-        <v>78624</v>
+        <v>96885</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7038,30 +7038,31 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>864</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7069,10 +7070,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>730743</v>
+        <v>730789</v>
       </c>
       <c r="R61" t="n">
-        <v>7280839</v>
+        <v>7280765</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7132,10 +7133,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120473132</v>
+        <v>120470867</v>
       </c>
       <c r="B62" t="n">
-        <v>96885</v>
+        <v>78542</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7144,31 +7145,30 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>730789</v>
+        <v>730630</v>
       </c>
       <c r="R62" t="n">
-        <v>7280765</v>
+        <v>7280999</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7206,12 +7206,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8196,10 +8196,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120470887</v>
+        <v>120473756</v>
       </c>
       <c r="B72" t="n">
-        <v>96885</v>
+        <v>78542</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8208,31 +8208,30 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8240,10 +8239,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>730622</v>
+        <v>730833</v>
       </c>
       <c r="R72" t="n">
-        <v>7281028</v>
+        <v>7280805</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8270,12 +8269,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8303,7 +8302,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120473756</v>
+        <v>120473713</v>
       </c>
       <c r="B73" t="n">
         <v>78542</v>
@@ -8346,10 +8345,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>730833</v>
+        <v>730844</v>
       </c>
       <c r="R73" t="n">
-        <v>7280805</v>
+        <v>7280770</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8409,10 +8408,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120473713</v>
+        <v>120470887</v>
       </c>
       <c r="B74" t="n">
-        <v>78542</v>
+        <v>96885</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8421,30 +8420,31 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8452,10 +8452,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>730844</v>
+        <v>730622</v>
       </c>
       <c r="R74" t="n">
-        <v>7280770</v>
+        <v>7281028</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8482,12 +8482,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8515,10 +8515,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120473140</v>
+        <v>120473592</v>
       </c>
       <c r="B75" t="n">
-        <v>78576</v>
+        <v>74651</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8527,25 +8527,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>311</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8558,10 +8558,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>730799</v>
+        <v>730891</v>
       </c>
       <c r="R75" t="n">
-        <v>7280750</v>
+        <v>7280715</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8621,10 +8621,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120473592</v>
+        <v>120473626</v>
       </c>
       <c r="B76" t="n">
-        <v>74651</v>
+        <v>79160</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8633,25 +8633,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>311</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8664,10 +8664,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>730891</v>
+        <v>730880</v>
       </c>
       <c r="R76" t="n">
-        <v>7280715</v>
+        <v>7280720</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8727,10 +8727,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120473626</v>
+        <v>120473140</v>
       </c>
       <c r="B77" t="n">
-        <v>79160</v>
+        <v>78576</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8743,21 +8743,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>730880</v>
+        <v>730799</v>
       </c>
       <c r="R77" t="n">
-        <v>7280720</v>
+        <v>7280750</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9575,10 +9575,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120473217</v>
+        <v>120473450</v>
       </c>
       <c r="B85" t="n">
-        <v>79160</v>
+        <v>77883</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9587,25 +9587,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>498</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9618,10 +9618,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>730876</v>
+        <v>730869</v>
       </c>
       <c r="R85" t="n">
-        <v>7280720</v>
+        <v>7280791</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9681,10 +9681,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120470853</v>
+        <v>120473217</v>
       </c>
       <c r="B86" t="n">
-        <v>82321</v>
+        <v>79160</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9697,21 +9697,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9724,10 +9724,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>730639</v>
+        <v>730876</v>
       </c>
       <c r="R86" t="n">
-        <v>7280973</v>
+        <v>7280720</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9754,12 +9754,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9787,10 +9787,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120470945</v>
+        <v>120470853</v>
       </c>
       <c r="B87" t="n">
-        <v>78576</v>
+        <v>82321</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9803,21 +9803,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9830,10 +9830,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>730551</v>
+        <v>730639</v>
       </c>
       <c r="R87" t="n">
-        <v>7281090</v>
+        <v>7280973</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9893,10 +9893,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120473450</v>
+        <v>120470945</v>
       </c>
       <c r="B88" t="n">
-        <v>77883</v>
+        <v>78576</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9905,25 +9905,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>498</v>
+        <v>185</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9936,10 +9936,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>730869</v>
+        <v>730551</v>
       </c>
       <c r="R88" t="n">
-        <v>7280791</v>
+        <v>7281090</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9966,12 +9966,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120470646</v>
+        <v>120473547</v>
       </c>
       <c r="B2" t="n">
-        <v>96885</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730765</v>
+        <v>730894</v>
       </c>
       <c r="R2" t="n">
-        <v>7280814</v>
+        <v>7280702</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120470546</v>
+        <v>120473132</v>
       </c>
       <c r="B3" t="n">
-        <v>78624</v>
+        <v>96885</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,30 +793,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730856</v>
+        <v>730789</v>
       </c>
       <c r="R3" t="n">
-        <v>7280769</v>
+        <v>7280765</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -855,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120470942</v>
+        <v>120473565</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730551</v>
+        <v>730915</v>
       </c>
       <c r="R4" t="n">
-        <v>7281090</v>
+        <v>7280682</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -961,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120470931</v>
+        <v>120473140</v>
       </c>
       <c r="B5" t="n">
-        <v>56532</v>
+        <v>78576</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,47 +1006,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730544</v>
+        <v>730799</v>
       </c>
       <c r="R5" t="n">
-        <v>7281102</v>
+        <v>7280750</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1084,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,6 +1081,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1116,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120473443</v>
+        <v>120473423</v>
       </c>
       <c r="B6" t="n">
-        <v>78624</v>
+        <v>78576</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730845</v>
+        <v>730869</v>
       </c>
       <c r="R6" t="n">
-        <v>7280809</v>
+        <v>7280766</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1222,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120473397</v>
+        <v>120473807</v>
       </c>
       <c r="B7" t="n">
-        <v>57431</v>
+        <v>57473</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,25 +1218,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1264,7 +1248,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>revir, ej häckning</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1274,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730897</v>
+        <v>730795</v>
       </c>
       <c r="R7" t="n">
-        <v>7280732</v>
+        <v>7280824</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1314,7 +1298,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>En familjgrupp i sitt revir. Det är gruppen som håller till kring Kikkejaureberget/Tjitterberget men mycket av deras revir och hemvist i naturskogsresterna har undan för undan avverkats trots miljölöften av statliga Sveaskog. Även aktuell fyndplats i naturskogsrestfragment är planerad för kalavverkning och markberedning!</t>
+          <t>Ett par med årets ungar i parets hemvist och häckningsrevir</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120473472</v>
+        <v>120470617</v>
       </c>
       <c r="B8" t="n">
-        <v>78624</v>
+        <v>96885</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,30 +1337,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1384,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730920</v>
+        <v>730776</v>
       </c>
       <c r="R8" t="n">
-        <v>7280729</v>
+        <v>7280790</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1414,12 +1399,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120470655</v>
+        <v>120470858</v>
       </c>
       <c r="B9" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1463,21 +1448,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730744</v>
+        <v>730638</v>
       </c>
       <c r="R9" t="n">
-        <v>7280840</v>
+        <v>7280995</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1553,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120470614</v>
+        <v>120473775</v>
       </c>
       <c r="B10" t="n">
-        <v>56524</v>
+        <v>78624</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,27 +1554,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1597,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730776</v>
+        <v>730816</v>
       </c>
       <c r="R10" t="n">
-        <v>7280790</v>
+        <v>7280822</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1627,12 +1611,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,6 +1625,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1659,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120470659</v>
+        <v>120470896</v>
       </c>
       <c r="B11" t="n">
-        <v>78624</v>
+        <v>78576</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1675,21 +1660,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1702,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>730744</v>
+        <v>730587</v>
       </c>
       <c r="R11" t="n">
-        <v>7280840</v>
+        <v>7281038</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1765,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120473462</v>
+        <v>120473475</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1808,10 +1793,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730869</v>
+        <v>730920</v>
       </c>
       <c r="R12" t="n">
-        <v>7280791</v>
+        <v>7280729</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1871,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120473485</v>
+        <v>120470733</v>
       </c>
       <c r="B13" t="n">
-        <v>57336</v>
+        <v>82321</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1887,43 +1872,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1931,10 +1899,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730938</v>
+        <v>730717</v>
       </c>
       <c r="R13" t="n">
-        <v>7280716</v>
+        <v>7280872</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1961,12 +1929,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1975,6 +1943,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1993,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120473635</v>
+        <v>120470964</v>
       </c>
       <c r="B14" t="n">
-        <v>79131</v>
+        <v>97951</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2005,30 +1974,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2036,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730880</v>
+        <v>730499</v>
       </c>
       <c r="R14" t="n">
-        <v>7280720</v>
+        <v>7281141</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2066,12 +2036,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2099,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120473545</v>
+        <v>120470872</v>
       </c>
       <c r="B15" t="n">
-        <v>56532</v>
+        <v>82321</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2111,39 +2081,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2151,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730894</v>
+        <v>730630</v>
       </c>
       <c r="R15" t="n">
-        <v>7280702</v>
+        <v>7280999</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2181,17 +2142,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Env höna med sina nästan utvuxna kycklingar på födosök i häckningsområdet.</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2200,6 +2156,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2218,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120470789</v>
+        <v>120470646</v>
       </c>
       <c r="B16" t="n">
-        <v>78576</v>
+        <v>96885</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2230,30 +2187,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2261,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730676</v>
+        <v>730765</v>
       </c>
       <c r="R16" t="n">
-        <v>7280903</v>
+        <v>7280814</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2324,10 +2282,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120470957</v>
+        <v>120470660</v>
       </c>
       <c r="B17" t="n">
-        <v>82321</v>
+        <v>96885</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2336,30 +2294,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2367,10 +2326,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730533</v>
+        <v>730744</v>
       </c>
       <c r="R17" t="n">
-        <v>7281130</v>
+        <v>7280840</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2430,10 +2389,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120470896</v>
+        <v>120470917</v>
       </c>
       <c r="B18" t="n">
-        <v>78576</v>
+        <v>96885</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2442,30 +2401,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2473,10 +2433,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730587</v>
+        <v>730563</v>
       </c>
       <c r="R18" t="n">
-        <v>7281038</v>
+        <v>7281056</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2536,10 +2496,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120470888</v>
+        <v>120473194</v>
       </c>
       <c r="B19" t="n">
-        <v>78576</v>
+        <v>79160</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2552,21 +2512,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2575,14 +2535,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran , Pi lm</t>
+          <t>Garpmesliden-Römyran, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>730611</v>
+        <v>730852</v>
       </c>
       <c r="R19" t="n">
-        <v>7281039</v>
+        <v>7280740</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2609,12 +2569,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2642,10 +2602,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120470478</v>
+        <v>120470931</v>
       </c>
       <c r="B20" t="n">
-        <v>82321</v>
+        <v>56532</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2654,30 +2614,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2685,10 +2662,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730827</v>
+        <v>730544</v>
       </c>
       <c r="R20" t="n">
-        <v>7280751</v>
+        <v>7281102</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2729,7 +2706,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2748,10 +2724,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120473697</v>
+        <v>120470614</v>
       </c>
       <c r="B21" t="n">
-        <v>78576</v>
+        <v>56524</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2764,26 +2740,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2791,10 +2768,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>730832</v>
+        <v>730776</v>
       </c>
       <c r="R21" t="n">
-        <v>7280746</v>
+        <v>7280790</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2821,12 +2798,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2835,7 +2812,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2854,10 +2830,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120473746</v>
+        <v>120473217</v>
       </c>
       <c r="B22" t="n">
-        <v>82321</v>
+        <v>79160</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2870,21 +2846,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2897,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730814</v>
+        <v>730876</v>
       </c>
       <c r="R22" t="n">
-        <v>7280788</v>
+        <v>7280720</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2960,10 +2936,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120473444</v>
+        <v>120473571</v>
       </c>
       <c r="B23" t="n">
-        <v>82321</v>
+        <v>90506</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2976,21 +2952,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>3242</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3003,10 +2979,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730845</v>
+        <v>730915</v>
       </c>
       <c r="R23" t="n">
-        <v>7280809</v>
+        <v>7280682</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3066,10 +3042,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120470660</v>
+        <v>120470889</v>
       </c>
       <c r="B24" t="n">
-        <v>96885</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3078,42 +3054,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran, Pi lm</t>
+          <t>Garpmesliden-Römyran , Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>730744</v>
+        <v>730611</v>
       </c>
       <c r="R24" t="n">
-        <v>7280840</v>
+        <v>7281039</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3173,10 +3148,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120470872</v>
+        <v>120473485</v>
       </c>
       <c r="B25" t="n">
-        <v>82321</v>
+        <v>57336</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3189,26 +3164,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3216,10 +3208,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>730630</v>
+        <v>730938</v>
       </c>
       <c r="R25" t="n">
-        <v>7280999</v>
+        <v>7280716</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3246,12 +3238,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3260,7 +3252,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3279,10 +3270,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120470997</v>
+        <v>120473563</v>
       </c>
       <c r="B26" t="n">
-        <v>78576</v>
+        <v>56524</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3295,26 +3286,35 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730452</v>
+        <v>730915</v>
       </c>
       <c r="R26" t="n">
-        <v>7281226</v>
+        <v>7280682</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3352,12 +3352,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>3 järpar i sin hemvist i den fuktiga gamla barrnaturskogen med sumpskogskaraktär som är planerad för kalhuggning och markberedning.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3366,7 +3371,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3385,10 +3389,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120473129</v>
+        <v>120473606</v>
       </c>
       <c r="B27" t="n">
-        <v>90594</v>
+        <v>79160</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3401,21 +3405,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3428,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730789</v>
+        <v>730869</v>
       </c>
       <c r="R27" t="n">
-        <v>7280765</v>
+        <v>7280698</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3491,10 +3495,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120470475</v>
+        <v>120473407</v>
       </c>
       <c r="B28" t="n">
-        <v>78624</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3507,21 +3511,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3534,10 +3538,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730827</v>
+        <v>730907</v>
       </c>
       <c r="R28" t="n">
-        <v>7280751</v>
+        <v>7280757</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3564,12 +3568,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3597,10 +3601,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120473808</v>
+        <v>120470942</v>
       </c>
       <c r="B29" t="n">
-        <v>78624</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3613,21 +3617,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3640,10 +3644,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730795</v>
+        <v>730551</v>
       </c>
       <c r="R29" t="n">
-        <v>7280824</v>
+        <v>7281090</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3670,12 +3674,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3810,10 +3814,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120470917</v>
+        <v>120470655</v>
       </c>
       <c r="B31" t="n">
-        <v>96885</v>
+        <v>82321</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3822,31 +3826,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3854,10 +3857,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730563</v>
+        <v>730744</v>
       </c>
       <c r="R31" t="n">
-        <v>7281056</v>
+        <v>7280840</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3917,10 +3920,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120470940</v>
+        <v>120473699</v>
       </c>
       <c r="B32" t="n">
-        <v>82321</v>
+        <v>89650</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3933,21 +3936,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>1962</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3960,10 +3963,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730551</v>
+        <v>730844</v>
       </c>
       <c r="R32" t="n">
-        <v>7281090</v>
+        <v>7280770</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3990,12 +3993,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4023,10 +4026,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120470739</v>
+        <v>120473467</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4039,21 +4042,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4066,10 +4069,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>730717</v>
+        <v>730894</v>
       </c>
       <c r="R33" t="n">
-        <v>7280872</v>
+        <v>7280757</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4096,12 +4099,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4129,10 +4132,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120473571</v>
+        <v>120473450</v>
       </c>
       <c r="B34" t="n">
-        <v>90506</v>
+        <v>77883</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4141,25 +4144,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3242</v>
+        <v>498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4172,10 +4175,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730915</v>
+        <v>730869</v>
       </c>
       <c r="R34" t="n">
-        <v>7280682</v>
+        <v>7280791</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4235,10 +4238,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120473699</v>
+        <v>120473572</v>
       </c>
       <c r="B35" t="n">
-        <v>89650</v>
+        <v>77474</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4251,21 +4254,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4278,10 +4281,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730844</v>
+        <v>730891</v>
       </c>
       <c r="R35" t="n">
-        <v>7280770</v>
+        <v>7280715</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4341,10 +4344,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120473694</v>
+        <v>120473226</v>
       </c>
       <c r="B36" t="n">
-        <v>57336</v>
+        <v>90545</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4353,35 +4356,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4389,10 +4387,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730832</v>
+        <v>730876</v>
       </c>
       <c r="R36" t="n">
-        <v>7280746</v>
+        <v>7280720</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4433,6 +4431,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4451,10 +4450,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120470935</v>
+        <v>120473626</v>
       </c>
       <c r="B37" t="n">
-        <v>82321</v>
+        <v>79160</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4467,21 +4466,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4494,10 +4493,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730544</v>
+        <v>730880</v>
       </c>
       <c r="R37" t="n">
-        <v>7281102</v>
+        <v>7280720</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4524,12 +4523,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4557,10 +4556,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120470795</v>
+        <v>120470739</v>
       </c>
       <c r="B38" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4569,25 +4568,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4600,10 +4599,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730676</v>
+        <v>730717</v>
       </c>
       <c r="R38" t="n">
-        <v>7280903</v>
+        <v>7280872</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4663,10 +4662,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120473156</v>
+        <v>120473713</v>
       </c>
       <c r="B39" t="n">
-        <v>78624</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4679,21 +4678,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4706,10 +4705,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730803</v>
+        <v>730844</v>
       </c>
       <c r="R39" t="n">
-        <v>7280729</v>
+        <v>7280770</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4769,10 +4768,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120470733</v>
+        <v>120470909</v>
       </c>
       <c r="B40" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4785,21 +4784,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4812,10 +4811,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>730717</v>
+        <v>730587</v>
       </c>
       <c r="R40" t="n">
-        <v>7280872</v>
+        <v>7281038</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4875,10 +4874,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120470890</v>
+        <v>120470867</v>
       </c>
       <c r="B41" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4891,21 +4890,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4914,14 +4913,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran , Pi lm</t>
+          <t>Garpmesliden-Römyran, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730611</v>
+        <v>730630</v>
       </c>
       <c r="R41" t="n">
-        <v>7281039</v>
+        <v>7280999</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4981,10 +4980,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120473565</v>
+        <v>120470940</v>
       </c>
       <c r="B42" t="n">
-        <v>78576</v>
+        <v>82321</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4997,21 +4996,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5024,10 +5023,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730915</v>
+        <v>730551</v>
       </c>
       <c r="R42" t="n">
-        <v>7280682</v>
+        <v>7281090</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5054,12 +5053,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5087,10 +5086,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120473807</v>
+        <v>120473462</v>
       </c>
       <c r="B43" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5103,35 +5102,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>revir, ej häckning</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5139,10 +5129,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>730795</v>
+        <v>730869</v>
       </c>
       <c r="R43" t="n">
-        <v>7280824</v>
+        <v>7280791</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5177,17 +5167,13 @@
           <t>2024-08-15</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ett par med årets ungar i parets hemvist och häckningsrevir</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5206,10 +5192,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120473492</v>
+        <v>120473143</v>
       </c>
       <c r="B44" t="n">
-        <v>78576</v>
+        <v>82321</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5222,21 +5208,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5249,10 +5235,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>730912</v>
+        <v>730799</v>
       </c>
       <c r="R44" t="n">
-        <v>7280701</v>
+        <v>7280750</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5312,10 +5298,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120473407</v>
+        <v>120470620</v>
       </c>
       <c r="B45" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5328,21 +5314,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5355,10 +5341,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>730907</v>
+        <v>730781</v>
       </c>
       <c r="R45" t="n">
-        <v>7280757</v>
+        <v>7280800</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5385,12 +5371,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5418,10 +5404,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120473148</v>
+        <v>120473635</v>
       </c>
       <c r="B46" t="n">
-        <v>82321</v>
+        <v>79131</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5434,21 +5420,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5461,10 +5447,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>730803</v>
+        <v>730880</v>
       </c>
       <c r="R46" t="n">
-        <v>7280729</v>
+        <v>7280720</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5524,10 +5510,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120470812</v>
+        <v>120473129</v>
       </c>
       <c r="B47" t="n">
-        <v>97951</v>
+        <v>90594</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5536,31 +5522,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>1204</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5568,10 +5553,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>730676</v>
+        <v>730789</v>
       </c>
       <c r="R47" t="n">
-        <v>7280903</v>
+        <v>7280765</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5598,12 +5583,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5631,10 +5616,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120470617</v>
+        <v>120470955</v>
       </c>
       <c r="B48" t="n">
-        <v>96885</v>
+        <v>77489</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5643,31 +5628,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5675,10 +5659,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>730776</v>
+        <v>730533</v>
       </c>
       <c r="R48" t="n">
-        <v>7280790</v>
+        <v>7281130</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5738,7 +5722,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120470889</v>
+        <v>120470967</v>
       </c>
       <c r="B49" t="n">
         <v>78542</v>
@@ -5777,14 +5761,14 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran , Pi lm</t>
+          <t>Garpmesliden-Römyran, Pi lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>730611</v>
+        <v>730499</v>
       </c>
       <c r="R49" t="n">
-        <v>7281039</v>
+        <v>7281166</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5844,10 +5828,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120473226</v>
+        <v>120473545</v>
       </c>
       <c r="B50" t="n">
-        <v>90545</v>
+        <v>56532</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5860,26 +5844,35 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5887,10 +5880,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>730876</v>
+        <v>730894</v>
       </c>
       <c r="R50" t="n">
-        <v>7280720</v>
+        <v>7280702</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5925,13 +5918,17 @@
           <t>2024-08-15</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Env höna med sina nästan utvuxna kycklingar på födosök i häckningsområdet.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5950,10 +5947,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120470498</v>
+        <v>120470935</v>
       </c>
       <c r="B51" t="n">
-        <v>57336</v>
+        <v>82321</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5966,43 +5963,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6010,10 +5990,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>730827</v>
+        <v>730544</v>
       </c>
       <c r="R51" t="n">
-        <v>7280751</v>
+        <v>7281102</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6054,6 +6034,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6072,10 +6053,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120470955</v>
+        <v>120473746</v>
       </c>
       <c r="B52" t="n">
-        <v>77489</v>
+        <v>82321</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6088,21 +6069,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>314</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6115,10 +6096,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>730533</v>
+        <v>730814</v>
       </c>
       <c r="R52" t="n">
-        <v>7281130</v>
+        <v>7280788</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6145,12 +6126,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6178,10 +6159,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120473410</v>
+        <v>120470890</v>
       </c>
       <c r="B53" t="n">
-        <v>78624</v>
+        <v>82321</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6194,21 +6175,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6217,14 +6198,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran, Pi lm</t>
+          <t>Garpmesliden-Römyran , Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>730907</v>
+        <v>730611</v>
       </c>
       <c r="R53" t="n">
-        <v>7280757</v>
+        <v>7281039</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6251,12 +6232,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6284,10 +6265,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120473467</v>
+        <v>120470659</v>
       </c>
       <c r="B54" t="n">
-        <v>82321</v>
+        <v>78624</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6300,21 +6281,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6327,10 +6308,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>730894</v>
+        <v>730744</v>
       </c>
       <c r="R54" t="n">
-        <v>7280757</v>
+        <v>7280840</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6357,12 +6338,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6390,10 +6371,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120470620</v>
+        <v>120470475</v>
       </c>
       <c r="B55" t="n">
-        <v>82321</v>
+        <v>78624</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6406,21 +6387,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6433,10 +6414,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>730781</v>
+        <v>730827</v>
       </c>
       <c r="R55" t="n">
-        <v>7280800</v>
+        <v>7280751</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6496,10 +6477,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120473750</v>
+        <v>120470915</v>
       </c>
       <c r="B56" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6512,21 +6493,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6539,10 +6520,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>730814</v>
+        <v>730563</v>
       </c>
       <c r="R56" t="n">
-        <v>7280788</v>
+        <v>7281056</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6569,12 +6550,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6602,10 +6583,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120473143</v>
+        <v>120470622</v>
       </c>
       <c r="B57" t="n">
-        <v>82321</v>
+        <v>96885</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6614,30 +6595,31 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6645,10 +6627,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>730799</v>
+        <v>730781</v>
       </c>
       <c r="R57" t="n">
-        <v>7280750</v>
+        <v>7280800</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6675,12 +6657,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6708,10 +6690,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120473572</v>
+        <v>120473421</v>
       </c>
       <c r="B58" t="n">
-        <v>77474</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6724,21 +6706,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6751,10 +6733,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730891</v>
+        <v>730869</v>
       </c>
       <c r="R58" t="n">
-        <v>7280715</v>
+        <v>7280766</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6814,10 +6796,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120473606</v>
+        <v>120473159</v>
       </c>
       <c r="B59" t="n">
-        <v>79160</v>
+        <v>96885</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6826,30 +6808,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6857,10 +6840,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>730869</v>
+        <v>730803</v>
       </c>
       <c r="R59" t="n">
-        <v>7280698</v>
+        <v>7280729</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6920,10 +6903,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120473837</v>
+        <v>120473492</v>
       </c>
       <c r="B60" t="n">
-        <v>78624</v>
+        <v>78576</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6936,21 +6919,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6963,10 +6946,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>730743</v>
+        <v>730912</v>
       </c>
       <c r="R60" t="n">
-        <v>7280839</v>
+        <v>7280701</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7026,10 +7009,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120473132</v>
+        <v>120473697</v>
       </c>
       <c r="B61" t="n">
-        <v>96885</v>
+        <v>78576</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7038,31 +7021,30 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7070,10 +7052,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>730789</v>
+        <v>730832</v>
       </c>
       <c r="R61" t="n">
-        <v>7280765</v>
+        <v>7280746</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7133,10 +7115,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120470867</v>
+        <v>120473443</v>
       </c>
       <c r="B62" t="n">
-        <v>78542</v>
+        <v>78624</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7149,21 +7131,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7176,10 +7158,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>730630</v>
+        <v>730845</v>
       </c>
       <c r="R62" t="n">
-        <v>7280999</v>
+        <v>7280809</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7206,12 +7188,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7239,10 +7221,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120473194</v>
+        <v>120473837</v>
       </c>
       <c r="B63" t="n">
-        <v>79160</v>
+        <v>78624</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7255,21 +7237,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7282,10 +7264,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>730852</v>
+        <v>730743</v>
       </c>
       <c r="R63" t="n">
-        <v>7280740</v>
+        <v>7280839</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7345,10 +7327,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120473201</v>
+        <v>120473472</v>
       </c>
       <c r="B64" t="n">
-        <v>96891</v>
+        <v>78624</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7357,31 +7339,30 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221941</v>
+        <v>864</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7389,10 +7370,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>730852</v>
+        <v>730920</v>
       </c>
       <c r="R64" t="n">
-        <v>7280740</v>
+        <v>7280729</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7452,7 +7433,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120473413</v>
+        <v>120473420</v>
       </c>
       <c r="B65" t="n">
         <v>82321</v>
@@ -7495,10 +7476,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>730907</v>
+        <v>730869</v>
       </c>
       <c r="R65" t="n">
-        <v>7280757</v>
+        <v>7280766</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7558,7 +7539,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120470858</v>
+        <v>120473756</v>
       </c>
       <c r="B66" t="n">
         <v>78542</v>
@@ -7601,10 +7582,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>730638</v>
+        <v>730833</v>
       </c>
       <c r="R66" t="n">
-        <v>7280995</v>
+        <v>7280805</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7631,12 +7612,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7664,10 +7645,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120470967</v>
+        <v>120470478</v>
       </c>
       <c r="B67" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7680,21 +7661,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7707,10 +7688,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>730499</v>
+        <v>730827</v>
       </c>
       <c r="R67" t="n">
-        <v>7281166</v>
+        <v>7280751</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7770,10 +7751,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120470964</v>
+        <v>120470853</v>
       </c>
       <c r="B68" t="n">
-        <v>97951</v>
+        <v>82321</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7782,31 +7763,30 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7814,10 +7794,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>730499</v>
+        <v>730639</v>
       </c>
       <c r="R68" t="n">
-        <v>7281141</v>
+        <v>7280973</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7877,10 +7857,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120470914</v>
+        <v>120473754</v>
       </c>
       <c r="B69" t="n">
-        <v>90594</v>
+        <v>78624</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7893,21 +7873,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7920,10 +7900,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>730563</v>
+        <v>730833</v>
       </c>
       <c r="R69" t="n">
-        <v>7281056</v>
+        <v>7280805</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7950,12 +7930,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7983,7 +7963,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120473423</v>
+        <v>120470789</v>
       </c>
       <c r="B70" t="n">
         <v>78576</v>
@@ -8026,10 +8006,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>730869</v>
+        <v>730676</v>
       </c>
       <c r="R70" t="n">
-        <v>7280766</v>
+        <v>7280903</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8056,12 +8036,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8089,10 +8069,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120473835</v>
+        <v>120473156</v>
       </c>
       <c r="B71" t="n">
-        <v>97951</v>
+        <v>78624</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8101,31 +8081,30 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>864</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -8133,10 +8112,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>730783</v>
+        <v>730803</v>
       </c>
       <c r="R71" t="n">
-        <v>7280820</v>
+        <v>7280729</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8196,10 +8175,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120473756</v>
+        <v>120473808</v>
       </c>
       <c r="B72" t="n">
-        <v>78542</v>
+        <v>78624</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8212,21 +8191,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8239,10 +8218,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>730833</v>
+        <v>730795</v>
       </c>
       <c r="R72" t="n">
-        <v>7280805</v>
+        <v>7280824</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8302,10 +8281,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120473713</v>
+        <v>120470795</v>
       </c>
       <c r="B73" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8314,25 +8293,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8345,10 +8324,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>730844</v>
+        <v>730676</v>
       </c>
       <c r="R73" t="n">
-        <v>7280770</v>
+        <v>7280903</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8375,12 +8354,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8408,10 +8387,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120470887</v>
+        <v>120470498</v>
       </c>
       <c r="B74" t="n">
-        <v>96885</v>
+        <v>57336</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8420,31 +8399,47 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8452,10 +8447,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>730622</v>
+        <v>730827</v>
       </c>
       <c r="R74" t="n">
-        <v>7281028</v>
+        <v>7280751</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8496,7 +8491,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8515,10 +8509,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120473592</v>
+        <v>120473148</v>
       </c>
       <c r="B75" t="n">
-        <v>74651</v>
+        <v>82321</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8527,25 +8521,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>311</v>
+        <v>1312</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8558,10 +8552,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>730891</v>
+        <v>730803</v>
       </c>
       <c r="R75" t="n">
-        <v>7280715</v>
+        <v>7280729</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8621,10 +8615,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120473626</v>
+        <v>120470914</v>
       </c>
       <c r="B76" t="n">
-        <v>79160</v>
+        <v>90594</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8637,21 +8631,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>1204</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8664,10 +8658,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>730880</v>
+        <v>730563</v>
       </c>
       <c r="R76" t="n">
-        <v>7280720</v>
+        <v>7281056</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8694,12 +8688,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8727,10 +8721,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120473140</v>
+        <v>120473750</v>
       </c>
       <c r="B77" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8743,21 +8737,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8770,10 +8764,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>730799</v>
+        <v>730814</v>
       </c>
       <c r="R77" t="n">
-        <v>7280750</v>
+        <v>7280788</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8833,10 +8827,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120470748</v>
+        <v>120473413</v>
       </c>
       <c r="B78" t="n">
-        <v>78576</v>
+        <v>82321</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8849,21 +8843,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8876,10 +8870,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>730697</v>
+        <v>730907</v>
       </c>
       <c r="R78" t="n">
-        <v>7280886</v>
+        <v>7280757</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8906,12 +8900,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8939,10 +8933,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120470909</v>
+        <v>120473397</v>
       </c>
       <c r="B79" t="n">
-        <v>78542</v>
+        <v>57431</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8951,30 +8945,39 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -8982,10 +8985,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>730587</v>
+        <v>730897</v>
       </c>
       <c r="R79" t="n">
-        <v>7281038</v>
+        <v>7280732</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9012,12 +9015,17 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>En familjgrupp i sitt revir. Det är gruppen som håller till kring Kikkejaureberget/Tjitterberget men mycket av deras revir och hemvist i naturskogsresterna har undan för undan avverkats trots miljölöften av statliga Sveaskog. Även aktuell fyndplats i naturskogsrestfragment är planerad för kalavverkning och markberedning!</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9026,7 +9034,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9045,7 +9052,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120470915</v>
+        <v>120470997</v>
       </c>
       <c r="B80" t="n">
         <v>78576</v>
@@ -9088,10 +9095,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>730563</v>
+        <v>730452</v>
       </c>
       <c r="R80" t="n">
-        <v>7281056</v>
+        <v>7281226</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9151,10 +9158,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120473754</v>
+        <v>120473592</v>
       </c>
       <c r="B81" t="n">
-        <v>78624</v>
+        <v>74651</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9163,25 +9170,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>864</v>
+        <v>311</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9194,10 +9201,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>730833</v>
+        <v>730891</v>
       </c>
       <c r="R81" t="n">
-        <v>7280805</v>
+        <v>7280715</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9257,7 +9264,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120473775</v>
+        <v>120470546</v>
       </c>
       <c r="B82" t="n">
         <v>78624</v>
@@ -9300,10 +9307,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>730816</v>
+        <v>730856</v>
       </c>
       <c r="R82" t="n">
-        <v>7280822</v>
+        <v>7280769</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9330,12 +9337,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9363,10 +9370,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120473421</v>
+        <v>120473694</v>
       </c>
       <c r="B83" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9379,26 +9386,31 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9406,10 +9418,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>730869</v>
+        <v>730832</v>
       </c>
       <c r="R83" t="n">
-        <v>7280766</v>
+        <v>7280746</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9450,7 +9462,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9469,7 +9480,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120473475</v>
+        <v>120473444</v>
       </c>
       <c r="B84" t="n">
         <v>82321</v>
@@ -9512,10 +9523,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>730920</v>
+        <v>730845</v>
       </c>
       <c r="R84" t="n">
-        <v>7280729</v>
+        <v>7280809</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9575,10 +9586,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120473450</v>
+        <v>120470887</v>
       </c>
       <c r="B85" t="n">
-        <v>77883</v>
+        <v>96885</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9587,30 +9598,31 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>498</v>
+        <v>221945</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -9618,10 +9630,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>730869</v>
+        <v>730622</v>
       </c>
       <c r="R85" t="n">
-        <v>7280791</v>
+        <v>7281028</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9648,12 +9660,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9681,10 +9693,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120473217</v>
+        <v>120470748</v>
       </c>
       <c r="B86" t="n">
-        <v>79160</v>
+        <v>78576</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9697,21 +9709,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9724,10 +9736,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>730876</v>
+        <v>730697</v>
       </c>
       <c r="R86" t="n">
-        <v>7280720</v>
+        <v>7280886</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9754,12 +9766,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9787,10 +9799,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120470853</v>
+        <v>120470888</v>
       </c>
       <c r="B87" t="n">
-        <v>82321</v>
+        <v>78576</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9803,21 +9815,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9826,14 +9838,14 @@
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran, Pi lm</t>
+          <t>Garpmesliden-Römyran , Pi lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>730639</v>
+        <v>730611</v>
       </c>
       <c r="R87" t="n">
-        <v>7280973</v>
+        <v>7281039</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9893,10 +9905,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120470945</v>
+        <v>120473410</v>
       </c>
       <c r="B88" t="n">
-        <v>78576</v>
+        <v>78624</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9909,21 +9921,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9936,10 +9948,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>730551</v>
+        <v>730907</v>
       </c>
       <c r="R88" t="n">
-        <v>7281090</v>
+        <v>7280757</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9966,12 +9978,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9999,10 +10011,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120473159</v>
+        <v>120470945</v>
       </c>
       <c r="B89" t="n">
-        <v>96885</v>
+        <v>78576</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10011,31 +10023,30 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221945</v>
+        <v>185</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10043,10 +10054,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>730803</v>
+        <v>730551</v>
       </c>
       <c r="R89" t="n">
-        <v>7280729</v>
+        <v>7281090</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10073,12 +10084,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10106,10 +10117,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120470622</v>
+        <v>120470957</v>
       </c>
       <c r="B90" t="n">
-        <v>96885</v>
+        <v>82321</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10118,31 +10129,30 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10150,10 +10160,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>730781</v>
+        <v>730533</v>
       </c>
       <c r="R90" t="n">
-        <v>7280800</v>
+        <v>7281130</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10213,10 +10223,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120473547</v>
+        <v>120470812</v>
       </c>
       <c r="B91" t="n">
-        <v>91858</v>
+        <v>97951</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10229,26 +10239,27 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>221952</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10256,10 +10267,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>730894</v>
+        <v>730676</v>
       </c>
       <c r="R91" t="n">
-        <v>7280702</v>
+        <v>7280903</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10286,12 +10297,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10319,10 +10330,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120473563</v>
+        <v>120473835</v>
       </c>
       <c r="B92" t="n">
-        <v>56524</v>
+        <v>97951</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10331,39 +10342,31 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>102612</v>
+        <v>221952</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -10371,10 +10374,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>730915</v>
+        <v>730783</v>
       </c>
       <c r="R92" t="n">
-        <v>7280682</v>
+        <v>7280820</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10409,17 +10412,13 @@
           <t>2024-08-15</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>3 järpar i sin hemvist i den fuktiga gamla barrnaturskogen med sumpskogskaraktär som är planerad för kalhuggning och markberedning.</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10438,10 +10437,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120473420</v>
+        <v>120473201</v>
       </c>
       <c r="B93" t="n">
-        <v>82321</v>
+        <v>96891</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10450,30 +10449,31 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1312</v>
+        <v>221941</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>730869</v>
+        <v>730852</v>
       </c>
       <c r="R93" t="n">
-        <v>7280766</v>
+        <v>7280740</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120473547</v>
+        <v>120470655</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>82321</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730894</v>
+        <v>730744</v>
       </c>
       <c r="R2" t="n">
-        <v>7280702</v>
+        <v>7280840</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,12 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120473132</v>
+        <v>120473420</v>
       </c>
       <c r="B3" t="n">
-        <v>96885</v>
+        <v>82321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,31 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730789</v>
+        <v>730869</v>
       </c>
       <c r="R3" t="n">
-        <v>7280765</v>
+        <v>7280766</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -888,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120473565</v>
+        <v>120473410</v>
       </c>
       <c r="B4" t="n">
-        <v>78576</v>
+        <v>78624</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730915</v>
+        <v>730907</v>
       </c>
       <c r="R4" t="n">
-        <v>7280682</v>
+        <v>7280757</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -994,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120473140</v>
+        <v>120473421</v>
       </c>
       <c r="B5" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730799</v>
+        <v>730869</v>
       </c>
       <c r="R5" t="n">
-        <v>7280750</v>
+        <v>7280766</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1100,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120473423</v>
+        <v>120473756</v>
       </c>
       <c r="B6" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730869</v>
+        <v>730833</v>
       </c>
       <c r="R6" t="n">
-        <v>7280766</v>
+        <v>7280805</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1206,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120473807</v>
+        <v>120473835</v>
       </c>
       <c r="B7" t="n">
-        <v>57473</v>
+        <v>97951</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,39 +1217,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>revir, ej häckning</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1258,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730795</v>
+        <v>730783</v>
       </c>
       <c r="R7" t="n">
-        <v>7280824</v>
+        <v>7280820</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1296,17 +1287,13 @@
           <t>2024-08-15</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ett par med årets ungar i parets hemvist och häckningsrevir</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1325,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120470617</v>
+        <v>120473423</v>
       </c>
       <c r="B8" t="n">
-        <v>96885</v>
+        <v>78576</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,31 +1324,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1369,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730776</v>
+        <v>730869</v>
       </c>
       <c r="R8" t="n">
-        <v>7280790</v>
+        <v>7280766</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1399,12 +1385,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120470858</v>
+        <v>120473413</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1448,21 +1434,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730638</v>
+        <v>730907</v>
       </c>
       <c r="R9" t="n">
-        <v>7280995</v>
+        <v>7280757</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1505,12 +1491,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120473775</v>
+        <v>120473492</v>
       </c>
       <c r="B10" t="n">
-        <v>78624</v>
+        <v>78576</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1554,21 +1540,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730816</v>
+        <v>730912</v>
       </c>
       <c r="R10" t="n">
-        <v>7280822</v>
+        <v>7280701</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1644,7 +1630,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120470896</v>
+        <v>120470888</v>
       </c>
       <c r="B11" t="n">
         <v>78576</v>
@@ -1683,14 +1669,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran, Pi lm</t>
+          <t>Garpmesliden-Römyran , Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>730587</v>
+        <v>730611</v>
       </c>
       <c r="R11" t="n">
-        <v>7281038</v>
+        <v>7281039</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1750,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120473475</v>
+        <v>120473485</v>
       </c>
       <c r="B12" t="n">
-        <v>82321</v>
+        <v>57336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,26 +1752,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1793,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730920</v>
+        <v>730938</v>
       </c>
       <c r="R12" t="n">
-        <v>7280729</v>
+        <v>7280716</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1837,7 +1840,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1856,10 +1858,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120470733</v>
+        <v>120470546</v>
       </c>
       <c r="B13" t="n">
-        <v>82321</v>
+        <v>78624</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,21 +1874,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1899,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730717</v>
+        <v>730856</v>
       </c>
       <c r="R13" t="n">
-        <v>7280872</v>
+        <v>7280769</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1962,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120470964</v>
+        <v>120470739</v>
       </c>
       <c r="B14" t="n">
-        <v>97951</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1974,31 +1976,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2006,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730499</v>
+        <v>730717</v>
       </c>
       <c r="R14" t="n">
-        <v>7281141</v>
+        <v>7280872</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2069,10 +2070,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120470872</v>
+        <v>120473563</v>
       </c>
       <c r="B15" t="n">
-        <v>82321</v>
+        <v>56524</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,26 +2086,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2112,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730630</v>
+        <v>730915</v>
       </c>
       <c r="R15" t="n">
-        <v>7280999</v>
+        <v>7280682</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2142,12 +2152,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>3 järpar i sin hemvist i den fuktiga gamla barrnaturskogen med sumpskogskaraktär som är planerad för kalhuggning och markberedning.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,7 +2171,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2175,10 +2189,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120470646</v>
+        <v>120470620</v>
       </c>
       <c r="B16" t="n">
-        <v>96885</v>
+        <v>82321</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2187,31 +2201,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2219,10 +2232,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730765</v>
+        <v>730781</v>
       </c>
       <c r="R16" t="n">
-        <v>7280814</v>
+        <v>7280800</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2282,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120470660</v>
+        <v>120473217</v>
       </c>
       <c r="B17" t="n">
-        <v>96885</v>
+        <v>79160</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2294,31 +2307,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2326,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730744</v>
+        <v>730876</v>
       </c>
       <c r="R17" t="n">
-        <v>7280840</v>
+        <v>7280720</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2356,12 +2368,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2389,10 +2401,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120470917</v>
+        <v>120473545</v>
       </c>
       <c r="B18" t="n">
-        <v>96885</v>
+        <v>56532</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2405,27 +2417,35 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2433,10 +2453,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730563</v>
+        <v>730894</v>
       </c>
       <c r="R18" t="n">
-        <v>7281056</v>
+        <v>7280702</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2463,12 +2483,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Env höna med sina nästan utvuxna kycklingar på födosök i häckningsområdet.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2477,7 +2502,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2496,10 +2520,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120473194</v>
+        <v>120473462</v>
       </c>
       <c r="B19" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2512,21 +2536,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2563,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>730852</v>
+        <v>730869</v>
       </c>
       <c r="R19" t="n">
-        <v>7280740</v>
+        <v>7280791</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2602,10 +2626,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120470931</v>
+        <v>120470795</v>
       </c>
       <c r="B20" t="n">
-        <v>56532</v>
+        <v>90545</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2618,43 +2642,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2662,10 +2669,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730544</v>
+        <v>730676</v>
       </c>
       <c r="R20" t="n">
-        <v>7281102</v>
+        <v>7280903</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2706,6 +2713,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2724,10 +2732,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120470614</v>
+        <v>120470997</v>
       </c>
       <c r="B21" t="n">
-        <v>56524</v>
+        <v>78576</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2740,27 +2748,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2768,10 +2775,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>730776</v>
+        <v>730452</v>
       </c>
       <c r="R21" t="n">
-        <v>7280790</v>
+        <v>7281226</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2812,6 +2819,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2830,10 +2838,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120473217</v>
+        <v>120470789</v>
       </c>
       <c r="B22" t="n">
-        <v>79160</v>
+        <v>78576</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2846,21 +2854,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2873,10 +2881,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730876</v>
+        <v>730676</v>
       </c>
       <c r="R22" t="n">
-        <v>7280720</v>
+        <v>7280903</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2903,12 +2911,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2936,10 +2944,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120473571</v>
+        <v>120473699</v>
       </c>
       <c r="B23" t="n">
-        <v>90506</v>
+        <v>89650</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2952,21 +2960,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3242</v>
+        <v>1962</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2979,10 +2987,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730915</v>
+        <v>730844</v>
       </c>
       <c r="R23" t="n">
-        <v>7280682</v>
+        <v>7280770</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3042,10 +3050,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120470889</v>
+        <v>120470957</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3058,21 +3066,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3081,14 +3089,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran , Pi lm</t>
+          <t>Garpmesliden-Römyran, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>730611</v>
+        <v>730533</v>
       </c>
       <c r="R24" t="n">
-        <v>7281039</v>
+        <v>7281130</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3148,10 +3156,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120473485</v>
+        <v>120470914</v>
       </c>
       <c r="B25" t="n">
-        <v>57336</v>
+        <v>90594</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3164,43 +3172,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3208,10 +3199,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>730938</v>
+        <v>730563</v>
       </c>
       <c r="R25" t="n">
-        <v>7280716</v>
+        <v>7281056</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3238,12 +3229,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3252,6 +3243,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3270,10 +3262,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120473563</v>
+        <v>120470498</v>
       </c>
       <c r="B26" t="n">
-        <v>56524</v>
+        <v>57336</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3286,16 +3278,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3305,14 +3297,22 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730915</v>
+        <v>730827</v>
       </c>
       <c r="R26" t="n">
-        <v>7280682</v>
+        <v>7280751</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3352,17 +3352,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>3 järpar i sin hemvist i den fuktiga gamla barrnaturskogen med sumpskogskaraktär som är planerad för kalhuggning och markberedning.</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3389,10 +3384,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120473606</v>
+        <v>120470917</v>
       </c>
       <c r="B27" t="n">
-        <v>79160</v>
+        <v>96885</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3401,30 +3396,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3432,10 +3428,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730869</v>
+        <v>730563</v>
       </c>
       <c r="R27" t="n">
-        <v>7280698</v>
+        <v>7281056</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3462,12 +3458,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3495,10 +3491,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120473407</v>
+        <v>120473226</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3507,25 +3503,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3538,10 +3534,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730907</v>
+        <v>730876</v>
       </c>
       <c r="R28" t="n">
-        <v>7280757</v>
+        <v>7280720</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3601,10 +3597,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120470942</v>
+        <v>120473807</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3617,26 +3613,35 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>revir, ej häckning</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3644,10 +3649,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730551</v>
+        <v>730795</v>
       </c>
       <c r="R29" t="n">
-        <v>7281090</v>
+        <v>7280824</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3674,12 +3679,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ett par med årets ungar i parets hemvist och häckningsrevir</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3688,7 +3698,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3707,10 +3716,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120470809</v>
+        <v>120470890</v>
       </c>
       <c r="B30" t="n">
-        <v>96885</v>
+        <v>82321</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3719,42 +3728,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran, Pi lm</t>
+          <t>Garpmesliden-Römyran , Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730676</v>
+        <v>730611</v>
       </c>
       <c r="R30" t="n">
-        <v>7280903</v>
+        <v>7281039</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3814,7 +3822,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120470655</v>
+        <v>120473467</v>
       </c>
       <c r="B31" t="n">
         <v>82321</v>
@@ -3857,10 +3865,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730744</v>
+        <v>730894</v>
       </c>
       <c r="R31" t="n">
-        <v>7280840</v>
+        <v>7280757</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3887,12 +3895,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3920,10 +3928,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120473699</v>
+        <v>120473132</v>
       </c>
       <c r="B32" t="n">
-        <v>89650</v>
+        <v>96885</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3932,30 +3940,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1962</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3963,10 +3972,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730844</v>
+        <v>730789</v>
       </c>
       <c r="R32" t="n">
-        <v>7280770</v>
+        <v>7280765</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4026,10 +4035,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120473467</v>
+        <v>120473201</v>
       </c>
       <c r="B33" t="n">
-        <v>82321</v>
+        <v>96891</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4038,30 +4047,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>221941</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4069,10 +4079,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>730894</v>
+        <v>730852</v>
       </c>
       <c r="R33" t="n">
-        <v>7280757</v>
+        <v>7280740</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4132,10 +4142,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120473450</v>
+        <v>120470478</v>
       </c>
       <c r="B34" t="n">
-        <v>77883</v>
+        <v>82321</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4144,25 +4154,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>498</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4175,10 +4185,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730869</v>
+        <v>730827</v>
       </c>
       <c r="R34" t="n">
-        <v>7280791</v>
+        <v>7280751</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4205,12 +4215,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4238,10 +4248,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120473572</v>
+        <v>120470733</v>
       </c>
       <c r="B35" t="n">
-        <v>77474</v>
+        <v>82321</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4254,21 +4264,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6487</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4281,10 +4291,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730891</v>
+        <v>730717</v>
       </c>
       <c r="R35" t="n">
-        <v>7280715</v>
+        <v>7280872</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4311,12 +4321,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4344,10 +4354,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120473226</v>
+        <v>120473697</v>
       </c>
       <c r="B36" t="n">
-        <v>90545</v>
+        <v>78576</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4356,25 +4366,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4387,10 +4397,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730876</v>
+        <v>730832</v>
       </c>
       <c r="R36" t="n">
-        <v>7280720</v>
+        <v>7280746</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4450,10 +4460,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120473626</v>
+        <v>120473592</v>
       </c>
       <c r="B37" t="n">
-        <v>79160</v>
+        <v>74651</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4462,25 +4472,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>311</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4493,10 +4503,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730880</v>
+        <v>730891</v>
       </c>
       <c r="R37" t="n">
-        <v>7280720</v>
+        <v>7280715</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4556,10 +4566,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120470739</v>
+        <v>120473754</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>78624</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4572,21 +4582,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4599,10 +4609,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730717</v>
+        <v>730833</v>
       </c>
       <c r="R38" t="n">
-        <v>7280872</v>
+        <v>7280805</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4629,12 +4639,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4662,10 +4672,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120473713</v>
+        <v>120473547</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4674,25 +4684,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4705,10 +4715,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730844</v>
+        <v>730894</v>
       </c>
       <c r="R39" t="n">
-        <v>7280770</v>
+        <v>7280702</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4768,10 +4778,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120470909</v>
+        <v>120473140</v>
       </c>
       <c r="B40" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4784,21 +4794,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4811,10 +4821,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>730587</v>
+        <v>730799</v>
       </c>
       <c r="R40" t="n">
-        <v>7281038</v>
+        <v>7280750</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4841,12 +4851,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4874,10 +4884,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120470867</v>
+        <v>120473444</v>
       </c>
       <c r="B41" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4890,21 +4900,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4917,10 +4927,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730630</v>
+        <v>730845</v>
       </c>
       <c r="R41" t="n">
-        <v>7280999</v>
+        <v>7280809</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4947,12 +4957,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4980,10 +4990,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120470940</v>
+        <v>120473194</v>
       </c>
       <c r="B42" t="n">
-        <v>82321</v>
+        <v>79160</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4996,21 +5006,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5023,10 +5033,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730551</v>
+        <v>730852</v>
       </c>
       <c r="R42" t="n">
-        <v>7281090</v>
+        <v>7280740</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5053,12 +5063,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5086,10 +5096,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120473462</v>
+        <v>120470945</v>
       </c>
       <c r="B43" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5102,21 +5112,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5129,10 +5139,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>730869</v>
+        <v>730551</v>
       </c>
       <c r="R43" t="n">
-        <v>7280791</v>
+        <v>7281090</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5159,12 +5169,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5192,7 +5202,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120473143</v>
+        <v>120470872</v>
       </c>
       <c r="B44" t="n">
         <v>82321</v>
@@ -5235,10 +5245,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>730799</v>
+        <v>730630</v>
       </c>
       <c r="R44" t="n">
-        <v>7280750</v>
+        <v>7280999</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5265,12 +5275,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5298,10 +5308,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120470620</v>
+        <v>120473626</v>
       </c>
       <c r="B45" t="n">
-        <v>82321</v>
+        <v>79160</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5314,21 +5324,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5341,10 +5351,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>730781</v>
+        <v>730880</v>
       </c>
       <c r="R45" t="n">
-        <v>7280800</v>
+        <v>7280720</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5371,12 +5381,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5404,10 +5414,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120473635</v>
+        <v>120470858</v>
       </c>
       <c r="B46" t="n">
-        <v>79131</v>
+        <v>78542</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5420,21 +5430,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5447,10 +5457,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>730880</v>
+        <v>730638</v>
       </c>
       <c r="R46" t="n">
-        <v>7280720</v>
+        <v>7280995</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5477,12 +5487,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5510,10 +5520,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120473129</v>
+        <v>120470867</v>
       </c>
       <c r="B47" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5526,21 +5536,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5553,10 +5563,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>730789</v>
+        <v>730630</v>
       </c>
       <c r="R47" t="n">
-        <v>7280765</v>
+        <v>7280999</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5583,12 +5593,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5616,10 +5626,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120470955</v>
+        <v>120473694</v>
       </c>
       <c r="B48" t="n">
-        <v>77489</v>
+        <v>57336</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5632,26 +5642,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>314</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5659,10 +5674,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>730533</v>
+        <v>730832</v>
       </c>
       <c r="R48" t="n">
-        <v>7281130</v>
+        <v>7280746</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5689,12 +5704,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5703,7 +5718,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5722,10 +5736,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120470967</v>
+        <v>120470896</v>
       </c>
       <c r="B49" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5738,21 +5752,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5765,10 +5779,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>730499</v>
+        <v>730587</v>
       </c>
       <c r="R49" t="n">
-        <v>7281166</v>
+        <v>7281038</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5828,10 +5842,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120473545</v>
+        <v>120473475</v>
       </c>
       <c r="B50" t="n">
-        <v>56532</v>
+        <v>82321</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5840,39 +5854,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5880,10 +5885,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>730894</v>
+        <v>730920</v>
       </c>
       <c r="R50" t="n">
-        <v>7280702</v>
+        <v>7280729</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5918,17 +5923,13 @@
           <t>2024-08-15</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Env höna med sina nästan utvuxna kycklingar på födosök i häckningsområdet.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5947,10 +5948,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120470935</v>
+        <v>120470967</v>
       </c>
       <c r="B51" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5963,21 +5964,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5990,10 +5991,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>730544</v>
+        <v>730499</v>
       </c>
       <c r="R51" t="n">
-        <v>7281102</v>
+        <v>7281166</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6053,10 +6054,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120473746</v>
+        <v>120473837</v>
       </c>
       <c r="B52" t="n">
-        <v>82321</v>
+        <v>78624</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6069,21 +6070,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6096,10 +6097,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>730814</v>
+        <v>730743</v>
       </c>
       <c r="R52" t="n">
-        <v>7280788</v>
+        <v>7280839</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6159,10 +6160,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120470890</v>
+        <v>120470915</v>
       </c>
       <c r="B53" t="n">
-        <v>82321</v>
+        <v>78576</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6175,21 +6176,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6198,14 +6199,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran , Pi lm</t>
+          <t>Garpmesliden-Römyran, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>730611</v>
+        <v>730563</v>
       </c>
       <c r="R53" t="n">
-        <v>7281039</v>
+        <v>7281056</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6265,10 +6266,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120470659</v>
+        <v>120470809</v>
       </c>
       <c r="B54" t="n">
-        <v>78624</v>
+        <v>96885</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6277,30 +6278,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>864</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6308,10 +6310,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>730744</v>
+        <v>730676</v>
       </c>
       <c r="R54" t="n">
-        <v>7280840</v>
+        <v>7280903</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6371,10 +6373,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120470475</v>
+        <v>120473159</v>
       </c>
       <c r="B55" t="n">
-        <v>78624</v>
+        <v>96885</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6383,30 +6385,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>864</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6414,10 +6417,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>730827</v>
+        <v>730803</v>
       </c>
       <c r="R55" t="n">
-        <v>7280751</v>
+        <v>7280729</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6444,12 +6447,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6477,10 +6480,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120470915</v>
+        <v>120470964</v>
       </c>
       <c r="B56" t="n">
-        <v>78576</v>
+        <v>97951</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6489,30 +6492,31 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>221952</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6520,10 +6524,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>730563</v>
+        <v>730499</v>
       </c>
       <c r="R56" t="n">
-        <v>7281056</v>
+        <v>7281141</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6583,10 +6587,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120470622</v>
+        <v>120473397</v>
       </c>
       <c r="B57" t="n">
-        <v>96885</v>
+        <v>57431</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6599,27 +6603,35 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6627,10 +6639,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>730781</v>
+        <v>730897</v>
       </c>
       <c r="R57" t="n">
-        <v>7280800</v>
+        <v>7280732</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6657,12 +6669,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>En familjgrupp i sitt revir. Det är gruppen som håller till kring Kikkejaureberget/Tjitterberget men mycket av deras revir och hemvist i naturskogsresterna har undan för undan avverkats trots miljölöften av statliga Sveaskog. Även aktuell fyndplats i naturskogsrestfragment är planerad för kalavverkning och markberedning!</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6671,7 +6688,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6690,10 +6706,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120473421</v>
+        <v>120473143</v>
       </c>
       <c r="B58" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6706,21 +6722,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6733,10 +6749,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>730869</v>
+        <v>730799</v>
       </c>
       <c r="R58" t="n">
-        <v>7280766</v>
+        <v>7280750</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6796,10 +6812,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120473159</v>
+        <v>120470889</v>
       </c>
       <c r="B59" t="n">
-        <v>96885</v>
+        <v>78542</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6808,42 +6824,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran, Pi lm</t>
+          <t>Garpmesliden-Römyran , Pi lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>730803</v>
+        <v>730611</v>
       </c>
       <c r="R59" t="n">
-        <v>7280729</v>
+        <v>7281039</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6870,12 +6885,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6903,10 +6918,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120473492</v>
+        <v>120473750</v>
       </c>
       <c r="B60" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6919,21 +6934,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6946,10 +6961,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>730912</v>
+        <v>730814</v>
       </c>
       <c r="R60" t="n">
-        <v>7280701</v>
+        <v>7280788</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7009,10 +7024,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120473697</v>
+        <v>120470940</v>
       </c>
       <c r="B61" t="n">
-        <v>78576</v>
+        <v>82321</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7025,21 +7040,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7052,10 +7067,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>730832</v>
+        <v>730551</v>
       </c>
       <c r="R61" t="n">
-        <v>7280746</v>
+        <v>7281090</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7082,12 +7097,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7115,10 +7130,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120473443</v>
+        <v>120473129</v>
       </c>
       <c r="B62" t="n">
-        <v>78624</v>
+        <v>90594</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7131,21 +7146,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>864</v>
+        <v>1204</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7158,10 +7173,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>730845</v>
+        <v>730789</v>
       </c>
       <c r="R62" t="n">
-        <v>7280809</v>
+        <v>7280765</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7221,10 +7236,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120473837</v>
+        <v>120470748</v>
       </c>
       <c r="B63" t="n">
-        <v>78624</v>
+        <v>78576</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7237,21 +7252,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7264,10 +7279,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>730743</v>
+        <v>730697</v>
       </c>
       <c r="R63" t="n">
-        <v>7280839</v>
+        <v>7280886</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7294,12 +7309,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7327,10 +7342,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120473472</v>
+        <v>120470955</v>
       </c>
       <c r="B64" t="n">
-        <v>78624</v>
+        <v>77489</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7343,21 +7358,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>864</v>
+        <v>314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7370,10 +7385,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>730920</v>
+        <v>730533</v>
       </c>
       <c r="R64" t="n">
-        <v>7280729</v>
+        <v>7281130</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7400,12 +7415,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7433,10 +7448,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120473420</v>
+        <v>120473443</v>
       </c>
       <c r="B65" t="n">
-        <v>82321</v>
+        <v>78624</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7449,21 +7464,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7476,10 +7491,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>730869</v>
+        <v>730845</v>
       </c>
       <c r="R65" t="n">
-        <v>7280766</v>
+        <v>7280809</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7539,10 +7554,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120473756</v>
+        <v>120470812</v>
       </c>
       <c r="B66" t="n">
-        <v>78542</v>
+        <v>97951</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7551,30 +7566,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7582,10 +7598,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>730833</v>
+        <v>730676</v>
       </c>
       <c r="R66" t="n">
-        <v>7280805</v>
+        <v>7280903</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7612,12 +7628,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7645,7 +7661,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120470478</v>
+        <v>120473148</v>
       </c>
       <c r="B67" t="n">
         <v>82321</v>
@@ -7688,10 +7704,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>730827</v>
+        <v>730803</v>
       </c>
       <c r="R67" t="n">
-        <v>7280751</v>
+        <v>7280729</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7718,12 +7734,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7751,10 +7767,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120470853</v>
+        <v>120473713</v>
       </c>
       <c r="B68" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7767,21 +7783,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7794,10 +7810,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>730639</v>
+        <v>730844</v>
       </c>
       <c r="R68" t="n">
-        <v>7280973</v>
+        <v>7280770</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7824,12 +7840,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7857,10 +7873,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120473754</v>
+        <v>120473572</v>
       </c>
       <c r="B69" t="n">
-        <v>78624</v>
+        <v>77474</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7873,21 +7889,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>864</v>
+        <v>6487</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7900,10 +7916,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>730833</v>
+        <v>730891</v>
       </c>
       <c r="R69" t="n">
-        <v>7280805</v>
+        <v>7280715</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7963,10 +7979,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120470789</v>
+        <v>120470614</v>
       </c>
       <c r="B70" t="n">
-        <v>78576</v>
+        <v>56524</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7979,26 +7995,27 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>185</v>
+        <v>102612</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8006,10 +8023,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>730676</v>
+        <v>730776</v>
       </c>
       <c r="R70" t="n">
-        <v>7280903</v>
+        <v>7280790</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8050,7 +8067,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8069,10 +8085,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120473156</v>
+        <v>120470622</v>
       </c>
       <c r="B71" t="n">
-        <v>78624</v>
+        <v>96885</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8081,30 +8097,31 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>864</v>
+        <v>221945</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -8112,10 +8129,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>730803</v>
+        <v>730781</v>
       </c>
       <c r="R71" t="n">
-        <v>7280729</v>
+        <v>7280800</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8142,12 +8159,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8175,10 +8192,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120473808</v>
+        <v>120473565</v>
       </c>
       <c r="B72" t="n">
-        <v>78624</v>
+        <v>78576</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8191,21 +8208,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8218,10 +8235,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>730795</v>
+        <v>730915</v>
       </c>
       <c r="R72" t="n">
-        <v>7280824</v>
+        <v>7280682</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8281,10 +8298,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120470795</v>
+        <v>120473746</v>
       </c>
       <c r="B73" t="n">
-        <v>90545</v>
+        <v>82321</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8293,25 +8310,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8324,10 +8341,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>730676</v>
+        <v>730814</v>
       </c>
       <c r="R73" t="n">
-        <v>7280903</v>
+        <v>7280788</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8354,12 +8371,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8387,10 +8404,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120470498</v>
+        <v>120473156</v>
       </c>
       <c r="B74" t="n">
-        <v>57336</v>
+        <v>78624</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8403,43 +8420,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>864</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8447,10 +8447,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>730827</v>
+        <v>730803</v>
       </c>
       <c r="R74" t="n">
-        <v>7280751</v>
+        <v>7280729</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8491,6 +8491,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8509,10 +8510,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120473148</v>
+        <v>120473775</v>
       </c>
       <c r="B75" t="n">
-        <v>82321</v>
+        <v>78624</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8525,21 +8526,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8552,10 +8553,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>730803</v>
+        <v>730816</v>
       </c>
       <c r="R75" t="n">
-        <v>7280729</v>
+        <v>7280822</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8615,10 +8616,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120470914</v>
+        <v>120473808</v>
       </c>
       <c r="B76" t="n">
-        <v>90594</v>
+        <v>78624</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8631,21 +8632,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8658,10 +8659,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>730563</v>
+        <v>730795</v>
       </c>
       <c r="R76" t="n">
-        <v>7281056</v>
+        <v>7280824</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8688,12 +8689,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8721,10 +8722,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120473750</v>
+        <v>120473472</v>
       </c>
       <c r="B77" t="n">
-        <v>78542</v>
+        <v>78624</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8737,21 +8738,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8764,10 +8765,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>730814</v>
+        <v>730920</v>
       </c>
       <c r="R77" t="n">
-        <v>7280788</v>
+        <v>7280729</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8827,7 +8828,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120473413</v>
+        <v>120470935</v>
       </c>
       <c r="B78" t="n">
         <v>82321</v>
@@ -8870,10 +8871,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>730907</v>
+        <v>730544</v>
       </c>
       <c r="R78" t="n">
-        <v>7280757</v>
+        <v>7281102</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8900,12 +8901,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8933,10 +8934,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120473397</v>
+        <v>120473635</v>
       </c>
       <c r="B79" t="n">
-        <v>57431</v>
+        <v>79131</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8945,39 +8946,30 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103031</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -8985,10 +8977,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>730897</v>
+        <v>730880</v>
       </c>
       <c r="R79" t="n">
-        <v>7280732</v>
+        <v>7280720</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9023,17 +9015,13 @@
           <t>2024-08-15</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>En familjgrupp i sitt revir. Det är gruppen som håller till kring Kikkejaureberget/Tjitterberget men mycket av deras revir och hemvist i naturskogsresterna har undan för undan avverkats trots miljölöften av statliga Sveaskog. Även aktuell fyndplats i naturskogsrestfragment är planerad för kalavverkning och markberedning!</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9052,10 +9040,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120470997</v>
+        <v>120470475</v>
       </c>
       <c r="B80" t="n">
-        <v>78576</v>
+        <v>78624</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9068,21 +9056,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9095,10 +9083,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>730452</v>
+        <v>730827</v>
       </c>
       <c r="R80" t="n">
-        <v>7281226</v>
+        <v>7280751</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9158,10 +9146,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120473592</v>
+        <v>120473450</v>
       </c>
       <c r="B81" t="n">
-        <v>74651</v>
+        <v>77883</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9170,25 +9158,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>311</v>
+        <v>498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9201,10 +9189,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>730891</v>
+        <v>730869</v>
       </c>
       <c r="R81" t="n">
-        <v>7280715</v>
+        <v>7280791</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9264,10 +9252,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120470546</v>
+        <v>120470853</v>
       </c>
       <c r="B82" t="n">
-        <v>78624</v>
+        <v>82321</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9280,21 +9268,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9307,10 +9295,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>730856</v>
+        <v>730639</v>
       </c>
       <c r="R82" t="n">
-        <v>7280769</v>
+        <v>7280973</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9370,10 +9358,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120473694</v>
+        <v>120470660</v>
       </c>
       <c r="B83" t="n">
-        <v>57336</v>
+        <v>96885</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9382,35 +9370,31 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9418,10 +9402,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>730832</v>
+        <v>730744</v>
       </c>
       <c r="R83" t="n">
-        <v>7280746</v>
+        <v>7280840</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9448,12 +9432,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9462,6 +9446,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9480,10 +9465,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120473444</v>
+        <v>120470942</v>
       </c>
       <c r="B84" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9496,21 +9481,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9523,10 +9508,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>730845</v>
+        <v>730551</v>
       </c>
       <c r="R84" t="n">
-        <v>7280809</v>
+        <v>7281090</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9553,12 +9538,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9586,10 +9571,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120470887</v>
+        <v>120470659</v>
       </c>
       <c r="B85" t="n">
-        <v>96885</v>
+        <v>78624</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9598,31 +9583,30 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221945</v>
+        <v>864</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -9630,10 +9614,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>730622</v>
+        <v>730744</v>
       </c>
       <c r="R85" t="n">
-        <v>7281028</v>
+        <v>7280840</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9693,10 +9677,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120470748</v>
+        <v>120473571</v>
       </c>
       <c r="B86" t="n">
-        <v>78576</v>
+        <v>90506</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9709,21 +9693,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>185</v>
+        <v>3242</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9736,10 +9720,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>730697</v>
+        <v>730915</v>
       </c>
       <c r="R86" t="n">
-        <v>7280886</v>
+        <v>7280682</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9766,12 +9750,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9799,10 +9783,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120470888</v>
+        <v>120473606</v>
       </c>
       <c r="B87" t="n">
-        <v>78576</v>
+        <v>79160</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9815,21 +9799,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9838,14 +9822,14 @@
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran , Pi lm</t>
+          <t>Garpmesliden-Römyran, Pi lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>730611</v>
+        <v>730869</v>
       </c>
       <c r="R87" t="n">
-        <v>7281039</v>
+        <v>7280698</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9872,12 +9856,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9905,10 +9889,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120473410</v>
+        <v>120473407</v>
       </c>
       <c r="B88" t="n">
-        <v>78624</v>
+        <v>78542</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9921,21 +9905,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10011,10 +9995,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120470945</v>
+        <v>120470909</v>
       </c>
       <c r="B89" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10027,21 +10011,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10054,10 +10038,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>730551</v>
+        <v>730587</v>
       </c>
       <c r="R89" t="n">
-        <v>7281090</v>
+        <v>7281038</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10117,10 +10101,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120470957</v>
+        <v>120470931</v>
       </c>
       <c r="B90" t="n">
-        <v>82321</v>
+        <v>56532</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10129,30 +10113,47 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10160,10 +10161,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>730533</v>
+        <v>730544</v>
       </c>
       <c r="R90" t="n">
-        <v>7281130</v>
+        <v>7281102</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10204,7 +10205,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -10223,10 +10223,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120470812</v>
+        <v>120470646</v>
       </c>
       <c r="B91" t="n">
-        <v>97951</v>
+        <v>96885</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10239,21 +10239,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10267,10 +10267,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>730676</v>
+        <v>730765</v>
       </c>
       <c r="R91" t="n">
-        <v>7280903</v>
+        <v>7280814</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10330,10 +10330,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120473835</v>
+        <v>120470617</v>
       </c>
       <c r="B92" t="n">
-        <v>97951</v>
+        <v>96885</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10346,21 +10346,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10374,10 +10374,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>730783</v>
+        <v>730776</v>
       </c>
       <c r="R92" t="n">
-        <v>7280820</v>
+        <v>7280790</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10404,12 +10404,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10437,10 +10437,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120473201</v>
+        <v>120470887</v>
       </c>
       <c r="B93" t="n">
-        <v>96891</v>
+        <v>96885</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10453,16 +10453,16 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>730852</v>
+        <v>730622</v>
       </c>
       <c r="R93" t="n">
-        <v>7280740</v>
+        <v>7281028</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10511,12 +10511,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD93" t="b">

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120470655</v>
+        <v>120473835</v>
       </c>
       <c r="B2" t="n">
-        <v>82321</v>
+        <v>97951</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730744</v>
+        <v>730783</v>
       </c>
       <c r="R2" t="n">
-        <v>7280840</v>
+        <v>7280820</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120473420</v>
+        <v>120470655</v>
       </c>
       <c r="B3" t="n">
         <v>82321</v>
@@ -824,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730869</v>
+        <v>730744</v>
       </c>
       <c r="R3" t="n">
-        <v>7280766</v>
+        <v>7280840</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -854,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120473410</v>
+        <v>120473420</v>
       </c>
       <c r="B4" t="n">
-        <v>78624</v>
+        <v>82321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730907</v>
+        <v>730869</v>
       </c>
       <c r="R4" t="n">
-        <v>7280757</v>
+        <v>7280766</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120473421</v>
+        <v>120473410</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>78624</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1010,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730869</v>
+        <v>730907</v>
       </c>
       <c r="R5" t="n">
-        <v>7280766</v>
+        <v>7280757</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,7 +1100,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120473756</v>
+        <v>120473421</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1142,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730833</v>
+        <v>730869</v>
       </c>
       <c r="R6" t="n">
-        <v>7280805</v>
+        <v>7280766</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120473835</v>
+        <v>120473756</v>
       </c>
       <c r="B7" t="n">
-        <v>97951</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,31 +1218,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730783</v>
+        <v>730833</v>
       </c>
       <c r="R7" t="n">
-        <v>7280820</v>
+        <v>7280805</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -2626,10 +2626,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120470795</v>
+        <v>120473699</v>
       </c>
       <c r="B20" t="n">
-        <v>90545</v>
+        <v>89650</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2638,25 +2638,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730676</v>
+        <v>730844</v>
       </c>
       <c r="R20" t="n">
-        <v>7280903</v>
+        <v>7280770</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2699,12 +2699,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2732,10 +2732,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120470997</v>
+        <v>120470957</v>
       </c>
       <c r="B21" t="n">
-        <v>78576</v>
+        <v>82321</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2748,21 +2748,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>730452</v>
+        <v>730533</v>
       </c>
       <c r="R21" t="n">
-        <v>7281226</v>
+        <v>7281130</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2838,10 +2838,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120470789</v>
+        <v>120470914</v>
       </c>
       <c r="B22" t="n">
-        <v>78576</v>
+        <v>90594</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2854,21 +2854,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2881,10 +2881,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730676</v>
+        <v>730563</v>
       </c>
       <c r="R22" t="n">
-        <v>7280903</v>
+        <v>7281056</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2944,10 +2944,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120473699</v>
+        <v>120470795</v>
       </c>
       <c r="B23" t="n">
-        <v>89650</v>
+        <v>90545</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2956,25 +2956,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1962</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730844</v>
+        <v>730676</v>
       </c>
       <c r="R23" t="n">
-        <v>7280770</v>
+        <v>7280903</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3017,12 +3017,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3050,10 +3050,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120470957</v>
+        <v>120470498</v>
       </c>
       <c r="B24" t="n">
-        <v>82321</v>
+        <v>57336</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3066,26 +3066,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3093,10 +3110,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>730533</v>
+        <v>730827</v>
       </c>
       <c r="R24" t="n">
-        <v>7281130</v>
+        <v>7280751</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3137,7 +3154,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3156,10 +3172,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120470914</v>
+        <v>120470997</v>
       </c>
       <c r="B25" t="n">
-        <v>90594</v>
+        <v>78576</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3172,21 +3188,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3199,10 +3215,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>730563</v>
+        <v>730452</v>
       </c>
       <c r="R25" t="n">
-        <v>7281056</v>
+        <v>7281226</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3262,10 +3278,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120470498</v>
+        <v>120470789</v>
       </c>
       <c r="B26" t="n">
-        <v>57336</v>
+        <v>78576</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3278,43 +3294,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3322,10 +3321,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730827</v>
+        <v>730676</v>
       </c>
       <c r="R26" t="n">
-        <v>7280751</v>
+        <v>7280903</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3366,6 +3365,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3928,10 +3928,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120473132</v>
+        <v>120473697</v>
       </c>
       <c r="B32" t="n">
-        <v>96885</v>
+        <v>78576</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3940,31 +3940,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3972,10 +3971,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730789</v>
+        <v>730832</v>
       </c>
       <c r="R32" t="n">
-        <v>7280765</v>
+        <v>7280746</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4035,10 +4034,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120473201</v>
+        <v>120473592</v>
       </c>
       <c r="B33" t="n">
-        <v>96891</v>
+        <v>74651</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4051,27 +4050,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221941</v>
+        <v>311</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4079,10 +4077,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>730852</v>
+        <v>730891</v>
       </c>
       <c r="R33" t="n">
-        <v>7280740</v>
+        <v>7280715</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4142,10 +4140,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120470478</v>
+        <v>120473754</v>
       </c>
       <c r="B34" t="n">
-        <v>82321</v>
+        <v>78624</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4158,21 +4156,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4185,10 +4183,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730827</v>
+        <v>730833</v>
       </c>
       <c r="R34" t="n">
-        <v>7280751</v>
+        <v>7280805</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4215,12 +4213,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4248,10 +4246,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120470733</v>
+        <v>120473547</v>
       </c>
       <c r="B35" t="n">
-        <v>82321</v>
+        <v>91858</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4260,25 +4258,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4291,10 +4289,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730717</v>
+        <v>730894</v>
       </c>
       <c r="R35" t="n">
-        <v>7280872</v>
+        <v>7280702</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4321,12 +4319,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4354,10 +4352,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120473697</v>
+        <v>120470478</v>
       </c>
       <c r="B36" t="n">
-        <v>78576</v>
+        <v>82321</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4370,21 +4368,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4397,10 +4395,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730832</v>
+        <v>730827</v>
       </c>
       <c r="R36" t="n">
-        <v>7280746</v>
+        <v>7280751</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4427,12 +4425,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4460,10 +4458,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120473592</v>
+        <v>120470733</v>
       </c>
       <c r="B37" t="n">
-        <v>74651</v>
+        <v>82321</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4472,25 +4470,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>311</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4503,10 +4501,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730891</v>
+        <v>730717</v>
       </c>
       <c r="R37" t="n">
-        <v>7280715</v>
+        <v>7280872</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4533,12 +4531,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4566,10 +4564,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120473754</v>
+        <v>120473132</v>
       </c>
       <c r="B38" t="n">
-        <v>78624</v>
+        <v>96885</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4578,30 +4576,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>864</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4609,10 +4608,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730833</v>
+        <v>730789</v>
       </c>
       <c r="R38" t="n">
-        <v>7280805</v>
+        <v>7280765</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4672,10 +4671,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120473547</v>
+        <v>120473201</v>
       </c>
       <c r="B39" t="n">
-        <v>91858</v>
+        <v>96891</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4688,26 +4687,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730894</v>
+        <v>730852</v>
       </c>
       <c r="R39" t="n">
-        <v>7280702</v>
+        <v>7280740</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5202,10 +5202,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120470872</v>
+        <v>120473626</v>
       </c>
       <c r="B44" t="n">
-        <v>82321</v>
+        <v>79160</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5218,21 +5218,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>730630</v>
+        <v>730880</v>
       </c>
       <c r="R44" t="n">
-        <v>7280999</v>
+        <v>7280720</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5308,10 +5308,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120473626</v>
+        <v>120470872</v>
       </c>
       <c r="B45" t="n">
-        <v>79160</v>
+        <v>82321</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5324,21 +5324,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5351,10 +5351,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>730880</v>
+        <v>730630</v>
       </c>
       <c r="R45" t="n">
-        <v>7280720</v>
+        <v>7280999</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5381,12 +5381,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -7236,10 +7236,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120470748</v>
+        <v>120473443</v>
       </c>
       <c r="B63" t="n">
-        <v>78576</v>
+        <v>78624</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7252,21 +7252,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>730697</v>
+        <v>730845</v>
       </c>
       <c r="R63" t="n">
-        <v>7280886</v>
+        <v>7280809</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7309,12 +7309,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7342,10 +7342,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120470955</v>
+        <v>120470812</v>
       </c>
       <c r="B64" t="n">
-        <v>77489</v>
+        <v>97951</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7354,30 +7354,31 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>314</v>
+        <v>221952</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7385,10 +7386,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>730533</v>
+        <v>730676</v>
       </c>
       <c r="R64" t="n">
-        <v>7281130</v>
+        <v>7280903</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7448,10 +7449,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120473443</v>
+        <v>120470748</v>
       </c>
       <c r="B65" t="n">
-        <v>78624</v>
+        <v>78576</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7464,21 +7465,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7491,10 +7492,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>730845</v>
+        <v>730697</v>
       </c>
       <c r="R65" t="n">
-        <v>7280809</v>
+        <v>7280886</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7521,12 +7522,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7554,10 +7555,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120470812</v>
+        <v>120470955</v>
       </c>
       <c r="B66" t="n">
-        <v>97951</v>
+        <v>77489</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7566,31 +7567,30 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221952</v>
+        <v>314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7598,10 +7598,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>730676</v>
+        <v>730533</v>
       </c>
       <c r="R66" t="n">
-        <v>7280903</v>
+        <v>7281130</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -9146,10 +9146,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120473450</v>
+        <v>120470942</v>
       </c>
       <c r="B81" t="n">
-        <v>77883</v>
+        <v>78542</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9158,25 +9158,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9189,10 +9189,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>730869</v>
+        <v>730551</v>
       </c>
       <c r="R81" t="n">
-        <v>7280791</v>
+        <v>7281090</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9219,12 +9219,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9252,10 +9252,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120470853</v>
+        <v>120470660</v>
       </c>
       <c r="B82" t="n">
-        <v>82321</v>
+        <v>96885</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9264,30 +9264,31 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9295,10 +9296,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>730639</v>
+        <v>730744</v>
       </c>
       <c r="R82" t="n">
-        <v>7280973</v>
+        <v>7280840</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9358,10 +9359,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120470660</v>
+        <v>120473450</v>
       </c>
       <c r="B83" t="n">
-        <v>96885</v>
+        <v>77883</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9370,31 +9371,30 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221945</v>
+        <v>498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9402,10 +9402,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>730744</v>
+        <v>730869</v>
       </c>
       <c r="R83" t="n">
-        <v>7280840</v>
+        <v>7280791</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9432,12 +9432,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9465,10 +9465,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120470942</v>
+        <v>120470853</v>
       </c>
       <c r="B84" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9481,21 +9481,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9508,10 +9508,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>730551</v>
+        <v>730639</v>
       </c>
       <c r="R84" t="n">
-        <v>7281090</v>
+        <v>7280973</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -10544,10 +10544,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121231715</v>
+        <v>121231798</v>
       </c>
       <c r="B94" t="n">
-        <v>56552</v>
+        <v>57504</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10560,33 +10560,29 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -10596,10 +10592,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>730569</v>
+        <v>730872</v>
       </c>
       <c r="R94" t="n">
-        <v>7281064</v>
+        <v>7280743</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10626,17 +10622,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>En tupp och tre höns.</t>
+          <t>Familjeflocken i sitt revir, dvs revirparet med kvarvarande ungfåglar.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10663,10 +10659,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121231790</v>
+        <v>121231720</v>
       </c>
       <c r="B95" t="n">
-        <v>57364</v>
+        <v>57504</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10679,37 +10675,33 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -10719,10 +10711,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>730862</v>
+        <v>730749</v>
       </c>
       <c r="R95" t="n">
-        <v>7280795</v>
+        <v>7280849</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10749,17 +10741,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>En adult hane på födosök i sitt revir dvs del av den.</t>
+          <t>De sågs även tidigare i sitt revir. Revirparet och kvarvarande ungfåglar.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10786,10 +10778,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121231720</v>
+        <v>121231680</v>
       </c>
       <c r="B96" t="n">
-        <v>57501</v>
+        <v>57462</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10798,32 +10790,28 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
@@ -10838,10 +10826,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>730749</v>
+        <v>730504</v>
       </c>
       <c r="R96" t="n">
-        <v>7280849</v>
+        <v>7281155</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10878,7 +10866,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>De sågs även tidigare i sitt revir. Revirparet och kvarvarande ungfåglar.</t>
+          <t>Familjgruppen som har tidigare observerats i området, naturskogen verkar tydligen vara en viktig del i deras revir och hemvist.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10905,10 +10893,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121231680</v>
+        <v>121231790</v>
       </c>
       <c r="B97" t="n">
-        <v>57459</v>
+        <v>57367</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10917,20 +10905,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10938,12 +10926,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -10953,10 +10949,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>730504</v>
+        <v>730862</v>
       </c>
       <c r="R97" t="n">
-        <v>7281155</v>
+        <v>7280795</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10983,17 +10979,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Familjgruppen som har tidigare observerats i området, naturskogen verkar tydligen vara en viktig del i deras revir och hemvist.</t>
+          <t>En adult hane på födosök i sitt revir dvs del av den.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11020,10 +11016,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121231798</v>
+        <v>121231715</v>
       </c>
       <c r="B98" t="n">
-        <v>57501</v>
+        <v>56555</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11036,29 +11032,33 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -11068,10 +11068,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>730872</v>
+        <v>730569</v>
       </c>
       <c r="R98" t="n">
-        <v>7280743</v>
+        <v>7281064</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11098,17 +11098,17 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Familjeflocken i sitt revir, dvs revirparet med kvarvarande ungfåglar.</t>
+          <t>En tupp och tre höns.</t>
         </is>
       </c>
       <c r="AD98" t="b">

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -10893,10 +10893,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121231790</v>
+        <v>121231715</v>
       </c>
       <c r="B97" t="n">
-        <v>57367</v>
+        <v>56555</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10909,16 +10909,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10928,18 +10928,14 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -10949,10 +10945,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>730862</v>
+        <v>730569</v>
       </c>
       <c r="R97" t="n">
-        <v>7280795</v>
+        <v>7281064</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10979,17 +10975,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>En adult hane på födosök i sitt revir dvs del av den.</t>
+          <t>En tupp och tre höns.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11016,10 +11012,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121231715</v>
+        <v>121231790</v>
       </c>
       <c r="B98" t="n">
-        <v>56555</v>
+        <v>57367</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11032,16 +11028,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -11051,14 +11047,18 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -11068,10 +11068,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>730569</v>
+        <v>730862</v>
       </c>
       <c r="R98" t="n">
-        <v>7281064</v>
+        <v>7280795</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11098,17 +11098,17 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>En tupp och tre höns.</t>
+          <t>En adult hane på födosök i sitt revir dvs del av den.</t>
         </is>
       </c>
       <c r="AD98" t="b">

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -10544,10 +10544,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121231798</v>
+        <v>121231680</v>
       </c>
       <c r="B94" t="n">
-        <v>57504</v>
+        <v>57462</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10556,25 +10556,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10582,7 +10582,7 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -10592,10 +10592,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>730872</v>
+        <v>730504</v>
       </c>
       <c r="R94" t="n">
-        <v>7280743</v>
+        <v>7281155</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10622,17 +10622,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Familjeflocken i sitt revir, dvs revirparet med kvarvarande ungfåglar.</t>
+          <t>Familjgruppen som har tidigare observerats i området, naturskogen verkar tydligen vara en viktig del i deras revir och hemvist.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10659,7 +10659,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121231720</v>
+        <v>121231798</v>
       </c>
       <c r="B95" t="n">
         <v>57504</v>
@@ -10692,16 +10692,12 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -10711,10 +10707,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>730749</v>
+        <v>730872</v>
       </c>
       <c r="R95" t="n">
-        <v>7280849</v>
+        <v>7280743</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10741,17 +10737,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>De sågs även tidigare i sitt revir. Revirparet och kvarvarande ungfåglar.</t>
+          <t>Familjeflocken i sitt revir, dvs revirparet med kvarvarande ungfåglar.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10778,10 +10774,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121231680</v>
+        <v>121231720</v>
       </c>
       <c r="B96" t="n">
-        <v>57462</v>
+        <v>57504</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10790,28 +10786,32 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
@@ -10826,10 +10826,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>730504</v>
+        <v>730749</v>
       </c>
       <c r="R96" t="n">
-        <v>7281155</v>
+        <v>7280849</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Familjgruppen som har tidigare observerats i området, naturskogen verkar tydligen vara en viktig del i deras revir och hemvist.</t>
+          <t>De sågs även tidigare i sitt revir. Revirparet och kvarvarande ungfåglar.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10893,10 +10893,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121231715</v>
+        <v>121231790</v>
       </c>
       <c r="B97" t="n">
-        <v>56555</v>
+        <v>57367</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10909,16 +10909,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10928,14 +10928,18 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -10945,10 +10949,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>730569</v>
+        <v>730862</v>
       </c>
       <c r="R97" t="n">
-        <v>7281064</v>
+        <v>7280795</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10975,17 +10979,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>En tupp och tre höns.</t>
+          <t>En adult hane på födosök i sitt revir dvs del av den.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11012,10 +11016,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121231790</v>
+        <v>121231715</v>
       </c>
       <c r="B98" t="n">
-        <v>57367</v>
+        <v>56555</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11028,16 +11032,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -11047,18 +11051,14 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -11068,10 +11068,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>730862</v>
+        <v>730569</v>
       </c>
       <c r="R98" t="n">
-        <v>7280795</v>
+        <v>7281064</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11098,17 +11098,17 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>En adult hane på födosök i sitt revir dvs del av den.</t>
+          <t>En tupp och tre höns.</t>
         </is>
       </c>
       <c r="AD98" t="b">

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -10544,10 +10544,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121231680</v>
+        <v>121231798</v>
       </c>
       <c r="B94" t="n">
-        <v>57462</v>
+        <v>57504</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10556,25 +10556,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10582,7 +10582,7 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -10592,10 +10592,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>730504</v>
+        <v>730872</v>
       </c>
       <c r="R94" t="n">
-        <v>7281155</v>
+        <v>7280743</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10622,17 +10622,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Familjgruppen som har tidigare observerats i området, naturskogen verkar tydligen vara en viktig del i deras revir och hemvist.</t>
+          <t>Familjeflocken i sitt revir, dvs revirparet med kvarvarande ungfåglar.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10659,10 +10659,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121231798</v>
+        <v>121231680</v>
       </c>
       <c r="B95" t="n">
-        <v>57504</v>
+        <v>57462</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10671,25 +10671,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10697,7 +10697,7 @@
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -10707,10 +10707,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>730872</v>
+        <v>730504</v>
       </c>
       <c r="R95" t="n">
-        <v>7280743</v>
+        <v>7281155</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10737,17 +10737,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Familjeflocken i sitt revir, dvs revirparet med kvarvarande ungfåglar.</t>
+          <t>Familjgruppen som har tidigare observerats i området, naturskogen verkar tydligen vara en viktig del i deras revir och hemvist.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10774,10 +10774,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121231720</v>
+        <v>121231790</v>
       </c>
       <c r="B96" t="n">
-        <v>57504</v>
+        <v>57367</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10790,33 +10790,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -10826,10 +10830,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>730749</v>
+        <v>730862</v>
       </c>
       <c r="R96" t="n">
-        <v>7280849</v>
+        <v>7280795</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10856,17 +10860,17 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>De sågs även tidigare i sitt revir. Revirparet och kvarvarande ungfåglar.</t>
+          <t>En adult hane på födosök i sitt revir dvs del av den.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10893,10 +10897,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121231790</v>
+        <v>121231715</v>
       </c>
       <c r="B97" t="n">
-        <v>57367</v>
+        <v>56555</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10909,16 +10913,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10928,18 +10932,14 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -10949,10 +10949,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>730862</v>
+        <v>730569</v>
       </c>
       <c r="R97" t="n">
-        <v>7280795</v>
+        <v>7281064</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10979,17 +10979,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>En adult hane på födosök i sitt revir dvs del av den.</t>
+          <t>En tupp och tre höns.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11016,10 +11016,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121231715</v>
+        <v>121231720</v>
       </c>
       <c r="B98" t="n">
-        <v>56555</v>
+        <v>57504</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11032,26 +11032,26 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -11068,10 +11068,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>730569</v>
+        <v>730749</v>
       </c>
       <c r="R98" t="n">
-        <v>7281064</v>
+        <v>7280849</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>En tupp och tre höns.</t>
+          <t>De sågs även tidigare i sitt revir. Revirparet och kvarvarande ungfåglar.</t>
         </is>
       </c>
       <c r="AD98" t="b">

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -10544,10 +10544,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121231798</v>
+        <v>121231680</v>
       </c>
       <c r="B94" t="n">
-        <v>57504</v>
+        <v>57462</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10556,25 +10556,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10582,7 +10582,7 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -10592,10 +10592,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>730872</v>
+        <v>730504</v>
       </c>
       <c r="R94" t="n">
-        <v>7280743</v>
+        <v>7281155</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10622,17 +10622,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Familjeflocken i sitt revir, dvs revirparet med kvarvarande ungfåglar.</t>
+          <t>Familjgruppen som har tidigare observerats i området, naturskogen verkar tydligen vara en viktig del i deras revir och hemvist.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10659,10 +10659,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121231680</v>
+        <v>121231720</v>
       </c>
       <c r="B95" t="n">
-        <v>57462</v>
+        <v>57504</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10671,28 +10671,32 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
@@ -10707,10 +10711,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>730504</v>
+        <v>730749</v>
       </c>
       <c r="R95" t="n">
-        <v>7281155</v>
+        <v>7280849</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10747,7 +10751,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Familjgruppen som har tidigare observerats i området, naturskogen verkar tydligen vara en viktig del i deras revir och hemvist.</t>
+          <t>De sågs även tidigare i sitt revir. Revirparet och kvarvarande ungfåglar.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10774,10 +10778,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121231790</v>
+        <v>121231715</v>
       </c>
       <c r="B96" t="n">
-        <v>57367</v>
+        <v>56555</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10790,16 +10794,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10809,18 +10813,14 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -10830,10 +10830,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>730862</v>
+        <v>730569</v>
       </c>
       <c r="R96" t="n">
-        <v>7280795</v>
+        <v>7281064</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10860,17 +10860,17 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>En adult hane på födosök i sitt revir dvs del av den.</t>
+          <t>En tupp och tre höns.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10897,10 +10897,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121231715</v>
+        <v>121231790</v>
       </c>
       <c r="B97" t="n">
-        <v>56555</v>
+        <v>57367</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10913,16 +10913,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10932,14 +10932,18 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -10949,10 +10953,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>730569</v>
+        <v>730862</v>
       </c>
       <c r="R97" t="n">
-        <v>7281064</v>
+        <v>7280795</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10979,17 +10983,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>En tupp och tre höns.</t>
+          <t>En adult hane på födosök i sitt revir dvs del av den.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11016,7 +11020,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121231720</v>
+        <v>121231798</v>
       </c>
       <c r="B98" t="n">
         <v>57504</v>
@@ -11049,16 +11053,12 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -11068,10 +11068,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>730749</v>
+        <v>730872</v>
       </c>
       <c r="R98" t="n">
-        <v>7280849</v>
+        <v>7280743</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11098,17 +11098,17 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>De sågs även tidigare i sitt revir. Revirparet och kvarvarande ungfåglar.</t>
+          <t>Familjeflocken i sitt revir, dvs revirparet med kvarvarande ungfåglar.</t>
         </is>
       </c>
       <c r="AD98" t="b">

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -10544,10 +10544,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121231680</v>
+        <v>121231720</v>
       </c>
       <c r="B94" t="n">
-        <v>57462</v>
+        <v>57507</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10556,28 +10556,32 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
@@ -10592,10 +10596,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>730504</v>
+        <v>730749</v>
       </c>
       <c r="R94" t="n">
-        <v>7281155</v>
+        <v>7280849</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10632,7 +10636,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Familjgruppen som har tidigare observerats i området, naturskogen verkar tydligen vara en viktig del i deras revir och hemvist.</t>
+          <t>De sågs även tidigare i sitt revir. Revirparet och kvarvarande ungfåglar.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10659,10 +10663,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121231720</v>
+        <v>121231798</v>
       </c>
       <c r="B95" t="n">
-        <v>57504</v>
+        <v>57507</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10692,16 +10696,12 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -10711,10 +10711,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>730749</v>
+        <v>730872</v>
       </c>
       <c r="R95" t="n">
-        <v>7280849</v>
+        <v>7280743</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10741,17 +10741,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>De sågs även tidigare i sitt revir. Revirparet och kvarvarande ungfåglar.</t>
+          <t>Familjeflocken i sitt revir, dvs revirparet med kvarvarande ungfåglar.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10778,10 +10778,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121231715</v>
+        <v>121231790</v>
       </c>
       <c r="B96" t="n">
-        <v>56555</v>
+        <v>57370</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10794,16 +10794,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10813,14 +10813,18 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -10830,10 +10834,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>730569</v>
+        <v>730862</v>
       </c>
       <c r="R96" t="n">
-        <v>7281064</v>
+        <v>7280795</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10860,17 +10864,17 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>En tupp och tre höns.</t>
+          <t>En adult hane på födosök i sitt revir dvs del av den.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10897,10 +10901,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121231790</v>
+        <v>121231680</v>
       </c>
       <c r="B97" t="n">
-        <v>57367</v>
+        <v>57465</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10909,20 +10913,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10930,20 +10934,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -10953,10 +10949,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>730862</v>
+        <v>730504</v>
       </c>
       <c r="R97" t="n">
-        <v>7280795</v>
+        <v>7281155</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10983,17 +10979,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>En adult hane på födosök i sitt revir dvs del av den.</t>
+          <t>Familjgruppen som har tidigare observerats i området, naturskogen verkar tydligen vara en viktig del i deras revir och hemvist.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11020,10 +11016,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121231798</v>
+        <v>121231715</v>
       </c>
       <c r="B98" t="n">
-        <v>57504</v>
+        <v>56558</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11036,29 +11032,33 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -11068,10 +11068,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>730872</v>
+        <v>730569</v>
       </c>
       <c r="R98" t="n">
-        <v>7280743</v>
+        <v>7281064</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11098,17 +11098,17 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Familjeflocken i sitt revir, dvs revirparet med kvarvarande ungfåglar.</t>
+          <t>En tupp och tre höns.</t>
         </is>
       </c>
       <c r="AD98" t="b">

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -10544,10 +10544,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121231720</v>
+        <v>121231715</v>
       </c>
       <c r="B94" t="n">
-        <v>57507</v>
+        <v>56558</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10560,26 +10560,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -10596,10 +10596,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>730749</v>
+        <v>730569</v>
       </c>
       <c r="R94" t="n">
-        <v>7280849</v>
+        <v>7281064</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10636,7 +10636,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>De sågs även tidigare i sitt revir. Revirparet och kvarvarande ungfåglar.</t>
+          <t>En tupp och tre höns.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11016,10 +11016,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121231715</v>
+        <v>121231720</v>
       </c>
       <c r="B98" t="n">
-        <v>56558</v>
+        <v>57507</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11032,26 +11032,26 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -11068,10 +11068,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>730569</v>
+        <v>730749</v>
       </c>
       <c r="R98" t="n">
-        <v>7281064</v>
+        <v>7280849</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>En tupp och tre höns.</t>
+          <t>De sågs även tidigare i sitt revir. Revirparet och kvarvarande ungfåglar.</t>
         </is>
       </c>
       <c r="AD98" t="b">

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -10544,10 +10544,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121231715</v>
+        <v>121231798</v>
       </c>
       <c r="B94" t="n">
-        <v>56558</v>
+        <v>57508</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10560,33 +10560,29 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -10596,10 +10592,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>730569</v>
+        <v>730872</v>
       </c>
       <c r="R94" t="n">
-        <v>7281064</v>
+        <v>7280743</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10626,17 +10622,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>En tupp och tre höns.</t>
+          <t>Familjeflocken i sitt revir, dvs revirparet med kvarvarande ungfåglar.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10663,10 +10659,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121231798</v>
+        <v>121231680</v>
       </c>
       <c r="B95" t="n">
-        <v>57507</v>
+        <v>57466</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10675,25 +10671,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10701,7 +10697,7 @@
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -10711,10 +10707,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>730872</v>
+        <v>730504</v>
       </c>
       <c r="R95" t="n">
-        <v>7280743</v>
+        <v>7281155</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10741,17 +10737,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Familjeflocken i sitt revir, dvs revirparet med kvarvarande ungfåglar.</t>
+          <t>Familjgruppen som har tidigare observerats i området, naturskogen verkar tydligen vara en viktig del i deras revir och hemvist.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10778,10 +10774,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121231790</v>
+        <v>121231715</v>
       </c>
       <c r="B96" t="n">
-        <v>57370</v>
+        <v>56559</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10794,16 +10790,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10813,18 +10809,14 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -10834,10 +10826,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>730862</v>
+        <v>730569</v>
       </c>
       <c r="R96" t="n">
-        <v>7280795</v>
+        <v>7281064</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10864,17 +10856,17 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>En adult hane på födosök i sitt revir dvs del av den.</t>
+          <t>En tupp och tre höns.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10901,10 +10893,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121231680</v>
+        <v>121231720</v>
       </c>
       <c r="B97" t="n">
-        <v>57465</v>
+        <v>57508</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10913,28 +10905,32 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
@@ -10949,10 +10945,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>730504</v>
+        <v>730749</v>
       </c>
       <c r="R97" t="n">
-        <v>7281155</v>
+        <v>7280849</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10989,7 +10985,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Familjgruppen som har tidigare observerats i området, naturskogen verkar tydligen vara en viktig del i deras revir och hemvist.</t>
+          <t>De sågs även tidigare i sitt revir. Revirparet och kvarvarande ungfåglar.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11016,10 +11012,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121231720</v>
+        <v>121231790</v>
       </c>
       <c r="B98" t="n">
-        <v>57507</v>
+        <v>57371</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11032,33 +11028,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -11068,10 +11068,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>730749</v>
+        <v>730862</v>
       </c>
       <c r="R98" t="n">
-        <v>7280849</v>
+        <v>7280795</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11098,17 +11098,17 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>De sågs även tidigare i sitt revir. Revirparet och kvarvarande ungfåglar.</t>
+          <t>En adult hane på födosök i sitt revir dvs del av den.</t>
         </is>
       </c>
       <c r="AD98" t="b">

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -10547,7 +10547,7 @@
         <v>121231798</v>
       </c>
       <c r="B94" t="n">
-        <v>57508</v>
+        <v>57509</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10659,10 +10659,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121231680</v>
+        <v>121231790</v>
       </c>
       <c r="B95" t="n">
-        <v>57466</v>
+        <v>57372</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10671,20 +10671,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -10692,12 +10692,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -10707,10 +10715,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>730504</v>
+        <v>730862</v>
       </c>
       <c r="R95" t="n">
-        <v>7281155</v>
+        <v>7280795</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10737,17 +10745,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Familjgruppen som har tidigare observerats i området, naturskogen verkar tydligen vara en viktig del i deras revir och hemvist.</t>
+          <t>En adult hane på födosök i sitt revir dvs del av den.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10774,10 +10782,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121231715</v>
+        <v>121231680</v>
       </c>
       <c r="B96" t="n">
-        <v>56559</v>
+        <v>57467</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10786,20 +10794,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>102612</v>
+        <v>103031</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10807,11 +10815,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
@@ -10826,10 +10830,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>730569</v>
+        <v>730504</v>
       </c>
       <c r="R96" t="n">
-        <v>7281064</v>
+        <v>7281155</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10866,7 +10870,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>En tupp och tre höns.</t>
+          <t>Familjgruppen som har tidigare observerats i området, naturskogen verkar tydligen vara en viktig del i deras revir och hemvist.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10893,10 +10897,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121231720</v>
+        <v>121231715</v>
       </c>
       <c r="B97" t="n">
-        <v>57508</v>
+        <v>56560</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10909,26 +10913,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -10945,10 +10949,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>730749</v>
+        <v>730569</v>
       </c>
       <c r="R97" t="n">
-        <v>7280849</v>
+        <v>7281064</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10985,7 +10989,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>De sågs även tidigare i sitt revir. Revirparet och kvarvarande ungfåglar.</t>
+          <t>En tupp och tre höns.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11012,10 +11016,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121231790</v>
+        <v>121231720</v>
       </c>
       <c r="B98" t="n">
-        <v>57371</v>
+        <v>57509</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11028,37 +11032,33 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -11068,10 +11068,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>730862</v>
+        <v>730749</v>
       </c>
       <c r="R98" t="n">
-        <v>7280795</v>
+        <v>7280849</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11098,17 +11098,17 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>En adult hane på födosök i sitt revir dvs del av den.</t>
+          <t>De sågs även tidigare i sitt revir. Revirparet och kvarvarande ungfåglar.</t>
         </is>
       </c>
       <c r="AD98" t="b">

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -10544,10 +10544,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121231798</v>
+        <v>121231680</v>
       </c>
       <c r="B94" t="n">
-        <v>57509</v>
+        <v>57467</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10556,25 +10556,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10582,7 +10582,7 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -10592,10 +10592,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>730872</v>
+        <v>730504</v>
       </c>
       <c r="R94" t="n">
-        <v>7280743</v>
+        <v>7281155</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10622,17 +10622,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Familjeflocken i sitt revir, dvs revirparet med kvarvarande ungfåglar.</t>
+          <t>Familjgruppen som har tidigare observerats i området, naturskogen verkar tydligen vara en viktig del i deras revir och hemvist.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10659,10 +10659,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121231790</v>
+        <v>121231798</v>
       </c>
       <c r="B95" t="n">
-        <v>57372</v>
+        <v>57509</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10675,33 +10675,25 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
@@ -10715,10 +10707,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>730862</v>
+        <v>730872</v>
       </c>
       <c r="R95" t="n">
-        <v>7280795</v>
+        <v>7280743</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10755,7 +10747,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>En adult hane på födosök i sitt revir dvs del av den.</t>
+          <t>Familjeflocken i sitt revir, dvs revirparet med kvarvarande ungfåglar.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10782,10 +10774,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121231680</v>
+        <v>121231715</v>
       </c>
       <c r="B96" t="n">
-        <v>57467</v>
+        <v>56560</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10794,20 +10786,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103031</v>
+        <v>102612</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10815,7 +10807,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
@@ -10830,10 +10826,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>730504</v>
+        <v>730569</v>
       </c>
       <c r="R96" t="n">
-        <v>7281155</v>
+        <v>7281064</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10870,7 +10866,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Familjgruppen som har tidigare observerats i området, naturskogen verkar tydligen vara en viktig del i deras revir och hemvist.</t>
+          <t>En tupp och tre höns.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10897,10 +10893,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121231715</v>
+        <v>121231790</v>
       </c>
       <c r="B97" t="n">
-        <v>56560</v>
+        <v>57372</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10913,16 +10909,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10932,14 +10928,18 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -10949,10 +10949,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>730569</v>
+        <v>730862</v>
       </c>
       <c r="R97" t="n">
-        <v>7281064</v>
+        <v>7280795</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10979,17 +10979,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>En tupp och tre höns.</t>
+          <t>En adult hane på födosök i sitt revir dvs del av den.</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -10544,10 +10544,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121231680</v>
+        <v>121231798</v>
       </c>
       <c r="B94" t="n">
-        <v>57467</v>
+        <v>57509</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10556,25 +10556,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10582,7 +10582,7 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -10592,10 +10592,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>730504</v>
+        <v>730872</v>
       </c>
       <c r="R94" t="n">
-        <v>7281155</v>
+        <v>7280743</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10622,17 +10622,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Familjgruppen som har tidigare observerats i området, naturskogen verkar tydligen vara en viktig del i deras revir och hemvist.</t>
+          <t>Familjeflocken i sitt revir, dvs revirparet med kvarvarande ungfåglar.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10659,10 +10659,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121231798</v>
+        <v>121231680</v>
       </c>
       <c r="B95" t="n">
-        <v>57509</v>
+        <v>57467</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10671,25 +10671,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10697,7 +10697,7 @@
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -10707,10 +10707,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>730872</v>
+        <v>730504</v>
       </c>
       <c r="R95" t="n">
-        <v>7280743</v>
+        <v>7281155</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10737,17 +10737,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Familjeflocken i sitt revir, dvs revirparet med kvarvarande ungfåglar.</t>
+          <t>Familjgruppen som har tidigare observerats i området, naturskogen verkar tydligen vara en viktig del i deras revir och hemvist.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10774,10 +10774,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121231715</v>
+        <v>121231790</v>
       </c>
       <c r="B96" t="n">
-        <v>56560</v>
+        <v>57372</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10790,16 +10790,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10809,14 +10809,18 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -10826,10 +10830,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>730569</v>
+        <v>730862</v>
       </c>
       <c r="R96" t="n">
-        <v>7281064</v>
+        <v>7280795</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10856,17 +10860,17 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>En tupp och tre höns.</t>
+          <t>En adult hane på födosök i sitt revir dvs del av den.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10893,10 +10897,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121231790</v>
+        <v>121231715</v>
       </c>
       <c r="B97" t="n">
-        <v>57372</v>
+        <v>56560</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10909,16 +10913,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10928,18 +10932,14 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -10949,10 +10949,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>730862</v>
+        <v>730569</v>
       </c>
       <c r="R97" t="n">
-        <v>7280795</v>
+        <v>7281064</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10979,17 +10979,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>En adult hane på födosök i sitt revir dvs del av den.</t>
+          <t>En tupp och tre höns.</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -7543,11 +7543,11 @@
         <v>120473485</v>
       </c>
       <c r="B66" t="n">
-        <v>57363</v>
+        <v>57400</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9362,11 +9362,11 @@
         <v>120470498</v>
       </c>
       <c r="B83" t="n">
-        <v>57363</v>
+        <v>57400</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -3227,11 +3227,11 @@
         <v>120473545</v>
       </c>
       <c r="B26" t="n">
-        <v>56559</v>
+        <v>56687</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -3227,7 +3227,7 @@
         <v>120473545</v>
       </c>
       <c r="B26" t="n">
-        <v>56687</v>
+        <v>56688</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>120473485</v>
       </c>
       <c r="B66" t="n">
-        <v>57400</v>
+        <v>57494</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>120470498</v>
       </c>
       <c r="B83" t="n">
-        <v>57400</v>
+        <v>57494</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -3227,7 +3227,7 @@
         <v>120473545</v>
       </c>
       <c r="B26" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY98"/>
+  <dimension ref="A1:AY102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11133,6 +11133,420 @@
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>127675443</v>
+      </c>
+      <c r="B99" t="n">
+        <v>97325</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Dubblabergen-Rörmyran , Pi lm</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>730788</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7280768</v>
+      </c>
+      <c r="S99" t="n">
+        <v>5</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>127675544</v>
+      </c>
+      <c r="B100" t="n">
+        <v>56853</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Dubblabergen-Rörmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>730893</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7280712</v>
+      </c>
+      <c r="S100" t="n">
+        <v>5</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>En höna med 4 vuxna kycklingar. Den dels försumpade ca 150 till 160 åriga naturskogsresten verkar vara ett viktig häcknings- och födoområde för tjäder.</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>127675440</v>
+      </c>
+      <c r="B101" t="n">
+        <v>91344</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Dubblabergen-Rörmyran , Pi lm</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>730788</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7280768</v>
+      </c>
+      <c r="S101" t="n">
+        <v>5</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>127675502</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79097</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>864</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Dubblabergen-Rörmyran , Pi lm</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>730812</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7280751</v>
+      </c>
+      <c r="S102" t="n">
+        <v>5</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -11138,7 +11138,7 @@
         <v>127675443</v>
       </c>
       <c r="B99" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>127675544</v>
       </c>
       <c r="B100" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>127675440</v>
       </c>
       <c r="B101" t="n">
-        <v>91344</v>
+        <v>91346</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>127675502</v>
       </c>
       <c r="B102" t="n">
-        <v>79097</v>
+        <v>79099</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -11138,7 +11138,7 @@
         <v>127675443</v>
       </c>
       <c r="B99" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>127675440</v>
       </c>
       <c r="B101" t="n">
-        <v>91346</v>
+        <v>91352</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -11138,7 +11138,7 @@
         <v>127675443</v>
       </c>
       <c r="B99" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>127675544</v>
       </c>
       <c r="B100" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>127675440</v>
       </c>
       <c r="B101" t="n">
-        <v>91352</v>
+        <v>91355</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>127675502</v>
       </c>
       <c r="B102" t="n">
-        <v>79099</v>
+        <v>79102</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -11138,7 +11138,7 @@
         <v>127675443</v>
       </c>
       <c r="B99" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>127675544</v>
       </c>
       <c r="B100" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>127675440</v>
       </c>
       <c r="B101" t="n">
-        <v>91355</v>
+        <v>91363</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>127675502</v>
       </c>
       <c r="B102" t="n">
-        <v>79102</v>
+        <v>79108</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -11138,7 +11138,7 @@
         <v>127675443</v>
       </c>
       <c r="B99" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>127675440</v>
       </c>
       <c r="B101" t="n">
-        <v>91363</v>
+        <v>91364</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY102"/>
+  <dimension ref="A1:AY104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11138,7 +11138,7 @@
         <v>127675443</v>
       </c>
       <c r="B99" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>127675440</v>
       </c>
       <c r="B101" t="n">
-        <v>91364</v>
+        <v>91365</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11547,6 +11547,231 @@
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>128256094</v>
+      </c>
+      <c r="B103" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Garpmesliden-Römyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>730780</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7280790</v>
+      </c>
+      <c r="S103" t="n">
+        <v>5</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Ett tiotal</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>128256204</v>
+      </c>
+      <c r="B104" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Garpmesliden-Römyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>730780</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7280790</v>
+      </c>
+      <c r="S104" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Revirparet inom sitt revir som utgörs av en långsmal naturskogsrest med olikåldrig och skitad skog. Området var tidigare klassad som naturvårdsskog av markägaren Sveaskog.</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -11138,7 +11138,7 @@
         <v>127675443</v>
       </c>
       <c r="B99" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>127675440</v>
       </c>
       <c r="B101" t="n">
-        <v>91365</v>
+        <v>91366</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -11138,7 +11138,7 @@
         <v>127675443</v>
       </c>
       <c r="B99" t="n">
-        <v>97347</v>
+        <v>97355</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>127675440</v>
       </c>
       <c r="B101" t="n">
-        <v>91366</v>
+        <v>91374</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>127675502</v>
       </c>
       <c r="B102" t="n">
-        <v>79108</v>
+        <v>79111</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>128256094</v>
       </c>
       <c r="B103" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>128256204</v>
       </c>
       <c r="B104" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -11552,7 +11552,7 @@
         <v>128256094</v>
       </c>
       <c r="B103" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>128256204</v>
       </c>
       <c r="B104" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -11552,7 +11552,7 @@
         <v>128256094</v>
       </c>
       <c r="B103" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>128256204</v>
       </c>
       <c r="B104" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -11552,7 +11552,7 @@
         <v>128256094</v>
       </c>
       <c r="B103" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -11552,7 +11552,7 @@
         <v>128256094</v>
       </c>
       <c r="B103" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -11552,7 +11552,7 @@
         <v>128256094</v>
       </c>
       <c r="B103" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -11552,7 +11552,7 @@
         <v>128256094</v>
       </c>
       <c r="B103" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>128256204</v>
       </c>
       <c r="B104" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -11552,7 +11552,7 @@
         <v>128256094</v>
       </c>
       <c r="B103" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -11240,7 +11240,7 @@
         <v>127675544</v>
       </c>
       <c r="B100" t="n">
-        <v>56864</v>
+        <v>57073</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -11774,10 +11774,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131217412</v>
+        <v>131217375</v>
       </c>
       <c r="B105" t="n">
-        <v>57064</v>
+        <v>58043</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11785,26 +11785,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -11821,10 +11821,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>730512</v>
+        <v>730627</v>
       </c>
       <c r="R105" t="n">
-        <v>7281151</v>
+        <v>7281017</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11851,17 +11851,17 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>En tupp och två höns som satt och plockade björkknoppar. Den dels försumpade kallbäckmiljön med sin gamla kontinuitetsskog är en optimal miljö för arten. Även på vintern hittar de födda i gammelskogen.</t>
+          <t>Revirparet</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11888,37 +11888,37 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131217375</v>
+        <v>131217371</v>
       </c>
       <c r="B106" t="n">
-        <v>58043</v>
+        <v>57988</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -11935,10 +11935,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>730627</v>
+        <v>730751</v>
       </c>
       <c r="R106" t="n">
-        <v>7281017</v>
+        <v>7280826</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11975,7 +11975,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Revirparet</t>
+          <t>En familjegrupp i sitt revir där det har gömt sina matförråd i de hänglavdrapperade gammelgranar så att dexklarar den bistra Lapplandvintern.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12002,27 +12002,27 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131217371</v>
+        <v>131217398</v>
       </c>
       <c r="B107" t="n">
-        <v>57988</v>
+        <v>57884</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -12032,11 +12032,19 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M107" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -12049,10 +12057,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>730751</v>
+        <v>730857</v>
       </c>
       <c r="R107" t="n">
-        <v>7280826</v>
+        <v>7280781</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12079,17 +12087,17 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>En familjegrupp i sitt revir där det har gömt sina matförråd i de hänglavdrapperade gammelgranar så att dexklarar den bistra Lapplandvintern.</t>
+          <t>Det noterades tidigare en revirmakerande hanne och typiska hackringar i området. Troligen samma hanne som har revir i den gamla ca 160 åriga kontinuitetsskogen.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12116,10 +12124,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131217398</v>
+        <v>131217412</v>
       </c>
       <c r="B108" t="n">
-        <v>57884</v>
+        <v>57064</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12127,16 +12135,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -12146,19 +12154,11 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -12171,10 +12171,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>730857</v>
+        <v>730512</v>
       </c>
       <c r="R108" t="n">
-        <v>7280781</v>
+        <v>7281151</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12201,17 +12201,17 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Det noterades tidigare en revirmakerande hanne och typiska hackringar i området. Troligen samma hanne som har revir i den gamla ca 160 åriga kontinuitetsskogen.</t>
+          <t>En tupp och två höns som satt och plockade björkknoppar. Den dels försumpade kallbäckmiljön med sin gamla kontinuitetsskog är en optimal miljö för arten. Även på vintern hittar de födda i gammelskogen.</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -12002,10 +12002,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131217398</v>
+        <v>131217412</v>
       </c>
       <c r="B107" t="n">
-        <v>57884</v>
+        <v>57064</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12013,16 +12013,16 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -12032,19 +12032,11 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -12057,10 +12049,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>730857</v>
+        <v>730512</v>
       </c>
       <c r="R107" t="n">
-        <v>7280781</v>
+        <v>7281151</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12087,17 +12079,17 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Det noterades tidigare en revirmakerande hanne och typiska hackringar i området. Troligen samma hanne som har revir i den gamla ca 160 åriga kontinuitetsskogen.</t>
+          <t>En tupp och två höns som satt och plockade björkknoppar. Den dels försumpade kallbäckmiljön med sin gamla kontinuitetsskog är en optimal miljö för arten. Även på vintern hittar de födda i gammelskogen.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12124,10 +12116,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131217412</v>
+        <v>131217398</v>
       </c>
       <c r="B108" t="n">
-        <v>57064</v>
+        <v>57884</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12135,16 +12127,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -12154,11 +12146,19 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M108" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -12171,10 +12171,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>730512</v>
+        <v>730857</v>
       </c>
       <c r="R108" t="n">
-        <v>7281151</v>
+        <v>7280781</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12201,17 +12201,17 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>En tupp och två höns som satt och plockade björkknoppar. Den dels försumpade kallbäckmiljön med sin gamla kontinuitetsskog är en optimal miljö för arten. Även på vintern hittar de födda i gammelskogen.</t>
+          <t>Det noterades tidigare en revirmakerande hanne och typiska hackringar i området. Troligen samma hanne som har revir i den gamla ca 160 åriga kontinuitetsskogen.</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -11240,7 +11240,7 @@
         <v>127675544</v>
       </c>
       <c r="B100" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>131217375</v>
       </c>
       <c r="B105" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         <v>131217371</v>
       </c>
       <c r="B106" t="n">
-        <v>57988</v>
+        <v>57990</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>131217412</v>
       </c>
       <c r="B107" t="n">
-        <v>57064</v>
+        <v>57066</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>131217398</v>
       </c>
       <c r="B108" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -11240,7 +11240,7 @@
         <v>127675544</v>
       </c>
       <c r="B100" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>131217375</v>
       </c>
       <c r="B105" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         <v>131217371</v>
       </c>
       <c r="B106" t="n">
-        <v>57990</v>
+        <v>57991</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>131217412</v>
       </c>
       <c r="B107" t="n">
-        <v>57066</v>
+        <v>57067</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>131217398</v>
       </c>
       <c r="B108" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -11777,7 +11777,7 @@
         <v>131217375</v>
       </c>
       <c r="B105" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         <v>131217371</v>
       </c>
       <c r="B106" t="n">
-        <v>57991</v>
+        <v>57992</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>131217398</v>
       </c>
       <c r="B108" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -11240,7 +11240,7 @@
         <v>127675544</v>
       </c>
       <c r="B100" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>131217375</v>
       </c>
       <c r="B105" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         <v>131217371</v>
       </c>
       <c r="B106" t="n">
-        <v>57992</v>
+        <v>57995</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>131217412</v>
       </c>
       <c r="B107" t="n">
-        <v>57067</v>
+        <v>57070</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>131217398</v>
       </c>
       <c r="B108" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -11240,7 +11240,7 @@
         <v>127675544</v>
       </c>
       <c r="B100" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>131217375</v>
       </c>
       <c r="B105" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         <v>131217371</v>
       </c>
       <c r="B106" t="n">
-        <v>57995</v>
+        <v>57996</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>131217412</v>
       </c>
       <c r="B107" t="n">
-        <v>57070</v>
+        <v>57071</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>131217398</v>
       </c>
       <c r="B108" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY108"/>
+  <dimension ref="A1:AY129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>120470748</v>
       </c>
       <c r="B2" t="n">
-        <v>78627</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120470888</v>
+        <v>120470755</v>
       </c>
       <c r="B3" t="n">
-        <v>78627</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,14 +810,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran , Pi lm</t>
+          <t>Garpmesliden-Römyran, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730611</v>
+        <v>730654</v>
       </c>
       <c r="R3" t="n">
-        <v>7281039</v>
+        <v>7280928</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120473423</v>
+        <v>120470789</v>
       </c>
       <c r="B4" t="n">
-        <v>78627</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730869</v>
+        <v>730676</v>
       </c>
       <c r="R4" t="n">
-        <v>7280766</v>
+        <v>7280903</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -960,12 +945,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120470614</v>
+        <v>120470825</v>
       </c>
       <c r="B5" t="n">
-        <v>56551</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,27 +989,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730776</v>
+        <v>730640</v>
       </c>
       <c r="R5" t="n">
-        <v>7280790</v>
+        <v>7280934</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1081,6 +1060,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1099,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120473226</v>
+        <v>120470888</v>
       </c>
       <c r="B6" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,14 +1113,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran, Pi lm</t>
+          <t>Garpmesliden-Römyran , Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730876</v>
+        <v>730611</v>
       </c>
       <c r="R6" t="n">
-        <v>7280720</v>
+        <v>7281039</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1172,12 +1147,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120470957</v>
+        <v>120470896</v>
       </c>
       <c r="B7" t="n">
-        <v>82377</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730533</v>
+        <v>730587</v>
       </c>
       <c r="R7" t="n">
-        <v>7281130</v>
+        <v>7281038</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120473444</v>
+        <v>120470915</v>
       </c>
       <c r="B8" t="n">
-        <v>82377</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730845</v>
+        <v>730563</v>
       </c>
       <c r="R8" t="n">
-        <v>7280809</v>
+        <v>7281056</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1384,12 +1349,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,43 +1382,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120470812</v>
+        <v>120470945</v>
       </c>
       <c r="B9" t="n">
-        <v>98066</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1461,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730676</v>
+        <v>730551</v>
       </c>
       <c r="R9" t="n">
-        <v>7280903</v>
+        <v>7281090</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1524,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120473694</v>
+        <v>120470997</v>
       </c>
       <c r="B10" t="n">
-        <v>57363</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1540,31 +1494,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1572,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730832</v>
+        <v>730452</v>
       </c>
       <c r="R10" t="n">
-        <v>7280746</v>
+        <v>7281226</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1602,12 +1551,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1616,6 +1565,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1634,15 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120470620</v>
+        <v>120473140</v>
       </c>
       <c r="B11" t="n">
-        <v>82377</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,21 +1595,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1677,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>730781</v>
+        <v>730799</v>
       </c>
       <c r="R11" t="n">
-        <v>7280800</v>
+        <v>7280750</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1707,12 +1652,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,15 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120473413</v>
+        <v>120473423</v>
       </c>
       <c r="B12" t="n">
-        <v>82377</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1783,10 +1723,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730907</v>
+        <v>730869</v>
       </c>
       <c r="R12" t="n">
-        <v>7280757</v>
+        <v>7280766</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1846,37 +1786,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120473547</v>
+        <v>120473492</v>
       </c>
       <c r="B13" t="n">
-        <v>91950</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1889,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730894</v>
+        <v>730912</v>
       </c>
       <c r="R13" t="n">
-        <v>7280702</v>
+        <v>7280701</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1952,15 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120473571</v>
+        <v>120473565</v>
       </c>
       <c r="B14" t="n">
-        <v>90600</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,21 +1898,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3242</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2058,15 +1988,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120470546</v>
+        <v>120473697</v>
       </c>
       <c r="B15" t="n">
-        <v>78675</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2074,21 +1999,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730856</v>
+        <v>730832</v>
       </c>
       <c r="R15" t="n">
-        <v>7280769</v>
+        <v>7280746</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2131,12 +2056,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2164,37 +2089,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120473129</v>
+        <v>120473592</v>
       </c>
       <c r="B16" t="n">
-        <v>90688</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83304</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2207,10 +2127,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730789</v>
+        <v>730891</v>
       </c>
       <c r="R16" t="n">
-        <v>7280765</v>
+        <v>7280715</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2270,37 +2190,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120473775</v>
+        <v>120470955</v>
       </c>
       <c r="B17" t="n">
-        <v>78675</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2313,10 +2228,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730816</v>
+        <v>730533</v>
       </c>
       <c r="R17" t="n">
-        <v>7280822</v>
+        <v>7281130</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2343,12 +2258,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2376,37 +2291,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120473808</v>
+        <v>120473450</v>
       </c>
       <c r="B18" t="n">
-        <v>78675</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2419,10 +2329,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730795</v>
+        <v>730869</v>
       </c>
       <c r="R18" t="n">
-        <v>7280824</v>
+        <v>7280791</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2482,15 +2392,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120470872</v>
+        <v>120470475</v>
       </c>
       <c r="B19" t="n">
-        <v>82377</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,21 +2403,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2525,10 +2430,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>730630</v>
+        <v>730827</v>
       </c>
       <c r="R19" t="n">
-        <v>7280999</v>
+        <v>7280751</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2588,15 +2493,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120470739</v>
+        <v>120470546</v>
       </c>
       <c r="B20" t="n">
-        <v>78593</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2604,21 +2504,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2631,10 +2531,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730717</v>
+        <v>730856</v>
       </c>
       <c r="R20" t="n">
-        <v>7280872</v>
+        <v>7280769</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2694,15 +2594,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120473143</v>
+        <v>120470659</v>
       </c>
       <c r="B21" t="n">
-        <v>82377</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2710,21 +2605,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2737,10 +2632,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>730799</v>
+        <v>730744</v>
       </c>
       <c r="R21" t="n">
-        <v>7280750</v>
+        <v>7280840</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2767,12 +2662,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,15 +2695,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120473606</v>
+        <v>120470701</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2816,21 +2706,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2843,10 +2733,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730869</v>
+        <v>730729</v>
       </c>
       <c r="R22" t="n">
-        <v>7280698</v>
+        <v>7280851</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2873,12 +2763,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2906,15 +2796,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120470967</v>
+        <v>120473156</v>
       </c>
       <c r="B23" t="n">
-        <v>78593</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2922,21 +2807,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2949,10 +2834,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730499</v>
+        <v>730803</v>
       </c>
       <c r="R23" t="n">
-        <v>7281166</v>
+        <v>7280729</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2979,12 +2864,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3012,15 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120473443</v>
+        <v>120473410</v>
       </c>
       <c r="B24" t="n">
-        <v>78675</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3055,10 +2935,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>730845</v>
+        <v>730907</v>
       </c>
       <c r="R24" t="n">
-        <v>7280809</v>
+        <v>7280757</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3118,15 +2998,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120470896</v>
+        <v>120473443</v>
       </c>
       <c r="B25" t="n">
-        <v>78627</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3134,21 +3009,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3036,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>730587</v>
+        <v>730845</v>
       </c>
       <c r="R25" t="n">
-        <v>7281038</v>
+        <v>7280809</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3191,12 +3066,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3224,51 +3099,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120473545</v>
+        <v>120473472</v>
       </c>
       <c r="B26" t="n">
-        <v>56691</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3276,10 +3137,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730894</v>
+        <v>730920</v>
       </c>
       <c r="R26" t="n">
-        <v>7280702</v>
+        <v>7280729</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3314,17 +3175,13 @@
           <t>2024-08-15</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Env höna med sina nästan utvuxna kycklingar på födosök i häckningsområdet.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3343,43 +3200,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120470646</v>
+        <v>120473754</v>
       </c>
       <c r="B27" t="n">
-        <v>96999</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>864</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3387,10 +3238,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730765</v>
+        <v>730833</v>
       </c>
       <c r="R27" t="n">
-        <v>7280814</v>
+        <v>7280805</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3417,12 +3268,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3450,43 +3301,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120470617</v>
+        <v>120473775</v>
       </c>
       <c r="B28" t="n">
-        <v>96999</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3494,10 +3339,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730776</v>
+        <v>730816</v>
       </c>
       <c r="R28" t="n">
-        <v>7280790</v>
+        <v>7280822</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3524,12 +3369,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3557,43 +3402,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120473201</v>
+        <v>120473808</v>
       </c>
       <c r="B29" t="n">
-        <v>97005</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221941</v>
+        <v>864</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3601,10 +3440,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730852</v>
+        <v>730795</v>
       </c>
       <c r="R29" t="n">
-        <v>7280740</v>
+        <v>7280824</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3664,15 +3503,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120473699</v>
+        <v>120473837</v>
       </c>
       <c r="B30" t="n">
-        <v>89734</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3680,21 +3514,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1962</v>
+        <v>864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3707,10 +3541,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730844</v>
+        <v>730743</v>
       </c>
       <c r="R30" t="n">
-        <v>7280770</v>
+        <v>7280839</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3770,15 +3604,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120470940</v>
+        <v>127675502</v>
       </c>
       <c r="B31" t="n">
-        <v>82377</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3786,21 +3615,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3809,14 +3638,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran, Pi lm</t>
+          <t>Dubblabergen-Rörmyran , Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730551</v>
+        <v>730812</v>
       </c>
       <c r="R31" t="n">
-        <v>7281090</v>
+        <v>7280751</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3843,12 +3672,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3876,37 +3705,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120473217</v>
+        <v>120470679</v>
       </c>
       <c r="B32" t="n">
-        <v>79211</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3919,10 +3743,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730876</v>
+        <v>730729</v>
       </c>
       <c r="R32" t="n">
-        <v>7280720</v>
+        <v>7280851</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3949,12 +3773,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3982,37 +3806,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120473572</v>
+        <v>120470914</v>
       </c>
       <c r="B33" t="n">
-        <v>77525</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6487</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4025,10 +3844,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>730891</v>
+        <v>730563</v>
       </c>
       <c r="R33" t="n">
-        <v>7280715</v>
+        <v>7281056</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4055,12 +3874,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4088,37 +3907,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120473492</v>
+        <v>120473129</v>
       </c>
       <c r="B34" t="n">
-        <v>78627</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4131,10 +3945,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730912</v>
+        <v>730789</v>
       </c>
       <c r="R34" t="n">
-        <v>7280701</v>
+        <v>7280765</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4194,37 +4008,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120470909</v>
+        <v>127675440</v>
       </c>
       <c r="B35" t="n">
-        <v>78593</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4233,14 +4042,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran, Pi lm</t>
+          <t>Dubblabergen-Rörmyran , Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730587</v>
+        <v>730788</v>
       </c>
       <c r="R35" t="n">
-        <v>7281038</v>
+        <v>7280768</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4267,12 +4076,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4300,15 +4109,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120470867</v>
+        <v>120470478</v>
       </c>
       <c r="B36" t="n">
-        <v>78593</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4316,21 +4120,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4343,10 +4147,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730630</v>
+        <v>730827</v>
       </c>
       <c r="R36" t="n">
-        <v>7280999</v>
+        <v>7280751</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4406,15 +4210,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120470915</v>
+        <v>120470620</v>
       </c>
       <c r="B37" t="n">
-        <v>78627</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4422,21 +4221,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4449,10 +4248,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730563</v>
+        <v>730781</v>
       </c>
       <c r="R37" t="n">
-        <v>7281056</v>
+        <v>7280800</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4512,37 +4311,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120470795</v>
+        <v>120470651</v>
       </c>
       <c r="B38" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4555,10 +4349,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730676</v>
+        <v>730744</v>
       </c>
       <c r="R38" t="n">
-        <v>7280903</v>
+        <v>7280825</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4618,15 +4412,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120473156</v>
+        <v>120470655</v>
       </c>
       <c r="B39" t="n">
-        <v>78675</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4634,21 +4423,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4661,10 +4450,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730803</v>
+        <v>730744</v>
       </c>
       <c r="R39" t="n">
-        <v>7280729</v>
+        <v>7280840</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4691,12 +4480,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4724,15 +4513,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120473635</v>
+        <v>120470705</v>
       </c>
       <c r="B40" t="n">
-        <v>79182</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4740,21 +4524,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4767,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>730880</v>
+        <v>730729</v>
       </c>
       <c r="R40" t="n">
-        <v>7280720</v>
+        <v>7280851</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4797,12 +4581,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4830,15 +4614,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120473475</v>
+        <v>120470733</v>
       </c>
       <c r="B41" t="n">
-        <v>82377</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4873,10 +4652,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730920</v>
+        <v>730717</v>
       </c>
       <c r="R41" t="n">
-        <v>7280729</v>
+        <v>7280872</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4903,12 +4682,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4936,15 +4715,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120470945</v>
+        <v>120470762</v>
       </c>
       <c r="B42" t="n">
-        <v>78627</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4952,21 +4726,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4979,10 +4753,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730551</v>
+        <v>730654</v>
       </c>
       <c r="R42" t="n">
-        <v>7281090</v>
+        <v>7280928</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5042,15 +4816,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120470890</v>
+        <v>120470820</v>
       </c>
       <c r="B43" t="n">
-        <v>82377</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5081,14 +4850,14 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran , Pi lm</t>
+          <t>Garpmesliden-Römyran, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>730611</v>
+        <v>730640</v>
       </c>
       <c r="R43" t="n">
-        <v>7281039</v>
+        <v>7280934</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5148,15 +4917,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120473713</v>
+        <v>120470845</v>
       </c>
       <c r="B44" t="n">
-        <v>78593</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5164,21 +4928,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5191,10 +4955,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>730844</v>
+        <v>730628</v>
       </c>
       <c r="R44" t="n">
-        <v>7280770</v>
+        <v>7280944</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5221,12 +4985,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5254,51 +5018,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120473397</v>
+        <v>120470853</v>
       </c>
       <c r="B45" t="n">
-        <v>57458</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103031</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5306,10 +5056,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>730897</v>
+        <v>730639</v>
       </c>
       <c r="R45" t="n">
-        <v>7280732</v>
+        <v>7280973</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5336,17 +5086,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>En familjgrupp i sitt revir. Det är gruppen som håller till kring Kikkejaureberget/Tjitterberget men mycket av deras revir och hemvist i naturskogsresterna har undan för undan avverkats trots miljölöften av statliga Sveaskog. Även aktuell fyndplats i naturskogsrestfragment är planerad för kalavverkning och markberedning!</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5355,6 +5100,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5373,15 +5119,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120473421</v>
+        <v>120470872</v>
       </c>
       <c r="B46" t="n">
-        <v>78593</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5389,21 +5130,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5416,10 +5157,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>730869</v>
+        <v>730630</v>
       </c>
       <c r="R46" t="n">
-        <v>7280766</v>
+        <v>7280999</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5446,12 +5187,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5479,15 +5220,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120470889</v>
+        <v>120470890</v>
       </c>
       <c r="B47" t="n">
-        <v>78593</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5495,21 +5231,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5585,15 +5321,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120470475</v>
+        <v>120470935</v>
       </c>
       <c r="B48" t="n">
-        <v>78675</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5601,21 +5332,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5628,10 +5359,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>730827</v>
+        <v>730544</v>
       </c>
       <c r="R48" t="n">
-        <v>7280751</v>
+        <v>7281102</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5691,59 +5422,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120470931</v>
+        <v>120470940</v>
       </c>
       <c r="B49" t="n">
-        <v>56559</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5751,10 +5460,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>730544</v>
+        <v>730551</v>
       </c>
       <c r="R49" t="n">
-        <v>7281102</v>
+        <v>7281090</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5795,6 +5504,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5813,15 +5523,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120473807</v>
+        <v>120470957</v>
       </c>
       <c r="B50" t="n">
-        <v>57500</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5829,35 +5534,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>revir, ej häckning</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5865,10 +5561,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>730795</v>
+        <v>730533</v>
       </c>
       <c r="R50" t="n">
-        <v>7280824</v>
+        <v>7281130</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5895,17 +5591,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ett par med årets ungar i parets hemvist och häckningsrevir</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5914,6 +5605,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5932,43 +5624,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120470964</v>
+        <v>120473143</v>
       </c>
       <c r="B51" t="n">
-        <v>98066</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5976,10 +5662,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>730499</v>
+        <v>730799</v>
       </c>
       <c r="R51" t="n">
-        <v>7281141</v>
+        <v>7280750</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6006,12 +5692,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6042,12 +5728,7 @@
         <v>120473148</v>
       </c>
       <c r="B52" t="n">
-        <v>82377</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6145,15 +5826,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120473410</v>
+        <v>120473413</v>
       </c>
       <c r="B53" t="n">
-        <v>78675</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6161,21 +5837,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6251,15 +5927,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120470478</v>
+        <v>120473420</v>
       </c>
       <c r="B54" t="n">
-        <v>82377</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6294,10 +5965,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>730827</v>
+        <v>730869</v>
       </c>
       <c r="R54" t="n">
-        <v>7280751</v>
+        <v>7280766</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6324,12 +5995,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6357,15 +6028,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120473563</v>
+        <v>120473444</v>
       </c>
       <c r="B55" t="n">
-        <v>56551</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6373,35 +6039,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6409,10 +6066,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>730915</v>
+        <v>730845</v>
       </c>
       <c r="R55" t="n">
-        <v>7280682</v>
+        <v>7280809</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6447,17 +6104,13 @@
           <t>2024-08-15</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>3 järpar i sin hemvist i den fuktiga gamla barrnaturskogen med sumpskogskaraktär som är planerad för kalhuggning och markberedning.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6476,37 +6129,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120473450</v>
+        <v>120473467</v>
       </c>
       <c r="B56" t="n">
-        <v>77934</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>498</v>
+        <v>1312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6519,10 +6167,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>730869</v>
+        <v>730894</v>
       </c>
       <c r="R56" t="n">
-        <v>7280791</v>
+        <v>7280757</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6582,15 +6230,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120473565</v>
+        <v>120473475</v>
       </c>
       <c r="B57" t="n">
-        <v>78627</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6598,21 +6241,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6625,10 +6268,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>730915</v>
+        <v>730920</v>
       </c>
       <c r="R57" t="n">
-        <v>7280682</v>
+        <v>7280729</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6691,12 +6334,7 @@
         <v>120473746</v>
       </c>
       <c r="B58" t="n">
-        <v>82377</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6794,54 +6432,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120470809</v>
+        <v>127675384</v>
       </c>
       <c r="B59" t="n">
-        <v>96999</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran, Pi lm</t>
+          <t>Dubblabergen-Rörmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>730676</v>
+        <v>730716</v>
       </c>
       <c r="R59" t="n">
-        <v>7280903</v>
+        <v>7280832</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6868,12 +6500,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6901,54 +6533,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120473159</v>
+        <v>127675459</v>
       </c>
       <c r="B60" t="n">
-        <v>96999</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran, Pi lm</t>
+          <t>Dubblabergen-Rörmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>730803</v>
+        <v>730787</v>
       </c>
       <c r="R60" t="n">
-        <v>7280729</v>
+        <v>7280750</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6975,12 +6601,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7008,15 +6634,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120473462</v>
+        <v>120473699</v>
       </c>
       <c r="B61" t="n">
-        <v>78593</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7024,21 +6645,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7051,10 +6672,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>730869</v>
+        <v>730844</v>
       </c>
       <c r="R61" t="n">
-        <v>7280791</v>
+        <v>7280770</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7114,15 +6735,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120473750</v>
+        <v>120473571</v>
       </c>
       <c r="B62" t="n">
-        <v>78593</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7130,21 +6746,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7157,10 +6773,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>730814</v>
+        <v>730915</v>
       </c>
       <c r="R62" t="n">
-        <v>7280788</v>
+        <v>7280682</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7220,43 +6836,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120473835</v>
+        <v>120473547</v>
       </c>
       <c r="B63" t="n">
-        <v>98066</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7264,10 +6874,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>730783</v>
+        <v>730894</v>
       </c>
       <c r="R63" t="n">
-        <v>7280820</v>
+        <v>7280702</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7327,15 +6937,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120473132</v>
+        <v>120470697</v>
       </c>
       <c r="B64" t="n">
-        <v>96999</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7343,27 +6948,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7371,10 +6975,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>730789</v>
+        <v>730729</v>
       </c>
       <c r="R64" t="n">
-        <v>7280765</v>
+        <v>7280851</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7401,12 +7005,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7434,37 +7038,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120470655</v>
+        <v>120470795</v>
       </c>
       <c r="B65" t="n">
-        <v>82377</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7477,10 +7076,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>730744</v>
+        <v>730676</v>
       </c>
       <c r="R65" t="n">
-        <v>7280840</v>
+        <v>7280903</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7540,59 +7139,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120473485</v>
+        <v>120473226</v>
       </c>
       <c r="B66" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7600,10 +7177,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>730938</v>
+        <v>730876</v>
       </c>
       <c r="R66" t="n">
-        <v>7280716</v>
+        <v>7280720</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7644,6 +7221,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7662,37 +7240,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120470789</v>
+        <v>127675482</v>
       </c>
       <c r="B67" t="n">
-        <v>78627</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7701,14 +7274,14 @@
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran, Pi lm</t>
+          <t>Dubblabergen-Rörmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>730676</v>
+        <v>730787</v>
       </c>
       <c r="R67" t="n">
-        <v>7280903</v>
+        <v>7280750</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7735,12 +7308,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7768,37 +7341,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120470733</v>
+        <v>120470674</v>
       </c>
       <c r="B68" t="n">
-        <v>82377</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7811,10 +7379,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>730717</v>
+        <v>730729</v>
       </c>
       <c r="R68" t="n">
-        <v>7280872</v>
+        <v>7280851</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7874,37 +7442,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120473467</v>
+        <v>120470739</v>
       </c>
       <c r="B69" t="n">
-        <v>82377</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7917,10 +7480,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>730894</v>
+        <v>730717</v>
       </c>
       <c r="R69" t="n">
-        <v>7280757</v>
+        <v>7280872</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7947,12 +7510,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7980,37 +7543,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120473837</v>
+        <v>120470828</v>
       </c>
       <c r="B70" t="n">
-        <v>78675</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8023,10 +7581,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>730743</v>
+        <v>730640</v>
       </c>
       <c r="R70" t="n">
-        <v>7280839</v>
+        <v>7280934</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8053,12 +7611,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8086,19 +7644,14 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120473756</v>
+        <v>120470858</v>
       </c>
       <c r="B71" t="n">
-        <v>78593</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -8129,10 +7682,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>730833</v>
+        <v>730638</v>
       </c>
       <c r="R71" t="n">
-        <v>7280805</v>
+        <v>7280995</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8159,12 +7712,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8192,37 +7745,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120470853</v>
+        <v>120470867</v>
       </c>
       <c r="B72" t="n">
-        <v>82377</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8235,10 +7783,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>730639</v>
+        <v>730630</v>
       </c>
       <c r="R72" t="n">
-        <v>7280973</v>
+        <v>7280999</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8298,19 +7846,14 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120470858</v>
+        <v>120470889</v>
       </c>
       <c r="B73" t="n">
-        <v>78593</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -8337,14 +7880,14 @@
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran, Pi lm</t>
+          <t>Garpmesliden-Römyran , Pi lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>730638</v>
+        <v>730611</v>
       </c>
       <c r="R73" t="n">
-        <v>7280995</v>
+        <v>7281039</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8404,37 +7947,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120473626</v>
+        <v>120470909</v>
       </c>
       <c r="B74" t="n">
-        <v>79211</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8447,10 +7985,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>730880</v>
+        <v>730587</v>
       </c>
       <c r="R74" t="n">
-        <v>7280720</v>
+        <v>7281038</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8477,12 +8015,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8510,37 +8048,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120470659</v>
+        <v>120470942</v>
       </c>
       <c r="B75" t="n">
-        <v>78675</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8553,10 +8086,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>730744</v>
+        <v>730551</v>
       </c>
       <c r="R75" t="n">
-        <v>7280840</v>
+        <v>7281090</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8616,37 +8149,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120473140</v>
+        <v>120470967</v>
       </c>
       <c r="B76" t="n">
-        <v>78627</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8659,10 +8187,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>730799</v>
+        <v>730499</v>
       </c>
       <c r="R76" t="n">
-        <v>7280750</v>
+        <v>7281166</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8689,12 +8217,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8722,37 +8250,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120473420</v>
+        <v>120473407</v>
       </c>
       <c r="B77" t="n">
-        <v>82377</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8765,10 +8288,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>730869</v>
+        <v>730907</v>
       </c>
       <c r="R77" t="n">
-        <v>7280766</v>
+        <v>7280757</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8828,37 +8351,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120470914</v>
+        <v>120473421</v>
       </c>
       <c r="B78" t="n">
-        <v>90688</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8871,10 +8389,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>730563</v>
+        <v>730869</v>
       </c>
       <c r="R78" t="n">
-        <v>7281056</v>
+        <v>7280766</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8901,12 +8419,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8934,43 +8452,37 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120470660</v>
+        <v>120473462</v>
       </c>
       <c r="B79" t="n">
-        <v>96999</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -8978,10 +8490,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>730744</v>
+        <v>730869</v>
       </c>
       <c r="R79" t="n">
-        <v>7280840</v>
+        <v>7280791</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9008,12 +8520,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9041,37 +8553,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120473697</v>
+        <v>120473713</v>
       </c>
       <c r="B80" t="n">
-        <v>78627</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9084,10 +8591,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>730832</v>
+        <v>730844</v>
       </c>
       <c r="R80" t="n">
-        <v>7280746</v>
+        <v>7280770</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9147,37 +8654,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120470935</v>
+        <v>120473750</v>
       </c>
       <c r="B81" t="n">
-        <v>82377</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9190,10 +8692,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>730544</v>
+        <v>730814</v>
       </c>
       <c r="R81" t="n">
-        <v>7281102</v>
+        <v>7280788</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9220,12 +8722,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9253,19 +8755,14 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120473407</v>
+        <v>120473756</v>
       </c>
       <c r="B82" t="n">
-        <v>78593</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -9296,10 +8793,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>730907</v>
+        <v>730833</v>
       </c>
       <c r="R82" t="n">
-        <v>7280757</v>
+        <v>7280805</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9359,70 +8856,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120470498</v>
+        <v>127675388</v>
       </c>
       <c r="B83" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran, Pi lm</t>
+          <t>Dubblabergen-Rörmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>730827</v>
+        <v>730716</v>
       </c>
       <c r="R83" t="n">
-        <v>7280751</v>
+        <v>7280832</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9449,12 +8924,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9463,6 +8938,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9481,15 +8957,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120470997</v>
+        <v>120470607</v>
       </c>
       <c r="B84" t="n">
-        <v>78627</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9497,21 +8968,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9524,10 +8995,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>730452</v>
+        <v>730851</v>
       </c>
       <c r="R84" t="n">
-        <v>7281226</v>
+        <v>7280828</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9587,15 +9058,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120473754</v>
+        <v>120473194</v>
       </c>
       <c r="B85" t="n">
-        <v>78675</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9603,21 +9069,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9630,10 +9096,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>730833</v>
+        <v>730852</v>
       </c>
       <c r="R85" t="n">
-        <v>7280805</v>
+        <v>7280740</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9693,15 +9159,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120473194</v>
+        <v>120473217</v>
       </c>
       <c r="B86" t="n">
-        <v>79211</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9736,10 +9197,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>730852</v>
+        <v>730876</v>
       </c>
       <c r="R86" t="n">
-        <v>7280740</v>
+        <v>7280720</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9799,37 +9260,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120473592</v>
+        <v>120473606</v>
       </c>
       <c r="B87" t="n">
-        <v>74698</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>311</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9842,10 +9298,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>730891</v>
+        <v>730869</v>
       </c>
       <c r="R87" t="n">
-        <v>7280715</v>
+        <v>7280698</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9905,15 +9361,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120473472</v>
+        <v>120473626</v>
       </c>
       <c r="B88" t="n">
-        <v>78675</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9921,21 +9372,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9948,10 +9399,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>730920</v>
+        <v>730880</v>
       </c>
       <c r="R88" t="n">
-        <v>7280729</v>
+        <v>7280720</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10011,15 +9462,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120470955</v>
+        <v>120473572</v>
       </c>
       <c r="B89" t="n">
-        <v>77540</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10027,21 +9473,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>314</v>
+        <v>6487</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10054,10 +9500,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>730533</v>
+        <v>730891</v>
       </c>
       <c r="R89" t="n">
-        <v>7281130</v>
+        <v>7280715</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10084,12 +9530,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10117,15 +9563,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120470622</v>
+        <v>120470498</v>
       </c>
       <c r="B90" t="n">
-        <v>96999</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10133,27 +9574,43 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10161,10 +9618,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>730781</v>
+        <v>730827</v>
       </c>
       <c r="R90" t="n">
-        <v>7280800</v>
+        <v>7280751</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10205,7 +9662,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -10224,15 +9680,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120470887</v>
+        <v>120473485</v>
       </c>
       <c r="B91" t="n">
-        <v>96999</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10240,27 +9691,43 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10268,10 +9735,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>730622</v>
+        <v>730938</v>
       </c>
       <c r="R91" t="n">
-        <v>7281028</v>
+        <v>7280716</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10298,12 +9765,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10312,7 +9779,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10331,15 +9797,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120470917</v>
+        <v>120473694</v>
       </c>
       <c r="B92" t="n">
-        <v>96999</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10347,27 +9808,31 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -10375,10 +9840,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>730563</v>
+        <v>730832</v>
       </c>
       <c r="R92" t="n">
-        <v>7281056</v>
+        <v>7280746</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10405,12 +9870,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10419,7 +9884,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10438,42 +9902,50 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120470942</v>
+        <v>121231790</v>
       </c>
       <c r="B93" t="n">
-        <v>78593</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -10481,10 +9953,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>730551</v>
+        <v>730862</v>
       </c>
       <c r="R93" t="n">
-        <v>7281090</v>
+        <v>7280795</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10511,12 +9983,17 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>En adult hane på födosök i sitt revir dvs del av den.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10525,7 +10002,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10544,15 +10020,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121231798</v>
+        <v>127675337</v>
       </c>
       <c r="B94" t="n">
-        <v>57509</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10560,42 +10031,54 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran, Pi lm</t>
+          <t>Dubblabergen-Rörmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>730872</v>
+        <v>730691</v>
       </c>
       <c r="R94" t="n">
-        <v>7280743</v>
+        <v>7280875</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10622,17 +10105,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Familjeflocken i sitt revir, dvs revirparet med kvarvarande ungfåglar.</t>
+          <t>En hane som höll på med ringhack på en gran. Ringhack är efter min över 30 åriga erfarenhet troligen ett sätt att markera reviret och inte för att dricka sav! Att suga sav ur en tall eller gran ger snarare kåda än sav och på björk brukar min inte se den tretåiga hackspettens göra hackringar. Sedan räcker det med enstaka hack om den verkligen skulle dricka sav så som större hackspett och gråspett ibland gör på björk.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10659,32 +10142,27 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121231680</v>
+        <v>131217398</v>
       </c>
       <c r="B95" t="n">
-        <v>57467</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -10692,9 +10170,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M95" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -10707,13 +10197,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>730504</v>
+        <v>730857</v>
       </c>
       <c r="R95" t="n">
-        <v>7281155</v>
+        <v>7280781</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10737,17 +10227,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Familjgruppen som har tidigare observerats i området, naturskogen verkar tydligen vara en viktig del i deras revir och hemvist.</t>
+          <t>Det noterades tidigare en revirmakerande hanne och typiska hackringar i området. Troligen samma hanne som har revir i den gamla ca 160 åriga kontinuitetsskogen.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10774,37 +10264,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121231790</v>
+        <v>120470931</v>
       </c>
       <c r="B96" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -10817,7 +10302,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M96" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -10830,10 +10319,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>730862</v>
+        <v>730544</v>
       </c>
       <c r="R96" t="n">
-        <v>7280795</v>
+        <v>7281102</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10860,17 +10349,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>En adult hane på födosök i sitt revir dvs del av den.</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10897,37 +10381,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121231715</v>
+        <v>120473545</v>
       </c>
       <c r="B97" t="n">
-        <v>56560</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -10939,7 +10418,7 @@
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -10949,10 +10428,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>730569</v>
+        <v>730894</v>
       </c>
       <c r="R97" t="n">
-        <v>7281064</v>
+        <v>7280702</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10979,17 +10458,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>En tupp och tre höns.</t>
+          <t>Env höna med sina nästan utvuxna kycklingar på födosök i häckningsområdet.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11016,62 +10495,53 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121231720</v>
+        <v>127675544</v>
       </c>
       <c r="B98" t="n">
-        <v>57509</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran, Pi lm</t>
+          <t>Dubblabergen-Rörmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>730749</v>
+        <v>730893</v>
       </c>
       <c r="R98" t="n">
-        <v>7280849</v>
+        <v>7280712</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11098,17 +10568,17 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>De sågs även tidigare i sitt revir. Revirparet och kvarvarande ungfåglar.</t>
+          <t>En höna med 4 vuxna kycklingar. Den dels försumpade ca 150 till 160 åriga naturskogsresten verkar vara ett viktig häcknings- och födoområde för tjäder.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11135,10 +10605,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127675443</v>
+        <v>120470614</v>
       </c>
       <c r="B99" t="n">
-        <v>97355</v>
+        <v>57132</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11146,38 +10616,38 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Dubblabergen-Rörmyran , Pi lm</t>
+          <t>Garpmesliden-Römyran, Pi lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>730788</v>
+        <v>730776</v>
       </c>
       <c r="R99" t="n">
-        <v>7280768</v>
+        <v>7280790</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11204,12 +10674,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11218,7 +10688,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11237,10 +10706,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127675544</v>
+        <v>120473563</v>
       </c>
       <c r="B100" t="n">
-        <v>57092</v>
+        <v>57132</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11248,42 +10717,46 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Dubblabergen-Rörmyran, Pi lm</t>
+          <t>Garpmesliden-Römyran, Pi lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>730893</v>
+        <v>730915</v>
       </c>
       <c r="R100" t="n">
-        <v>7280712</v>
+        <v>7280682</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11310,17 +10783,17 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>En höna med 4 vuxna kycklingar. Den dels försumpade ca 150 till 160 åriga naturskogsresten verkar vara ett viktig häcknings- och födoområde för tjäder.</t>
+          <t>3 järpar i sin hemvist i den fuktiga gamla barrnaturskogen med sumpskogskaraktär som är planerad för kalhuggning och markberedning.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11347,51 +10820,60 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127675440</v>
+        <v>131217412</v>
       </c>
       <c r="B101" t="n">
-        <v>91374</v>
+        <v>57132</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1204</v>
+        <v>102612</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Dubblabergen-Rörmyran , Pi lm</t>
+          <t>Garpmesliden-Römyran, Pi lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>730788</v>
+        <v>730512</v>
       </c>
       <c r="R101" t="n">
-        <v>7280768</v>
+        <v>7281151</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11415,12 +10897,17 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>En tupp och två höns som satt och plockade björkknoppar. Den dels försumpade kallbäckmiljön med sin gamla kontinuitetsskog är en optimal miljö för arten. Även på vintern hittar de födda i gammelskogen.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11429,7 +10916,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11448,10 +10934,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127675502</v>
+        <v>120473807</v>
       </c>
       <c r="B102" t="n">
-        <v>79111</v>
+        <v>58114</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11459,37 +10945,46 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>864</v>
+        <v>103021</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>revir, ej häckning</t>
+        </is>
+      </c>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Dubblabergen-Rörmyran , Pi lm</t>
+          <t>Garpmesliden-Römyran, Pi lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>730812</v>
+        <v>730795</v>
       </c>
       <c r="R102" t="n">
-        <v>7280751</v>
+        <v>7280824</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11516,12 +11011,17 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Ett par med årets ungar i parets hemvist och häckningsrevir</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11530,7 +11030,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11549,38 +11048,46 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128256094</v>
+        <v>121231720</v>
       </c>
       <c r="B103" t="n">
-        <v>98632</v>
+        <v>58114</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -11588,10 +11095,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>730780</v>
+        <v>730749</v>
       </c>
       <c r="R103" t="n">
-        <v>7280790</v>
+        <v>7280849</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -11618,17 +11125,17 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Ett tiotal</t>
+          <t>De sågs även tidigare i sitt revir. Revirparet och kvarvarande ungfåglar.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11637,7 +11144,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11656,10 +11162,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128256204</v>
+        <v>121231798</v>
       </c>
       <c r="B104" t="n">
-        <v>57876</v>
+        <v>58114</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11684,20 +11190,12 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
@@ -11707,10 +11205,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>730780</v>
+        <v>730872</v>
       </c>
       <c r="R104" t="n">
-        <v>7280790</v>
+        <v>7280743</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11737,17 +11235,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Revirparet inom sitt revir som utgörs av en långsmal naturskogsrest med olikåldrig och skitad skog. Området var tidigare klassad som naturvårdsskog av markägaren Sveaskog.</t>
+          <t>Familjeflocken i sitt revir, dvs revirparet med kvarvarande ungfåglar.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11774,10 +11272,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131217375</v>
+        <v>127675430</v>
       </c>
       <c r="B105" t="n">
-        <v>58057</v>
+        <v>58114</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11804,7 +11302,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -11817,17 +11315,17 @@
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Garpmesliden-Römyran, Pi lm</t>
+          <t>Dubblabergen-Rörmyran , Pi lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>730627</v>
+        <v>730767</v>
       </c>
       <c r="R105" t="n">
-        <v>7281017</v>
+        <v>7280795</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11851,17 +11349,17 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Revirparet</t>
+          <t>Ett par som tydligen har revir I området med tre av sina kvarvarande ungar.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11888,40 +11386,44 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131217371</v>
+        <v>128256204</v>
       </c>
       <c r="B106" t="n">
-        <v>58002</v>
+        <v>58114</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
@@ -11935,13 +11437,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>730751</v>
+        <v>730780</v>
       </c>
       <c r="R106" t="n">
-        <v>7280826</v>
+        <v>7280790</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11965,17 +11467,17 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>En familjegrupp i sitt revir där det har gömt sina matförråd i de hänglavdrapperade gammelgranar så att dexklarar den bistra Lapplandvintern.</t>
+          <t>Revirparet inom sitt revir som utgörs av en långsmal naturskogsrest med olikåldrig och skitad skog. Området var tidigare klassad som naturvårdsskog av markägaren Sveaskog.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12002,10 +11504,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131217412</v>
+        <v>131217375</v>
       </c>
       <c r="B107" t="n">
-        <v>57083</v>
+        <v>58114</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12013,26 +11515,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -12049,10 +11551,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>730512</v>
+        <v>730627</v>
       </c>
       <c r="R107" t="n">
-        <v>7281151</v>
+        <v>7281017</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12079,17 +11581,17 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>En tupp och två höns som satt och plockade björkknoppar. Den dels försumpade kallbäckmiljön med sin gamla kontinuitetsskog är en optimal miljö för arten. Även på vintern hittar de födda i gammelskogen.</t>
+          <t>Revirparet</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12116,10 +11618,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131217398</v>
+        <v>120473397</v>
       </c>
       <c r="B108" t="n">
-        <v>57904</v>
+        <v>58057</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12127,16 +11629,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -12146,19 +11648,11 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -12171,13 +11665,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>730857</v>
+        <v>730897</v>
       </c>
       <c r="R108" t="n">
-        <v>7280781</v>
+        <v>7280732</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12201,17 +11695,17 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Det noterades tidigare en revirmakerande hanne och typiska hackringar i området. Troligen samma hanne som har revir i den gamla ca 160 åriga kontinuitetsskogen.</t>
+          <t>En familjgrupp i sitt revir. Det är gruppen som håller till kring Kikkejaureberget/Tjitterberget men mycket av deras revir och hemvist i naturskogsresterna har undan för undan avverkats trots miljölöften av statliga Sveaskog. Även aktuell fyndplats i naturskogsrestfragment är planerad för kalavverkning och markberedning!</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12235,6 +11729,2172 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>121231680</v>
+      </c>
+      <c r="B109" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Garpmesliden-Römyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>730504</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7281155</v>
+      </c>
+      <c r="S109" t="n">
+        <v>5</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Familjgruppen som har tidigare observerats i området, naturskogen verkar tydligen vara en viktig del i deras revir och hemvist.</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>131217371</v>
+      </c>
+      <c r="B110" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Garpmesliden-Römyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>730751</v>
+      </c>
+      <c r="R110" t="n">
+        <v>7280826</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>En familjegrupp i sitt revir där det har gömt sina matförråd i de hänglavdrapperade gammelgranar så att dexklarar den bistra Lapplandvintern.</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>128256094</v>
+      </c>
+      <c r="B111" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Garpmesliden-Römyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>730780</v>
+      </c>
+      <c r="R111" t="n">
+        <v>7280790</v>
+      </c>
+      <c r="S111" t="n">
+        <v>5</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Ett tiotal</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF111" t="inlineStr"/>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>120473201</v>
+      </c>
+      <c r="B112" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Garpmesliden-Römyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>730852</v>
+      </c>
+      <c r="R112" t="n">
+        <v>7280740</v>
+      </c>
+      <c r="S112" t="n">
+        <v>5</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>120470617</v>
+      </c>
+      <c r="B113" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Garpmesliden-Römyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>730776</v>
+      </c>
+      <c r="R113" t="n">
+        <v>7280790</v>
+      </c>
+      <c r="S113" t="n">
+        <v>5</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>120470622</v>
+      </c>
+      <c r="B114" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Garpmesliden-Römyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>730781</v>
+      </c>
+      <c r="R114" t="n">
+        <v>7280800</v>
+      </c>
+      <c r="S114" t="n">
+        <v>5</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>120470646</v>
+      </c>
+      <c r="B115" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Garpmesliden-Römyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>730765</v>
+      </c>
+      <c r="R115" t="n">
+        <v>7280814</v>
+      </c>
+      <c r="S115" t="n">
+        <v>5</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>120470660</v>
+      </c>
+      <c r="B116" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Garpmesliden-Römyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>730744</v>
+      </c>
+      <c r="R116" t="n">
+        <v>7280840</v>
+      </c>
+      <c r="S116" t="n">
+        <v>5</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>120470665</v>
+      </c>
+      <c r="B117" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Garpmesliden-Römyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>730729</v>
+      </c>
+      <c r="R117" t="n">
+        <v>7280851</v>
+      </c>
+      <c r="S117" t="n">
+        <v>5</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>120470809</v>
+      </c>
+      <c r="B118" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Garpmesliden-Römyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>730676</v>
+      </c>
+      <c r="R118" t="n">
+        <v>7280903</v>
+      </c>
+      <c r="S118" t="n">
+        <v>5</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>120470887</v>
+      </c>
+      <c r="B119" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Garpmesliden-Römyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>730622</v>
+      </c>
+      <c r="R119" t="n">
+        <v>7281028</v>
+      </c>
+      <c r="S119" t="n">
+        <v>5</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>120470917</v>
+      </c>
+      <c r="B120" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Garpmesliden-Römyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>730563</v>
+      </c>
+      <c r="R120" t="n">
+        <v>7281056</v>
+      </c>
+      <c r="S120" t="n">
+        <v>5</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120473132</v>
+      </c>
+      <c r="B121" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Garpmesliden-Römyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>730789</v>
+      </c>
+      <c r="R121" t="n">
+        <v>7280765</v>
+      </c>
+      <c r="S121" t="n">
+        <v>5</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>120473159</v>
+      </c>
+      <c r="B122" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Garpmesliden-Römyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>730803</v>
+      </c>
+      <c r="R122" t="n">
+        <v>7280729</v>
+      </c>
+      <c r="S122" t="n">
+        <v>5</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF122" t="inlineStr"/>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>127675433</v>
+      </c>
+      <c r="B123" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Dubblabergen-Rörmyran , Pi lm</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>730767</v>
+      </c>
+      <c r="R123" t="n">
+        <v>7280795</v>
+      </c>
+      <c r="S123" t="n">
+        <v>5</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>127675443</v>
+      </c>
+      <c r="B124" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Dubblabergen-Rörmyran , Pi lm</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>730788</v>
+      </c>
+      <c r="R124" t="n">
+        <v>7280768</v>
+      </c>
+      <c r="S124" t="n">
+        <v>5</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>127675492</v>
+      </c>
+      <c r="B125" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Dubblabergen-Rörmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>730787</v>
+      </c>
+      <c r="R125" t="n">
+        <v>7280750</v>
+      </c>
+      <c r="S125" t="n">
+        <v>5</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>120470812</v>
+      </c>
+      <c r="B126" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Garpmesliden-Römyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>730676</v>
+      </c>
+      <c r="R126" t="n">
+        <v>7280903</v>
+      </c>
+      <c r="S126" t="n">
+        <v>5</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>120470964</v>
+      </c>
+      <c r="B127" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Garpmesliden-Römyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>730499</v>
+      </c>
+      <c r="R127" t="n">
+        <v>7281141</v>
+      </c>
+      <c r="S127" t="n">
+        <v>5</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>120473835</v>
+      </c>
+      <c r="B128" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Garpmesliden-Römyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>730783</v>
+      </c>
+      <c r="R128" t="n">
+        <v>7280820</v>
+      </c>
+      <c r="S128" t="n">
+        <v>5</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>120473635</v>
+      </c>
+      <c r="B129" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Garpmesliden-Römyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>730880</v>
+      </c>
+      <c r="R129" t="n">
+        <v>7280720</v>
+      </c>
+      <c r="S129" t="n">
+        <v>5</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY129"/>
+  <dimension ref="A1:AZ129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470748</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470755</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470789</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470825</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470888</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470896</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470915</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470945</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470997</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473140</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473423</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473492</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473565</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473697</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473592</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470955</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473450</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470475</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2591,6 +2686,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470546</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2692,6 +2792,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470659</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2793,6 +2898,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470701</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2894,6 +3004,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473156</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2995,6 +3110,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473410</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3096,6 +3216,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473443</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3197,6 +3322,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473472</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3298,6 +3428,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473754</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3399,6 +3534,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473775</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3500,6 +3640,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473808</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3601,6 +3746,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473837</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3702,6 +3852,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675502</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3803,6 +3958,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470679</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3904,6 +4064,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470914</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4005,6 +4170,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473129</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4106,6 +4276,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675440</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4207,6 +4382,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470478</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4308,6 +4488,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470620</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4409,6 +4594,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470651</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4510,6 +4700,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470655</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4611,6 +4806,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470705</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4712,6 +4912,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470733</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4813,6 +5018,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470762</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4914,6 +5124,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470820</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5015,6 +5230,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470845</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5116,6 +5336,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470853</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5217,6 +5442,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470872</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5318,6 +5548,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470890</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5419,6 +5654,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470935</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5520,6 +5760,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470940</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5621,6 +5866,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470957</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5722,6 +5972,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473143</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5823,6 +6078,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473148</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5924,6 +6184,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473413</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6025,6 +6290,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473420</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6126,6 +6396,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473444</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6227,6 +6502,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473467</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6328,6 +6608,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473475</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6429,6 +6714,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473746</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6530,6 +6820,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675384</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6631,6 +6926,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675459</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6732,6 +7032,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473699</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6833,6 +7138,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473571</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6934,6 +7244,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473547</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7035,6 +7350,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470697</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7136,6 +7456,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470795</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7237,6 +7562,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473226</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7338,6 +7668,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675482</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7439,6 +7774,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470674</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7540,6 +7880,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470739</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7641,6 +7986,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470828</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7742,6 +8092,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470858</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7843,6 +8198,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470867</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7944,6 +8304,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470889</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8045,6 +8410,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470909</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8146,6 +8516,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470942</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8247,6 +8622,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470967</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8348,6 +8728,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473407</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8449,6 +8834,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473421</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8550,6 +8940,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473462</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8651,6 +9046,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473713</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8752,6 +9152,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473750</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8853,6 +9258,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473756</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8954,6 +9364,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675388</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9055,6 +9470,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470607</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9156,6 +9576,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473194</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9257,6 +9682,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473217</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9358,6 +9788,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473606</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9459,6 +9894,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473626</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9560,6 +10000,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473572</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9677,6 +10122,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470498</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9794,6 +10244,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473485</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9899,6 +10354,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473694</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10017,6 +10477,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231790</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10139,6 +10604,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675337</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10261,6 +10731,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131217398</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10378,6 +10853,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470931</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10492,6 +10972,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473545</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10602,6 +11087,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675544</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10703,6 +11193,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470614</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10817,6 +11312,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473563</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10931,6 +11431,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131217412</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11045,6 +11550,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473807</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11159,6 +11669,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231720</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11269,6 +11784,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231798</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11383,6 +11903,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675430</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11501,6 +12026,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128256204</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11615,6 +12145,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131217375</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11729,6 +12264,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473397</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11839,6 +12379,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231680</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11953,6 +12498,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131217371</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12060,6 +12610,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128256094</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12162,6 +12717,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473201</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12264,6 +12824,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470617</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12366,6 +12931,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470622</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12468,6 +13038,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470646</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12570,6 +13145,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470660</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12672,6 +13252,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470665</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12774,6 +13359,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470809</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12876,6 +13466,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470887</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12978,6 +13573,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470917</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13080,6 +13680,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473132</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13182,6 +13787,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473159</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13284,6 +13894,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675433</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13386,6 +14001,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675443</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13488,6 +14108,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675492</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13590,6 +14215,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470812</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13692,6 +14322,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120470964</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13794,6 +14429,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473835</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13895,8 +14535,143 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120473635</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -2167,7 +2167,7 @@
         <v>136252206</v>
       </c>
       <c r="B16" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136252251</v>
       </c>
       <c r="B17" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136252510</v>
       </c>
       <c r="B18" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136252492</v>
       </c>
       <c r="B21" t="n">
-        <v>83422</v>
+        <v>83423</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136252584</v>
       </c>
       <c r="B23" t="n">
-        <v>79513</v>
+        <v>79514</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>136252259</v>
       </c>
       <c r="B37" t="n">
-        <v>79523</v>
+        <v>79524</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136252411</v>
       </c>
       <c r="B38" t="n">
-        <v>79523</v>
+        <v>79524</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>136252520</v>
       </c>
       <c r="B39" t="n">
-        <v>79523</v>
+        <v>79524</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>136252894</v>
       </c>
       <c r="B40" t="n">
-        <v>79523</v>
+        <v>79524</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>136252466</v>
       </c>
       <c r="B45" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>136252770</v>
       </c>
       <c r="B46" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>136252908</v>
       </c>
       <c r="B47" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>136252214</v>
       </c>
       <c r="B73" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>136252239</v>
       </c>
       <c r="B74" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>136252374</v>
       </c>
       <c r="B75" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>136252691</v>
       </c>
       <c r="B76" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>136252717</v>
       </c>
       <c r="B77" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>136252731</v>
       </c>
       <c r="B78" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>136252743</v>
       </c>
       <c r="B79" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>136252776</v>
       </c>
       <c r="B80" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>136252794</v>
       </c>
       <c r="B81" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>136252848</v>
       </c>
       <c r="B82" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>136252877</v>
       </c>
       <c r="B83" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>136252954</v>
       </c>
       <c r="B84" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>136252218</v>
       </c>
       <c r="B86" t="n">
-        <v>91075</v>
+        <v>91076</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>136252271</v>
       </c>
       <c r="B93" t="n">
-        <v>92527</v>
+        <v>92528</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>136252457</v>
       </c>
       <c r="B110" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>136252545</v>
       </c>
       <c r="B111" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>136252698</v>
       </c>
       <c r="B112" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>136252712</v>
       </c>
       <c r="B113" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>136252748</v>
       </c>
       <c r="B114" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>136252797</v>
       </c>
       <c r="B115" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>136252368</v>
       </c>
       <c r="B121" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>136252235</v>
       </c>
       <c r="B127" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>136252481</v>
       </c>
       <c r="B130" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>136252863</v>
       </c>
       <c r="B134" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>136252672</v>
       </c>
       <c r="B139" t="n">
-        <v>57160</v>
+        <v>57161</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>136252454</v>
       </c>
       <c r="B146" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>136252833</v>
       </c>
       <c r="B150" t="n">
-        <v>58086</v>
+        <v>58087</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>136252222</v>
       </c>
       <c r="B166" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>136252915</v>
       </c>
       <c r="B167" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -2167,7 +2167,7 @@
         <v>136252206</v>
       </c>
       <c r="B16" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136252251</v>
       </c>
       <c r="B17" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136252510</v>
       </c>
       <c r="B18" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136252492</v>
       </c>
       <c r="B21" t="n">
-        <v>83423</v>
+        <v>83427</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136252584</v>
       </c>
       <c r="B23" t="n">
-        <v>79514</v>
+        <v>79518</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>136252259</v>
       </c>
       <c r="B37" t="n">
-        <v>79524</v>
+        <v>79528</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136252411</v>
       </c>
       <c r="B38" t="n">
-        <v>79524</v>
+        <v>79528</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>136252520</v>
       </c>
       <c r="B39" t="n">
-        <v>79524</v>
+        <v>79528</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>136252894</v>
       </c>
       <c r="B40" t="n">
-        <v>79524</v>
+        <v>79528</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>136252466</v>
       </c>
       <c r="B45" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>136252770</v>
       </c>
       <c r="B46" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>136252908</v>
       </c>
       <c r="B47" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>136252214</v>
       </c>
       <c r="B73" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>136252239</v>
       </c>
       <c r="B74" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>136252374</v>
       </c>
       <c r="B75" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>136252691</v>
       </c>
       <c r="B76" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>136252717</v>
       </c>
       <c r="B77" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>136252731</v>
       </c>
       <c r="B78" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>136252743</v>
       </c>
       <c r="B79" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>136252776</v>
       </c>
       <c r="B80" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>136252794</v>
       </c>
       <c r="B81" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>136252848</v>
       </c>
       <c r="B82" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>136252877</v>
       </c>
       <c r="B83" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>136252954</v>
       </c>
       <c r="B84" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>136252218</v>
       </c>
       <c r="B86" t="n">
-        <v>91076</v>
+        <v>91082</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>136252271</v>
       </c>
       <c r="B93" t="n">
-        <v>92528</v>
+        <v>92534</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>136252457</v>
       </c>
       <c r="B110" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>136252545</v>
       </c>
       <c r="B111" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>136252698</v>
       </c>
       <c r="B112" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>136252712</v>
       </c>
       <c r="B113" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>136252748</v>
       </c>
       <c r="B114" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>136252797</v>
       </c>
       <c r="B115" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>136252368</v>
       </c>
       <c r="B121" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>136252235</v>
       </c>
       <c r="B127" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>136252481</v>
       </c>
       <c r="B130" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>136252863</v>
       </c>
       <c r="B134" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>136252672</v>
       </c>
       <c r="B139" t="n">
-        <v>57161</v>
+        <v>57165</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>136252454</v>
       </c>
       <c r="B146" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>136252833</v>
       </c>
       <c r="B150" t="n">
-        <v>58087</v>
+        <v>58091</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>136252222</v>
       </c>
       <c r="B166" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>136252915</v>
       </c>
       <c r="B167" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -2167,7 +2167,7 @@
         <v>136252206</v>
       </c>
       <c r="B16" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136252251</v>
       </c>
       <c r="B17" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136252510</v>
       </c>
       <c r="B18" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136252492</v>
       </c>
       <c r="B21" t="n">
-        <v>83427</v>
+        <v>83428</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136252584</v>
       </c>
       <c r="B23" t="n">
-        <v>79518</v>
+        <v>79519</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>136252259</v>
       </c>
       <c r="B37" t="n">
-        <v>79528</v>
+        <v>79529</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136252411</v>
       </c>
       <c r="B38" t="n">
-        <v>79528</v>
+        <v>79529</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>136252520</v>
       </c>
       <c r="B39" t="n">
-        <v>79528</v>
+        <v>79529</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>136252894</v>
       </c>
       <c r="B40" t="n">
-        <v>79528</v>
+        <v>79529</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>136252466</v>
       </c>
       <c r="B45" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>136252770</v>
       </c>
       <c r="B46" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>136252908</v>
       </c>
       <c r="B47" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>136252214</v>
       </c>
       <c r="B73" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>136252239</v>
       </c>
       <c r="B74" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>136252374</v>
       </c>
       <c r="B75" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>136252691</v>
       </c>
       <c r="B76" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>136252717</v>
       </c>
       <c r="B77" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>136252731</v>
       </c>
       <c r="B78" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>136252743</v>
       </c>
       <c r="B79" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>136252776</v>
       </c>
       <c r="B80" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>136252794</v>
       </c>
       <c r="B81" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>136252848</v>
       </c>
       <c r="B82" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>136252877</v>
       </c>
       <c r="B83" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>136252954</v>
       </c>
       <c r="B84" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>136252218</v>
       </c>
       <c r="B86" t="n">
-        <v>91082</v>
+        <v>91083</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>136252271</v>
       </c>
       <c r="B93" t="n">
-        <v>92534</v>
+        <v>92535</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>136252457</v>
       </c>
       <c r="B110" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>136252545</v>
       </c>
       <c r="B111" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>136252698</v>
       </c>
       <c r="B112" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>136252712</v>
       </c>
       <c r="B113" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>136252748</v>
       </c>
       <c r="B114" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>136252797</v>
       </c>
       <c r="B115" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>136252368</v>
       </c>
       <c r="B121" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>136252235</v>
       </c>
       <c r="B127" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>136252481</v>
       </c>
       <c r="B130" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>136252863</v>
       </c>
       <c r="B134" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>136252672</v>
       </c>
       <c r="B139" t="n">
-        <v>57165</v>
+        <v>57166</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>136252454</v>
       </c>
       <c r="B146" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>136252833</v>
       </c>
       <c r="B150" t="n">
-        <v>58091</v>
+        <v>58092</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>136252222</v>
       </c>
       <c r="B166" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>136252915</v>
       </c>
       <c r="B167" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -2167,7 +2167,7 @@
         <v>136252206</v>
       </c>
       <c r="B16" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136252251</v>
       </c>
       <c r="B17" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136252510</v>
       </c>
       <c r="B18" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136252492</v>
       </c>
       <c r="B21" t="n">
-        <v>83428</v>
+        <v>83432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136252584</v>
       </c>
       <c r="B23" t="n">
-        <v>79519</v>
+        <v>79523</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>136252259</v>
       </c>
       <c r="B37" t="n">
-        <v>79529</v>
+        <v>79533</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136252411</v>
       </c>
       <c r="B38" t="n">
-        <v>79529</v>
+        <v>79533</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>136252520</v>
       </c>
       <c r="B39" t="n">
-        <v>79529</v>
+        <v>79533</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>136252894</v>
       </c>
       <c r="B40" t="n">
-        <v>79529</v>
+        <v>79533</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>136252466</v>
       </c>
       <c r="B45" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>136252770</v>
       </c>
       <c r="B46" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>136252908</v>
       </c>
       <c r="B47" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>136252214</v>
       </c>
       <c r="B73" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>136252239</v>
       </c>
       <c r="B74" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>136252374</v>
       </c>
       <c r="B75" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>136252691</v>
       </c>
       <c r="B76" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>136252717</v>
       </c>
       <c r="B77" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>136252731</v>
       </c>
       <c r="B78" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>136252743</v>
       </c>
       <c r="B79" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>136252776</v>
       </c>
       <c r="B80" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>136252794</v>
       </c>
       <c r="B81" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>136252848</v>
       </c>
       <c r="B82" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>136252877</v>
       </c>
       <c r="B83" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>136252954</v>
       </c>
       <c r="B84" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>136252218</v>
       </c>
       <c r="B86" t="n">
-        <v>91083</v>
+        <v>91089</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>136252271</v>
       </c>
       <c r="B93" t="n">
-        <v>92535</v>
+        <v>92541</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>136252457</v>
       </c>
       <c r="B110" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>136252545</v>
       </c>
       <c r="B111" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>136252698</v>
       </c>
       <c r="B112" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>136252712</v>
       </c>
       <c r="B113" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>136252748</v>
       </c>
       <c r="B114" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>136252797</v>
       </c>
       <c r="B115" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>136252368</v>
       </c>
       <c r="B121" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>136252222</v>
       </c>
       <c r="B166" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>136252915</v>
       </c>
       <c r="B167" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -2167,7 +2167,7 @@
         <v>136252206</v>
       </c>
       <c r="B16" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136252251</v>
       </c>
       <c r="B17" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136252510</v>
       </c>
       <c r="B18" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136252492</v>
       </c>
       <c r="B21" t="n">
-        <v>83432</v>
+        <v>83438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136252584</v>
       </c>
       <c r="B23" t="n">
-        <v>79523</v>
+        <v>79529</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>136252259</v>
       </c>
       <c r="B37" t="n">
-        <v>79533</v>
+        <v>79539</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136252411</v>
       </c>
       <c r="B38" t="n">
-        <v>79533</v>
+        <v>79539</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>136252520</v>
       </c>
       <c r="B39" t="n">
-        <v>79533</v>
+        <v>79539</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>136252894</v>
       </c>
       <c r="B40" t="n">
-        <v>79533</v>
+        <v>79539</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>136252466</v>
       </c>
       <c r="B45" t="n">
-        <v>92094</v>
+        <v>92101</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>136252770</v>
       </c>
       <c r="B46" t="n">
-        <v>92094</v>
+        <v>92101</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>136252908</v>
       </c>
       <c r="B47" t="n">
-        <v>92094</v>
+        <v>92101</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>136252214</v>
       </c>
       <c r="B73" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>136252239</v>
       </c>
       <c r="B74" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>136252374</v>
       </c>
       <c r="B75" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>136252691</v>
       </c>
       <c r="B76" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>136252717</v>
       </c>
       <c r="B77" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>136252731</v>
       </c>
       <c r="B78" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>136252743</v>
       </c>
       <c r="B79" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>136252776</v>
       </c>
       <c r="B80" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>136252794</v>
       </c>
       <c r="B81" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>136252848</v>
       </c>
       <c r="B82" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>136252877</v>
       </c>
       <c r="B83" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>136252954</v>
       </c>
       <c r="B84" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>136252218</v>
       </c>
       <c r="B86" t="n">
-        <v>91089</v>
+        <v>91096</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>136252271</v>
       </c>
       <c r="B93" t="n">
-        <v>92541</v>
+        <v>92548</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>136252457</v>
       </c>
       <c r="B110" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>136252545</v>
       </c>
       <c r="B111" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>136252698</v>
       </c>
       <c r="B112" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>136252712</v>
       </c>
       <c r="B113" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>136252748</v>
       </c>
       <c r="B114" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>136252797</v>
       </c>
       <c r="B115" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>136252368</v>
       </c>
       <c r="B121" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>136252235</v>
       </c>
       <c r="B127" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>136252481</v>
       </c>
       <c r="B130" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>136252863</v>
       </c>
       <c r="B134" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>136252672</v>
       </c>
       <c r="B139" t="n">
-        <v>57166</v>
+        <v>57171</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>136252454</v>
       </c>
       <c r="B146" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>136252833</v>
       </c>
       <c r="B150" t="n">
-        <v>58092</v>
+        <v>58097</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>136252222</v>
       </c>
       <c r="B166" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>136252915</v>
       </c>
       <c r="B167" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -5246,7 +5246,7 @@
         <v>136252466</v>
       </c>
       <c r="B45" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>136252770</v>
       </c>
       <c r="B46" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>136252908</v>
       </c>
       <c r="B47" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>136252218</v>
       </c>
       <c r="B86" t="n">
-        <v>91096</v>
+        <v>91097</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>136252271</v>
       </c>
       <c r="B93" t="n">
-        <v>92548</v>
+        <v>92549</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>136252222</v>
       </c>
       <c r="B166" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>136252915</v>
       </c>
       <c r="B167" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -2167,7 +2167,7 @@
         <v>136252206</v>
       </c>
       <c r="B16" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136252251</v>
       </c>
       <c r="B17" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136252510</v>
       </c>
       <c r="B18" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136252492</v>
       </c>
       <c r="B21" t="n">
-        <v>83438</v>
+        <v>83451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136252584</v>
       </c>
       <c r="B23" t="n">
-        <v>79529</v>
+        <v>79542</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>136252259</v>
       </c>
       <c r="B37" t="n">
-        <v>79539</v>
+        <v>79552</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136252411</v>
       </c>
       <c r="B38" t="n">
-        <v>79539</v>
+        <v>79552</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>136252520</v>
       </c>
       <c r="B39" t="n">
-        <v>79539</v>
+        <v>79552</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>136252894</v>
       </c>
       <c r="B40" t="n">
-        <v>79539</v>
+        <v>79552</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>136252466</v>
       </c>
       <c r="B45" t="n">
-        <v>92102</v>
+        <v>92115</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>136252770</v>
       </c>
       <c r="B46" t="n">
-        <v>92102</v>
+        <v>92115</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>136252908</v>
       </c>
       <c r="B47" t="n">
-        <v>92102</v>
+        <v>92115</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>136252214</v>
       </c>
       <c r="B73" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>136252239</v>
       </c>
       <c r="B74" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>136252374</v>
       </c>
       <c r="B75" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>136252691</v>
       </c>
       <c r="B76" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>136252717</v>
       </c>
       <c r="B77" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>136252731</v>
       </c>
       <c r="B78" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>136252743</v>
       </c>
       <c r="B79" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>136252776</v>
       </c>
       <c r="B80" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>136252794</v>
       </c>
       <c r="B81" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>136252848</v>
       </c>
       <c r="B82" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>136252877</v>
       </c>
       <c r="B83" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>136252954</v>
       </c>
       <c r="B84" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>136252218</v>
       </c>
       <c r="B86" t="n">
-        <v>91097</v>
+        <v>91110</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>136252271</v>
       </c>
       <c r="B93" t="n">
-        <v>92549</v>
+        <v>92562</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>136252457</v>
       </c>
       <c r="B110" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>136252545</v>
       </c>
       <c r="B111" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>136252698</v>
       </c>
       <c r="B112" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>136252712</v>
       </c>
       <c r="B113" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>136252748</v>
       </c>
       <c r="B114" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>136252797</v>
       </c>
       <c r="B115" t="n">
-        <v>83447</v>
+        <v>83460</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>136252368</v>
       </c>
       <c r="B121" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>136252235</v>
       </c>
       <c r="B127" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>136252481</v>
       </c>
       <c r="B130" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>136252863</v>
       </c>
       <c r="B134" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>136252672</v>
       </c>
       <c r="B139" t="n">
-        <v>57171</v>
+        <v>57184</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>136252454</v>
       </c>
       <c r="B146" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>136252833</v>
       </c>
       <c r="B150" t="n">
-        <v>58097</v>
+        <v>58110</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>136252222</v>
       </c>
       <c r="B166" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>136252915</v>
       </c>
       <c r="B167" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -2167,7 +2167,7 @@
         <v>136252206</v>
       </c>
       <c r="B16" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136252251</v>
       </c>
       <c r="B17" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136252510</v>
       </c>
       <c r="B18" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136252492</v>
       </c>
       <c r="B21" t="n">
-        <v>83451</v>
+        <v>83452</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136252584</v>
       </c>
       <c r="B23" t="n">
-        <v>79542</v>
+        <v>79543</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>136252259</v>
       </c>
       <c r="B37" t="n">
-        <v>79552</v>
+        <v>79553</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136252411</v>
       </c>
       <c r="B38" t="n">
-        <v>79552</v>
+        <v>79553</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>136252520</v>
       </c>
       <c r="B39" t="n">
-        <v>79552</v>
+        <v>79553</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>136252894</v>
       </c>
       <c r="B40" t="n">
-        <v>79552</v>
+        <v>79553</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>136252466</v>
       </c>
       <c r="B45" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>136252770</v>
       </c>
       <c r="B46" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>136252908</v>
       </c>
       <c r="B47" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>136252214</v>
       </c>
       <c r="B73" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>136252239</v>
       </c>
       <c r="B74" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>136252374</v>
       </c>
       <c r="B75" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>136252691</v>
       </c>
       <c r="B76" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>136252717</v>
       </c>
       <c r="B77" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>136252731</v>
       </c>
       <c r="B78" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>136252743</v>
       </c>
       <c r="B79" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>136252776</v>
       </c>
       <c r="B80" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>136252794</v>
       </c>
       <c r="B81" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>136252848</v>
       </c>
       <c r="B82" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>136252877</v>
       </c>
       <c r="B83" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>136252954</v>
       </c>
       <c r="B84" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>136252218</v>
       </c>
       <c r="B86" t="n">
-        <v>91110</v>
+        <v>91111</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>136252271</v>
       </c>
       <c r="B93" t="n">
-        <v>92562</v>
+        <v>92563</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>136252457</v>
       </c>
       <c r="B110" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>136252545</v>
       </c>
       <c r="B111" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>136252698</v>
       </c>
       <c r="B112" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>136252712</v>
       </c>
       <c r="B113" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>136252748</v>
       </c>
       <c r="B114" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>136252797</v>
       </c>
       <c r="B115" t="n">
-        <v>83460</v>
+        <v>83461</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>136252368</v>
       </c>
       <c r="B121" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>136252222</v>
       </c>
       <c r="B166" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>136252915</v>
       </c>
       <c r="B167" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
